--- a/docs/examples/demo-cko-3_FERG.xlsx
+++ b/docs/examples/demo-cko-3_FERG.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C440"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,7 +517,7 @@
         <v>[R_01_闪光]</v>
       </c>
       <c r="C11" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>[R_01_闪光背景]</v>
       </c>
       <c r="C12" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>[R_01_采样]</v>
       </c>
       <c r="C13" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>[R_01_分析时间]</v>
       </c>
       <c r="C14" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="15">
@@ -572,7 +572,7 @@
         <v>[R_01_详细数据(uv)]</v>
       </c>
       <c r="C16" t="str">
-        <v>0.02,0.04,0.06,0.08,0.1,0.12,0.14,0.16,0.18,0.2,0.22,0.25,0.27,0.29,0.31,0.33,0.35,0.37,0.39,0.41,0.43,0.45,0.47,0.49,0.51,0.53,0.55,0.57,0.58,0.6,0.62,0.64,0.66,0.67,0.69,0.7,0.72,0.73,0.74,0.75,0.76,0.76,0.77,0.76,0.76,0.75,0.73,0.71,0.69,0.65,0.61,0.55,0.49,0.41,0.32,0.21,0.09,-0.05,-0.22,-0.4,-0.61,-0.85,-1.12,-1.43,-1.76,-2.14,-2.55,-3,-3.5,-4.05,-4.64,-5.28,-5.97,-6.72,-7.52,-8.37,-9.28,-10.24,-11.25,-12.31,-13.41,-14.57,-15.76,-16.99,-18.24,-19.52,-20.82,-22.13,-23.43,-24.73,-26.01,-27.26,-28.46,-29.62,-30.71,-31.72,-32.64,-33.45,-34.15,-34.72,-35.15,-35.42,-35.53,-35.45,-35.2,-34.74,-34.08,-33.2,-32.11,-30.78,-29.23,-27.44,-25.42,-23.16,-20.66,-17.93,-14.96,-11.77,-8.36,-4.72,-0.88,3.17,7.41,11.84,16.45,21.22,26.15,31.22,36.43,41.76,47.21,52.75,58.39,64.12,69.91,75.76,81.66,87.61,93.58,99.58,105.59,111.61,117.62,123.61,129.59,135.54,141.45,147.31,153.13,158.88,164.56,170.16,175.68,181.1,186.42,191.63,196.72,201.69,206.51,211.2,215.73,220.1,224.3,228.33,232.17,235.81,239.26,242.49,245.52,248.31,250.89,253.22,255.32,257.17,258.78,260.13,261.23,262.07,262.65,262.97,263.02,262.82,262.36,261.64,260.66,259.43,257.96,256.24,254.28,252.09,249.67,247.03,244.18,241.13,237.88,234.45,230.83,227.06,223.13,219.05,214.83,210.49,206.04,201.49,196.85,192.12,187.33,182.48,177.59,172.66,167.7,162.73,157.76,152.79,147.83,142.9,138.01,133.15,128.34,123.59,118.9,114.28,109.74,105.28,100.91,96.63,92.45,88.36,84.38,80.5,76.74,73.08,69.53,66.1,62.78,59.57,56.48,53.51,50.64,47.89,45.25,42.71,40.29,37.97,35.75,33.64,31.62,29.7,27.88,26.14,24.5,22.93,21.45,20.05,18.72,17.47,16.28,15.16,14.11,13.11,12.17,11.29,10.45,9.67,8.93,8.23,7.57,6.95,6.37,5.82,5.3,4.81,4.34,3.9,3.48,3.08,2.7,2.34,1.99,1.66,1.34,1.03,0.73,0.44,0.16,-0.11,-0.38,-0.65,-0.91,-1.17,-1.43,-1.68,-1.94,-2.19,-2.44,-2.7,-2.96,-3.21,-3.47,-3.74,-4,-4.27,-4.55,-4.83,-5.11,-5.39,-5.68,-5.98,-6.28,-6.59,-6.9,-7.22,-7.54,-7.87,-8.2,-8.54,-8.88,-9.24,-9.59,-9.96,-10.32,-10.7,-11.08,-11.47,-11.86,-12.25,-12.66,-13.07,-13.48,-13.9,-14.32,-14.75,-15.19,-15.63,-16.07,-16.52,-16.97,-17.43,-17.89,-18.36,-18.83,-19.3,-19.77,-20.25,-20.73,-21.21,-21.7,-22.19,-22.68,-23.17,-23.66,-24.15,-24.65,-25.14,-25.63,-26.13,-26.62,-27.11,-27.6,-28.09,-28.58,-29.06,-29.54,-30.02,-30.5,-30.97,-31.44,-31.9,-32.36,-32.82,-33.27,-33.71,-34.15,-34.58,-35.01,-35.43,-35.84,-36.24,-36.64,-37.02,-37.4,-37.77,-38.13,-38.48,-38.82,-39.16,-39.48,-39.79,-40.09,-40.37,-40.65,-40.92,-41.17,-41.41,-41.64,-41.86,-42.06,-42.25,-42.43,-42.6,-42.75,-42.89,-43.01,-43.12,-43.22,-43.3,-43.38,-43.43,-43.47,-43.5,-43.52,-43.52,-43.51,-43.48,-43.44,-43.38,-43.32,-43.23,-43.14,-43.03,-42.91,-42.77,-42.62,-42.46,-42.29,-42.1,-41.9,-41.69,-41.47,-41.23,-40.99,-40.73,-40.46,-40.18,-39.89,-39.59,-39.29,-38.97,-38.64,-38.3,-37.95,-37.6,-37.24,-36.86,-36.49,-36.1,-35.71,-35.31,-34.91,-34.49,-34.08,-33.66,-33.23,-32.8,-32.37,-31.93,-31.49,-31.04,-30.59,-30.14,-29.69,-29.24,-28.78,-28.33,-27.87,-27.41,-26.95,-26.5,-26.04,-25.58,-25.13,-24.67,-24.22,-23.77,-23.32,-22.87,-22.43,-21.99,-21.55,-21.11,-20.68,-20.25,-19.83,-19.41,-18.99,-18.58,-18.17,-17.77,-17.37,-16.98,-16.59,-16.21,-15.83,-15.46,-15.09,-14.73,-14.38,-14.03,-13.68,-13.35</v>
+        <v>-17.65,-17.35,-17.04,-16.72,-16.37,-16.01,-15.65,-15.27,-14.88,-14.49,-14.1,-13.7,-13.31,-12.92,-12.54,-12.17,-11.81,-11.46,-11.12,-10.81,-10.51,-10.23,-9.98,-9.75,-9.55,-9.37,-9.22,-9.1,-9.01,-8.95,-8.92,-8.92,-8.95,-9.01,-9.1,-9.23,-9.38,-9.56,-9.76,-9.99,-10.25,-10.53,-10.83,-11.15,-11.48,-11.84,-12.2,-12.58,-12.97,-13.36,-13.76,-14.19,-14.59,-14.98,-15.4,-15.76,-16.21,-16.55,-16.97,-17.39,-17.67,-18.04,-18.52,-18.91,-19.25,-19.33,-19.8,-19.74,-20.51,-20.83,-21.34,-21.31,-21.15,-22.13,-22.77,-22.22,-23.28,-22.97,-23.27,-23.16,-26.12,-23.91,-24.33,-28.1,-28.19,-26.66,-26.61,-29.25,-32.22,-30.31,-28.8,-34.92,-32.56,-36.52,-30.84,-38.87,-37.03,-33.71,-34.49,-39.92,-32.55,-40.87,-43.6,-36.2,-37.15,-33.45,-39.16,-32.67,-33.89,-42.23,-37.99,-40.36,-31.25,-33.93,-29.41,-35.09,-27.75,-26.6,-29,-22.8,-19.8,-15.84,-18.32,-11.87,-5.76,-5.91,-7.7,2.95,-0.98,10.49,14.37,17.8,14.05,20.26,22.29,29.94,35.83,41.33,32.57,39.78,41.77,62.6,54.11,63.1,74.09,82.36,70.35,93.58,91.43,95.65,81.79,103.03,119.16,98.15,111.81,122.97,115.67,115.58,115.21,150.22,126.81,132.62,156.83,162.92,164.05,172.51,158.2,173.32,186.07,175.35,171.97,174.96,171.91,174.14,178.32,216.02,197.95,213.33,190.75,185.38,197.36,201.82,209.19,195.01,196.59,193.99,193.4,195.89,176.51,193.51,179.67,169.2,185.46,186.98,184.19,193.02,160.99,177.11,150.21,174.32,146.21,161.2,141.98,157.05,148.55,119.73,128.59,140.37,119.6,114.83,108.38,99.06,110.63,104.02,92.88,82.13,82.24,85.18,76.03,76.47,65.54,52.17,51.35,45.34,51.74,48.6,44.19,42.82,30.78,26.2,27.12,20.32,21.91,17.04,20.23,12.54,13.76,10.82,12.77,5.65,7.05,3.19,4.36,3.44,3.43,0.37,2.15,0.61,0.43,0.62,0.02,-0.54,-0.35,-0.53,-1.48,-0.19,-0.78,-0.35,-1.08,-0.01,-0.09,0.2,0.31,0.72,0.45,0.38,0.6,1.26,1.18,1.67,1.61,1.64,1.87,1.54,1.28,1.7,0.47,1.02,1.13,0.24,0.03,-0.59,-0.46,-1.53,-1.47,-3.39,-3.1,-3.43,-4.09,-4.43,-5.11,-6.05,-8.24,-9.12,-8.63,-9.15,-10.92,-12.96,-12.15,-14.59,-12.92,-14.63,-17,-17.11,-16.58,-17.11,-18.87,-18.21,-20.6,-22.56,-19.73,-23.34,-24.27,-21.78,-21.86,-24.1,-24.89,-22.77,-23.75,-26.26,-25.08,-22.16,-23.86,-26.96,-22.15,-26.88,-24.26,-23.74,-24.71,-22.79,-22.73,-23.41,-18.82,-18.18,-24.86,-23.2,-22.05,-23.72,-20.56,-21,-15.63,-20.81,-15.74,-16.01,-15.64,-12.17,-16.08,-18.74,-14.65,-11.09,-16.94,-14.59,-11.56,-17.64,-20.74,-10.69,-16.44,-9.89,-21.83,-21.89,-11.17,-12.33,-20.83,-15.27,-17.81,-15.23,-25.96,-20.71,-15.8,-17.61,-23.72,-31.98,-28.72,-25.74,-26.86,-33.05,-26.93,-34.86,-27.32,-40.43,-40.92,-38.98,-34.96,-43.79,-31.96,-39.92,-44.32,-35.38,-49,-42.04,-34.7,-41.23,-36.41,-50.05,-47.85,-46.6,-53.15,-52.88,-48.36,-50.24,-38.88,-53.8,-55.44,-42.12,-45.66,-43.47,-50.31,-49.79,-52.73,-50.98,-35.62,-38.43,-37.89,-34.31,-34.95,-31.69,-44.34,-33.19,-40.77,-41.63,-34.14,-44.48,-40.85,-34.25,-35.5,-29.86,-34.6,-35.28,-33.79,-24.43,-24.12,-20.28,-21.16,-26.88,-26.1,-20.81,-18.71,-22.03,-29.25,-22.52,-14.98,-28.28,-22.64,-13.99,-12.54,-25.58,-15.51,-14.97,-24.74,-25.54,-13.69,-23.84,-14.98,-12.82,-23.94,-23.72,-19.16,-24.48,-17.66,-16.88,-17.29,-18.18,-20.73,-23.03,-26.71,-24.63,-26.61,-28.69,-23.82,-27.55,-20.95,-26.09,-21.47,-21.71,-25.62,-25.8,-24.08,-23.1,-26.24,-26.88,-29.99,-26.59,-27.47,-27.12,-23.89,-24.39,-21.51,-24.32,-24.6,-21.59,-21.91,-22.9,-23.59,-22.76,-16.83,-16.57,-19.57,-16.67,-14.27,-16.25</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>[R_01_标记]</v>
       </c>
       <c r="C17" t="str">
-        <v>a: 17.6ms -58.2uv b: 36.6ms 267.1uv</v>
+        <v>a: 15.2ms -15.9uv b: 34.5ms 59.8uv</v>
       </c>
     </row>
     <row r="18">
@@ -616,7 +616,7 @@
         <v>[L_01_闪光]</v>
       </c>
       <c r="C20" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>[L_01_闪光背景]</v>
       </c>
       <c r="C21" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="22">
@@ -638,7 +638,7 @@
         <v>[L_01_采样]</v>
       </c>
       <c r="C22" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="23">
@@ -649,7 +649,7 @@
         <v>[L_01_分析时间]</v>
       </c>
       <c r="C23" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="24">
@@ -671,7 +671,7 @@
         <v>[L_01_详细数据(uv)]</v>
       </c>
       <c r="C25" t="str">
-        <v>1.1,2.05,2.71,2.99,2.85,2.31,1.45,0.38,-0.74,-1.76,-2.53,-2.95,-2.95,-2.54,-1.77,-0.75,0.37,1.44,2.3,2.85,2.99,2.72,2.06,1.12,0.01,-1.09,-2.05,-2.71,-3,-2.86,-2.33,-1.47,-0.41,0.71,1.73,2.5,2.91,2.92,2.5,1.73,0.7,-0.43,-1.52,-2.41,-2.98,-3.16,-2.92,-2.31,-1.41,-0.36,0.69,1.58,2.17,2.37,2.13,1.48,0.49,-0.73,-2.02,-3.24,-4.23,-4.9,-5.18,-5.08,-4.66,-4.01,-3.3,-2.67,-2.28,-2.26,-2.67,-3.56,-4.88,-6.54,-8.41,-10.33,-12.16,-13.75,-15.01,-15.9,-16.43,-16.67,-16.74,-16.79,-16.97,-17.4,-18.21,-19.44,-21.08,-23.07,-25.3,-27.6,-29.83,-31.81,-33.4,-34.53,-35.14,-35.28,-35.01,-34.46,-33.77,-33.09,-32.52,-32.17,-32.06,-32.17,-32.42,-32.67,-32.78,-32.57,-31.91,-30.68,-28.81,-26.31,-23.22,-19.66,-15.77,-11.71,-7.63,-3.66,0.1,3.64,6.97,10.19,13.4,16.77,20.43,24.5,29.08,34.2,39.82,45.87,52.22,58.71,65.17,71.45,77.43,83.03,88.25,93.13,97.76,102.29,106.85,111.59,116.63,122.04,127.84,133.98,140.36,146.86,153.3,159.52,165.38,170.77,175.66,180.03,183.96,187.56,190.97,194.33,197.79,201.45,205.36,209.51,213.86,218.28,222.63,226.74,230.46,233.66,236.24,238.18,239.51,240.32,240.72,240.88,240.93,241.03,241.25,241.65,242.21,242.86,243.47,243.91,244.02,243.66,242.71,241.12,238.9,236.09,232.81,229.21,225.45,221.68,218.05,214.64,211.48,208.55,205.78,203.04,200.18,197.07,193.58,189.61,185.14,180.2,174.85,169.23,163.5,157.83,152.37,147.25,142.53,138.23,134.3,130.67,127.18,123.69,120.06,116.18,111.95,107.37,102.48,97.36,92.16,87.02,82.12,77.58,73.51,69.96,66.92,64.32,62.04,59.94,57.86,55.65,53.2,50.45,47.39,44.06,40.59,37.09,33.73,30.66,27.99,25.82,24.16,22.97,22.18,21.65,21.21,20.72,20.03,19.04,17.71,16.04,14.09,11.99,9.88,7.91,6.22,4.94,4.1,3.73,3.77,4.12,4.62,5.13,5.48,5.56,5.27,4.58,3.53,2.21,0.73,-0.76,-2.08,-3.12,-3.78,-4,-3.8,-3.25,-2.48,-1.62,-0.84,-0.28,-0.06,-0.25,-0.84,-1.81,-3.03,-4.38,-5.69,-6.83,-7.65,-8.08,-8.09,-7.71,-7.03,-6.18,-5.31,-4.58,-4.12,-4.03,-4.37,-5.11,-6.2,-7.52,-8.92,-10.24,-11.33,-12.09,-12.44,-12.39,-11.97,-11.29,-10.49,-9.72,-9.14,-8.87,-9.01,-9.56,-10.52,-11.78,-13.23,-14.71,-16.05,-17.14,-17.86,-18.16,-18.07,-17.64,-16.99,-16.26,-15.63,-15.22,-15.16,-15.51,-16.28,-17.42,-18.83,-20.38,-21.9,-23.24,-24.28,-24.93,-25.16,-25,-24.54,-23.9,-23.23,-22.7,-22.43,-22.53,-23.05,-23.98,-25.25,-26.74,-28.31,-29.8,-31.06,-31.98,-32.49,-32.58,-32.3,-31.75,-31.06,-30.39,-29.89,-29.7,-29.9,-30.51,-31.5,-32.8,-34.27,-35.76,-37.12,-38.2,-38.91,-39.19,-39.05,-38.57,-37.85,-37.04,-36.3,-35.77,-35.57,-35.77,-36.37,-37.34,-38.56,-39.91,-41.22,-42.34,-43.15,-43.55,-43.53,-43.09,-42.34,-41.39,-40.4,-39.52,-38.9,-38.63,-38.77,-39.3,-40.16,-41.23,-42.38,-43.44,-44.26,-44.73,-44.78,-44.4,-43.64,-42.59,-41.39,-40.21,-39.18,-38.45,-38.09,-38.14,-38.58,-39.31,-40.21,-41.13,-41.92,-42.43,-42.56,-42.27,-41.55,-40.48,-39.17,-37.77,-36.43,-35.3,-34.49,-34.09,-34.09,-34.46,-35.09,-35.85,-36.58,-37.13,-37.38,-37.22,-36.64,-35.66,-34.36,-32.87,-31.35,-29.94,-28.79,-28,-27.62,-27.65,-28.02,-28.62,-29.31,-29.92,-30.3,-30.36,-30,-29.23,-28.08,-26.65,-25.09,-23.55,-22.18,-21.11,-20.43,-20.17,-20.31,-20.76,-21.4,-22.08,-22.64,-22.94,-22.88,-22.4,-21.52,-20.3,-18.84,-17.31,-15.84,-14.6,-13.7,-13.2,-13.13,-13.44,-14.03,-14.76,-15.48,-16.04,-16.3,-16.18,-15.64,-14.72,-13.49,-12.07</v>
+        <v>6.71,7.66,8.57,9.43,10.24,10.99,11.69,12.33,12.91,13.44,13.89,14.29,14.62,14.89,15.09,15.23,15.3,15.31,15.25,15.14,14.96,14.72,14.42,14.07,13.66,13.2,12.69,12.14,11.54,10.89,10.21,9.5,8.75,7.97,7.17,6.35,5.5,4.64,3.77,2.89,2.01,1.12,0.24,-0.64,-1.51,-2.37,-3.22,-4.05,-4.86,-5.64,-6.4,-7.14,-7.84,-8.52,-9.16,-9.77,-10.33,-10.88,-11.36,-11.84,-12.25,-12.63,-12.96,-13.3,-13.54,-13.77,-13.93,-14.05,-14.27,-14.4,-14.36,-14.34,-14.47,-14.47,-14.36,-14.27,-14.13,-14.24,-14.55,-14.42,-14.03,-14.07,-13.79,-13.9,-13.46,-13.6,-14.81,-14.31,-15.26,-14.91,-15.32,-14.05,-15.8,-14.79,-15.87,-14.14,-17.72,-16.19,-17.31,-19.27,-19.6,-19.98,-16.36,-23.16,-20.76,-21.74,-18.11,-25.04,-18.29,-26.05,-20.81,-26.83,-21.05,-23.36,-21.83,-26.49,-25.26,-24.43,-20.92,-19.54,-15.16,-15.52,-16.55,-20.15,-17.19,-21.11,-12.35,-7.76,-6.47,-1.34,0.2,-1.49,4.51,2.49,3.4,4.81,12.84,16.91,28.79,25.07,26.61,30.15,39.47,37.95,48.09,50.9,44.5,62.52,67.23,72.95,65.33,74.15,82.89,77.61,99.53,103.13,101.37,109.4,115.57,111.11,121.83,104.05,129.56,134.31,141.84,149,130.26,140.73,145.41,143.15,140.24,151.4,145.09,147.78,156.49,156.76,156,186.92,195.32,199.14,200.27,173.59,198.63,182.16,191.9,206.31,184.72,176.76,184.48,202.43,178,170.41,207.54,173.23,195.86,200.44,184.17,201,184.24,175.71,191.06,200.21,181.1,196.19,179.62,177.69,178.67,167.6,174.12,173.13,154.47,154.86,151.02,164.22,154.11,138.24,139.79,131.75,132.42,134.78,138.37,121.01,115.41,106.26,105.67,117.01,115.14,93.02,109.19,107.74,86.81,86.88,88.47,81.76,87.02,78.05,71.38,69.13,72.4,72.33,74.48,66.77,64.1,58.81,57.63,64.59,56.14,57.66,55.23,55.1,51.86,46.24,46.68,46.52,44.97,44.33,40.88,38.78,39.7,37.69,35.74,34.12,33.19,33.23,32.08,28.8,28.9,26.79,25.28,22.98,21.53,20.29,18.72,18.18,16.16,14.54,13.79,12.83,10.74,9.43,7.59,6.67,5.44,4.34,2.44,0.28,-0.28,-2.21,-2.86,-4.78,-5.99,-7.07,-7.86,-8.43,-10,-11.54,-12.81,-13.15,-13.98,-15.66,-14.74,-16.66,-16.4,-17.7,-18.3,-17.39,-18.66,-18.41,-18.3,-19.82,-20.17,-20.41,-18.26,-19.62,-19.65,-18.56,-19.03,-18.17,-17.73,-18.22,-17.72,-13.8,-12.68,-13.99,-12.63,-11.81,-10.16,-8.13,-7.29,-9.22,-5.07,-8.83,-3.48,-2.69,-5.53,0.69,-0.45,1.28,-0.92,2.29,-0.36,1.35,2.65,5.31,6.42,3.46,6.98,5.05,9,10.43,11.84,10.42,8.77,11.09,14.35,13.82,13.27,9.2,8.72,12.04,6.57,13.85,14.18,12.89,9.11,10.44,3.25,4.66,6.99,6.66,-1.94,-0.26,-2.76,-3.76,-5.22,-0.18,-10.39,-5.48,-8.33,-4.23,-14.2,-7.98,-8.6,-19.08,-21.17,-12.42,-21.22,-21.07,-19.8,-24.29,-27.08,-30.51,-25.87,-33.04,-37.52,-28.84,-28.38,-34.14,-36.09,-40.33,-45.65,-33.95,-45.27,-39.08,-49.46,-36,-39.73,-49.96,-49.84,-41.24,-51.3,-45.76,-44,-46.72,-52.1,-34.56,-43.33,-33.25,-40.6,-43.59,-46.94,-31.64,-38.75,-44.15,-39.34,-32.33,-41.52,-35,-36.35,-37.77,-32.03,-25.72,-24.45,-31.57,-18.62,-20.38,-31.59,-21.93,-24.99,-27.18,-10.93,-10.94,-24.29,-15.56,-21.04,-9.09,-3.8,-11.17,-18.02,-9.73,-3.05,-2.44,-4.33,-7.43,-0.08,-10.87,-7,4.62,-5.53,-4.76,4.64,-0.1,2.06,3.63,-3.73,-2.57,0.95,4.4,-4.28,1.52,0.61,-2.48,7.23,1.41,2.02,-2.61,5.67,3.37,4.32,-3.33,-0.31,2.46,0.12,-1.15,2.98,-1.88,-0.46,-3.43,-6.92,-0.69,-6.08,-1.59,-1.94,-2.58,-6.16,-7.49,-3.99,-9.55,-8.64,-7.51</v>
       </c>
     </row>
     <row r="26">
@@ -682,7 +682,7 @@
         <v>[L_01_标记]</v>
       </c>
       <c r="C26" t="str">
-        <v>a: 17.6ms -54.7uv b: 36.6ms 251.1uv</v>
+        <v>a: 15.4ms -18.6uv b: 34.6ms 98.8uv</v>
       </c>
     </row>
     <row r="27">
@@ -693,7 +693,7 @@
         <v>[R_02_名字]</v>
       </c>
       <c r="C27" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="28">
@@ -715,7 +715,7 @@
         <v>[R_02_闪光]</v>
       </c>
       <c r="C29" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="30">
@@ -726,7 +726,7 @@
         <v>[R_02_闪光背景]</v>
       </c>
       <c r="C30" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="31">
@@ -737,7 +737,7 @@
         <v>[R_02_采样]</v>
       </c>
       <c r="C31" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="32">
@@ -748,7 +748,7 @@
         <v>[R_02_分析时间]</v>
       </c>
       <c r="C32" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="33">
@@ -770,7 +770,7 @@
         <v>[R_02_详细数据(uv)]</v>
       </c>
       <c r="C34" t="str">
-        <v>1.1,2.05,2.71,2.99,2.85,2.31,1.45,0.38,-0.74,-1.76,-2.53,-2.95,-2.95,-2.54,-1.78,-0.76,0.36,1.42,2.29,2.83,2.96,2.68,2.01,1.05,-0.07,-1.19,-2.17,-2.86,-3.18,-3.09,-2.61,-1.81,-0.82,0.22,1.13,1.78,2.05,1.89,1.28,0.29,-0.99,-2.42,-3.85,-5.13,-6.14,-6.81,-7.13,-7.14,-6.94,-6.67,-6.48,-6.55,-7.01,-7.95,-9.43,-11.43,-13.87,-16.65,-19.6,-22.58,-25.44,-28.07,-30.39,-32.41,-34.16,-35.75,-37.29,-38.94,-40.82,-43.04,-45.64,-48.63,-51.94,-55.45,-58.99,-62.39,-65.44,-67.98,-69.88,-71.06,-71.52,-71.27,-70.42,-69.08,-67.38,-65.43,-63.31,-61.07,-58.69,-56.1,-53.17,-49.76,-45.7,-40.85,-35.08,-28.31,-20.54,-11.82,-2.25,8.02,18.82,29.95,41.27,52.65,64.01,75.35,86.71,98.17,109.86,121.88,134.37,147.39,160.98,175.1,189.67,204.56,219.59,234.57,249.33,263.72,277.64,291.02,303.88,316.28,328.34,340.18,351.93,363.69,375.56,387.53,399.57,411.59,423.44,434.96,445.96,456.27,465.77,474.38,482.06,488.87,494.88,500.22,505.04,509.47,513.62,517.58,521.34,524.88,528.11,530.87,533.04,534.44,534.96,534.5,533.03,530.58,527.23,523.12,518.41,513.28,507.89,502.38,496.84,491.29,485.7,480.01,474.09,467.82,461.07,453.76,445.82,437.27,428.17,418.63,408.82,398.92,389.1,379.53,370.34,361.58,353.27,345.36,337.74,330.29,322.86,315.33,307.6,299.61,291.37,282.95,274.45,266.02,257.81,250,242.69,235.98,229.88,224.35,219.32,214.64,210.16,205.7,201.14,196.37,191.33,186.03,180.54,174.96,169.43,164.11,159.13,154.59,150.55,147.02,143.92,141.16,138.57,136.01,133.31,130.35,127.03,123.34,119.29,114.97,110.52,106.07,101.8,97.82,94.25,91.12,88.42,86.09,84,82.01,79.96,77.71,75.15,72.22,68.9,65.27,61.41,57.48,53.62,50.01,46.75,43.94,41.61,39.72,38.19,36.88,35.66,34.36,32.85,31.02,28.84,26.31,23.52,20.56,17.59,14.77,12.25,10.12,8.47,7.29,6.53,6.09,5.82,5.58,5.2,4.55,3.56,2.19,0.48,-1.5,-3.61,-5.7,-7.63,-9.25,-10.46,-11.23,-11.56,-11.54,-11.26,-10.9,-10.59,-10.5,-10.73,-11.36,-12.39,-13.77,-15.41,-17.16,-18.87,-20.38,-21.59,-22.39,-22.76,-22.74,-22.42,-21.91,-21.38,-20.98,-20.85,-21.09,-21.75,-22.82,-24.22,-25.85,-27.55,-29.17,-30.57,-31.62,-32.26,-32.49,-32.35,-31.95,-31.42,-30.92,-30.61,-30.6,-30.99,-31.8,-33,-34.5,-36.19,-37.89,-39.47,-40.77,-41.7,-42.22,-42.32,-42.09,-41.63,-41.09,-40.62,-40.38,-40.48,-40.99,-41.91,-43.19,-44.74,-46.41,-48.04,-49.5,-50.64,-51.38,-51.69,-51.61,-51.22,-50.63,-50.02,-49.53,-49.29,-49.42,-49.96,-50.89,-52.16,-53.64,-55.19,-56.66,-57.88,-58.76,-59.22,-59.24,-58.89,-58.26,-57.48,-56.72,-56.12,-55.82,-55.89,-56.37,-57.23,-58.39,-59.71,-61.04,-62.23,-63.14,-63.67,-63.77,-63.44,-62.75,-61.83,-60.81,-59.85,-59.1,-58.67,-58.63,-59,-59.72,-60.7,-61.8,-62.85,-63.71,-64.26,-64.4,-64.1,-63.39,-62.36,-61.13,-59.86,-58.71,-57.8,-57.24,-57.09,-57.33,-57.91,-58.69,-59.55,-60.31,-60.85,-61.03,-60.79,-60.12,-59.07,-57.73,-56.25,-54.78,-53.47,-52.46,-51.82,-51.59,-51.75,-52.21,-52.84,-53.5,-54.02,-54.26,-54.14,-53.58,-52.62,-51.3,-49.74,-48.09,-46.51,-45.14,-44.11,-43.47,-43.25,-43.4,-43.81,-44.36,-44.88,-45.23,-45.27,-44.92,-44.15,-42.98,-41.5,-39.83,-38.12,-36.54,-35.22,-34.27,-33.73,-33.6,-33.82,-34.27,-34.81,-35.28,-35.53,-35.44,-34.96,-34.05,-32.78,-31.24,-29.56,-27.9,-26.42,-25.24,-24.46,-24.1,-24.14,-24.49,-25.04,-25.63,-26.1,-26.32,-26.18,-25.62,-24.66,-23.36,-21.84,-20.23,-18.7,-17.39,-16.42,-15.86,-15.73,-15.98,-16.51,-17.19,-17.86,-18.36,-18.57,-18.4,-17.82,-16.85,-15.57,-14.11</v>
+        <v>13.02,14.93,14.83,12.66,8.8,3.92,-1.08,-5.3,-7.96,-8.63,-7.25,-4.14,-0.01,4.28,7.81,9.82,9.85,7.84,4.12,-0.63,-5.54,-9.68,-12.29,-12.89,-11.41,-8.18,-3.86,0.69,4.53,6.9,7.33,5.7,2.33,-2.08,-6.7,-10.61,-12.99,-13.41,-11.8,-8.33,-3.74,0.98,5.16,7.91,8.67,7.22,4.17,-0.31,-4.55,-8.58,-10.79,-11.79,-10.16,-6.94,-2.19,2.38,6.77,8.42,9.11,7.38,4.71,-1.07,-4.58,-10.57,-11.77,-15.35,-13.97,-12.09,-6.74,-1.5,0.64,3.58,3.79,2,-6.23,-10.96,-12.66,-17.89,-27.69,-22.4,-27.75,-24.55,-20.5,-20.02,-10.11,-9.21,-6.91,-11.87,-18.73,-19.91,-28.09,-27.64,-32.49,-42.7,-35.3,-27.3,-25.97,-19.32,-14.14,-13,-7.75,-10.36,-14.93,-12.33,-21.06,-12.93,-23.19,-20.28,-17.63,-9,1.44,5.52,5.68,13.58,19.5,23.57,25.97,20.28,32.18,21.79,33.2,32.06,28.68,35.26,46.56,61.58,61.26,72.47,70.43,89,82.64,91.29,87.17,75.25,99.92,90.06,102.76,92.59,117.17,117.93,126.7,145.27,132.78,139.43,136.98,165.95,139.16,132.58,151.28,151.64,138.65,165.17,160.73,160.36,178.77,181.73,208.27,209.77,189.57,203.77,184.45,201.83,194.26,184.34,166.69,197.29,203.4,195.63,195.15,225.9,228.54,188.96,191,204.21,175.91,165.01,173.41,163.49,167.1,188.42,190.77,175.48,177.7,180.22,194.37,176.52,161.08,173.39,151.38,139.98,153.13,142.76,144.26,122.79,114.32,135.34,123.57,130.97,123.64,136.79,114.75,119.52,97.66,93.56,94.33,88.45,78.69,65.02,84.66,79.66,72.71,84.72,82.39,78.19,69.58,59.8,46.03,48.23,39.16,36.56,31.01,34.9,29.46,32.4,35.55,37.87,41.04,40.6,38.21,30.01,26.11,16.42,10.01,8.67,5.33,6.1,11.77,12.4,19.99,21.88,21.07,19.83,17.24,14.02,9.3,4.3,-2.13,-5.12,-5.24,-3.18,-1.01,3.35,6.97,10.89,12.52,11.65,9.23,5.02,-0.2,-5.29,-10.41,-12.62,-13.04,-12.42,-9.02,-5.19,-0.45,2.04,3.35,3.72,0.62,-3.41,-8.58,-13.1,-18.44,-21.2,-20.57,-20.75,-17.43,-13.34,-10.12,-4.77,-3.92,-3.87,-5.46,-9.21,-15.32,-18.91,-24.2,-25.87,-28.64,-26.64,-24.58,-18.13,-13.7,-10.97,-10.64,-9.77,-11.29,-12.27,-17.62,-22.78,-27.72,-30.88,-28.25,-30.13,-23.77,-21.69,-15.28,-10.71,-9.77,-8.45,-10.81,-16.33,-21.11,-26.08,-30.05,-32.14,-30.91,-31.95,-22.92,-20.89,-19.94,-10.73,-12.09,-6.86,-8.27,-11.81,-20.15,-25.55,-31.01,-32.45,-34.82,-31.99,-23.52,-22.7,-19.12,-18.83,-11.97,-16.89,-13.3,-20.48,-22.43,-32.35,-34.08,-30.25,-36.93,-35.32,-32.45,-24.94,-24.46,-25.32,-14.39,-23.42,-18.33,-28.46,-33.36,-38.2,-34.22,-43.48,-49.27,-52.52,-39.21,-43.89,-40.03,-31.58,-37.39,-29.62,-30.06,-33.3,-33.18,-49.38,-46.25,-52.71,-47.87,-50.81,-52.67,-51.96,-40.63,-35.84,-35.97,-31.18,-39.43,-37.4,-36.03,-48.82,-46.4,-48.97,-65.62,-63.74,-60.71,-51.55,-50.07,-45.99,-39.37,-42.03,-43.21,-39.91,-35.47,-46.42,-51.25,-60.92,-62.04,-57,-48.94,-44.47,-39.33,-41.21,-26.33,-40,-23.33,-38.98,-40.64,-40.66,-41.06,-47.55,-41.15,-52.02,-41.78,-43.27,-43.25,-25.05,-32.37,-24.04,-18.52,-35.28,-32.46,-35.46,-46.21,-39.74,-43.23,-51.64,-40.49,-33.16,-30.95,-25.76,-22.47,-24.85,-24.32,-23.95,-26.79,-39.18,-35.98,-47.02,-47.23,-50.7,-46.92,-32.48,-36.71,-33.71,-26.89,-20.98,-22.02,-28.19,-31.46,-35.28,-41.22,-39.97,-42.39,-48.69,-46.36,-41.56,-33.11,-27.94,-20.69,-26.33,-23.98,-23.32,-32.73,-35.16,-40.49,-40.35,-40.91,-44.1,-41.36,-34.33,-27.59,-22.44,-21.78,-18.17,-21.23,-20.92,-24.76,-30.13,-34.56,-34.23,-35.52,-38.38,-32.78,-31.7,-23.82,-22.59,-16.17,-12.4,-15.76,-14.76,-17.27,-20.81,-29.73,-29.15</v>
       </c>
     </row>
     <row r="35">
@@ -781,7 +781,7 @@
         <v>[R_02_标记]</v>
       </c>
       <c r="C35" t="str">
-        <v>a: 19.6ms -116.4uv b: 40.6ms 520.6uv</v>
+        <v>a: 17.2ms -36.3uv b: 37.9ms 127.8uv</v>
       </c>
     </row>
     <row r="36">
@@ -792,7 +792,7 @@
         <v>[L_02_名字]</v>
       </c>
       <c r="C36" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="37">
@@ -814,7 +814,7 @@
         <v>[L_02_闪光]</v>
       </c>
       <c r="C38" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="39">
@@ -825,7 +825,7 @@
         <v>[L_02_闪光背景]</v>
       </c>
       <c r="C39" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="40">
@@ -836,7 +836,7 @@
         <v>[L_02_采样]</v>
       </c>
       <c r="C40" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="41">
@@ -847,7 +847,7 @@
         <v>[L_02_分析时间]</v>
       </c>
       <c r="C41" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="42">
@@ -869,7 +869,7 @@
         <v>[L_02_详细数据(uv)]</v>
       </c>
       <c r="C43" t="str">
-        <v>2.04,2.99,2.35,0.46,-1.68,-2.92,-2.61,-0.91,1.27,2.78,2.81,1.34,-0.84,-2.58,-2.94,-1.74,0.38,2.29,2.98,2.07,0.05,-2.02,-3.03,-2.46,-0.61,1.52,2.79,2.5,0.8,-1.42,-3.02,-3.16,-1.8,0.29,1.95,2.25,0.96,-1.31,-3.44,-4.4,-3.8,-2.09,-0.35,0.32,-0.65,-2.98,-5.69,-7.65,-8.14,-7.3,-5.97,-5.35,-6.27,-8.82,-12.25,-15.42,-17.39,-17.89,-17.52,-17.39,-18.55,-21.42,-25.57,-29.93,-33.39,-35.35,-36.06,-36.45,-37.66,-40.42,-44.6,-49.35,-53.47,-56.07,-57.03,-57.02,-57.16,-58.39,-60.96,-64.27,-67.18,-68.6,-68.05,-65.89,-63.15,-60.91,-59.75,-59.43,-59,-57.26,-53.47,-47.66,-40.65,-33.6,-27.41,-22.2,-17.29,-11.55,-4.01,5.62,16.79,28.36,39.26,48.97,57.85,66.88,77.16,89.31,103.09,117.54,131.47,144.08,155.36,166.08,177.38,190.12,204.45,219.67,234.6,248.23,260.19,270.96,281.62,293.22,306.24,320.3,334.38,347.32,358.43,367.87,376.52,385.53,395.66,406.9,418.45,429.13,438,444.86,450.32,455.51,461.42,468.41,475.97,483.02,488.45,491.73,493.16,493.75,494.62,496.46,499.12,501.72,503.1,502.45,499.74,495.74,491.63,488.35,486.14,484.4,482.02,477.99,471.94,464.37,456.35,449.01,442.94,437.87,432.85,426.76,418.93,409.48,399.33,389.67,381.35,374.48,368.33,361.77,353.88,344.44,334.05,323.85,314.92,307.67,301.7,295.96,289.36,281.32,272.13,262.74,254.32,247.61,242.51,238.19,233.47,227.51,220.2,212.26,204.83,198.89,194.7,191.69,188.73,184.78,179.37,172.91,166.43,161.05,157.35,155.1,153.34,150.9,147.05,141.81,136.02,130.83,127.12,125,123.78,122.3,119.57,115.3,110.01,104.82,100.77,98.36,97.18,96.22,94.34,90.92,86.17,81.01,76.61,73.73,72.36,71.67,70.52,68.01,63.98,59.11,54.54,51.27,49.64,49.13,48.65,47.12,44.05,39.78,35.35,31.87,30.01,29.58,29.68,29.15,27.19,23.8,19.77,16.26,14.18,13.73,14.24,14.58,13.75,11.37,7.94,4.55,2.27,1.62,2.3,3.28,3.44,2.09,-0.62,-3.8,-6.29,-7.27,-6.72,-5.4,-4.48,-4.89,-6.84,-9.71,-12.37,-13.8,-13.62,-12.29,-10.88,-10.49,-11.68,-14.14,-16.9,-18.81,-19.17,-18.11,-16.49,-15.49,-15.94,-17.9,-20.62,-22.96,-23.95,-23.37,-21.82,-20.4,-20.17,-21.54,-24.07,-26.7,-28.32,-28.36,-27.09,-25.47,-24.66,-25.38,-27.54,-30.28,-32.43,-33.15,-32.35,-30.74,-29.48,-29.54,-31.17,-33.82,-36.35,-37.73,-37.52,-36.11,-34.57,-34,-35,-37.34,-40.06,-42.01,-42.44,-41.41,-39.76,-38.66,-38.97,-40.82,-43.5,-45.86,-46.93,-46.42,-44.85,-43.35,-42.97,-44.19,-46.6,-49.2,-50.84,-50.9,-49.6,-47.87,-46.87,-47.36,-49.31,-51.91,-53.99,-54.66,-53.77,-52,-50.48,-50.23,-51.55,-53.93,-56.28,-57.51,-57.13,-55.5,-53.64,-52.68,-53.27,-55.23,-57.63,-59.31,-59.5,-58.19,-56.17,-54.61,-54.42,-55.77,-58.01,-60.01,-60.75,-59.88,-57.9,-55.9,-54.95,-55.58,-57.46,-59.58,-60.81,-60.47,-58.72,-56.46,-54.85,-54.7,-56.04,-58.08,-59.68,-59.9,-58.55,-56.24,-54.12,-53.19,-53.85,-55.62,-57.43,-58.19,-57.35,-55.2,-52.75,-51.13,-51.04,-52.36,-54.2,-55.4,-55.14,-53.35,-50.79,-48.61,-47.77,-48.49,-50.17,-51.69,-52,-50.72,-48.27,-45.72,-44.18,-44.22,-45.55,-47.22,-48.07,-47.39,-45.26,-42.56,-40.44,-39.76,-40.6,-42.23,-43.51,-43.46,-41.83,-39.2,-36.67,-35.31,-35.55,-36.96,-38.51,-39.07,-38.05,-35.71,-32.99,-31.04,-30.62,-31.64,-33.28,-34.37,-34.03,-32.16,-29.46,-27.08,-26,-26.5,-28.04,-29.51,-29.85,-28.59,-26.14,-23.51,-21.84,-21.74,-23,-24.67,-25.61,-25.05,-23.03,-20.37,-18.23,-17.49,-18.31,-20,-21.42,-21.57,-20.14,-17.65,-15.21,-13.87,-14.14,-15.65,-17.37,-18.18,-17.44,-15.33,-12.77,-10.93,-10.58,-11.73</v>
+        <v>7.76,11.4,14.19,15.82,16.1,14.97,12.49,8.87,4.43,-0.45,-5.33,-9.79,-13.41,-15.91,-17.07,-16.84,-15.27,-12.56,-9.03,-5.05,-1.06,2.51,5.28,6.93,7.28,6.26,3.93,0.49,-3.74,-8.37,-12.97,-17.12,-20.4,-22.54,-23.33,-22.66,-20.67,-17.47,-13.44,-8.95,-4.49,-0.35,2.99,5.21,6.08,5.73,3.77,0.92,-2.89,-7.03,-11.02,-14.98,-17.55,-19.57,-20.31,-18.97,-16.63,-13.07,-9.18,-4.72,0.33,4.59,7.24,9.76,10.12,10.09,8.32,5.19,0.78,-3.67,-8.65,-14.69,-15.19,-19.48,-21.4,-21.31,-17.83,-15.67,-11.38,-7.62,-5.7,-2.81,-1.98,-0.8,4.74,1.99,-0.58,-7.02,-6.81,-15.03,-21.38,-21.68,-26.12,-36.55,-34.05,-30.58,-28.54,-35.8,-29.71,-17.81,-20.6,-18.28,-5.25,-4.22,0.05,-10.85,-10.59,-6.86,-12.81,-6.93,-21.81,-17.11,-16.41,-24.51,-15.78,-19.73,-14.49,-10.09,-1.85,11.91,10.75,24.54,20.95,38.2,37.76,36.99,47.68,45.49,41.68,38.08,37.81,35.48,50.42,39.52,38.7,58.18,74.22,56.93,74.73,88.72,93.79,115.08,101.78,122.35,112.04,125.82,140.32,121.04,128.28,140.83,142.25,141.58,126.06,141.72,140.95,136.74,141.55,165.66,143.49,160.14,179.4,189.39,168.56,196.67,184.16,204.01,179.83,198.38,184.22,168.56,170.96,164.03,175.95,155.85,175.52,155.46,197.07,196.33,202.55,192.55,173.37,174.05,196.27,193.26,197.94,185.33,181.77,173.07,201.51,177.77,179.63,175.57,148.71,131.77,142.38,126.06,144.08,137.07,133.31,133.39,140.13,163,149.67,132.32,146.69,138.83,151.05,129.31,117.39,108.84,116.12,88.93,101.67,101.83,72.71,79.53,70.96,83.22,88.45,77.11,95.87,81.09,91.14,92.33,83.03,86.9,76.66,65.3,59.05,64.55,54.02,48.35,41.03,37.68,34.59,29.73,36.22,33.3,37.33,36.73,35.81,42.51,42.6,48.34,40.76,41.01,38.28,31.62,28.63,21.72,19.81,12.26,7.35,3.26,1.32,1.76,1.35,5.61,6.65,11.74,15.6,15.27,19.41,21.7,19.84,20.03,17.4,12.86,6.88,2.15,-2.71,-7.45,-12.72,-16.36,-18.69,-18.23,-16.7,-15.06,-11.91,-8.88,-5.08,-1.51,1.09,2.15,2.87,1.06,-0.61,-4.92,-9.4,-14.47,-19.83,-24.88,-28.83,-31.78,-32.73,-32.97,-29.93,-29.23,-24.38,-21.54,-18.04,-13.98,-8.07,-8.65,-7.3,-8.3,-9.7,-13.02,-17.63,-21.57,-26.57,-29.51,-31.42,-33.72,-35.72,-36.1,-33.01,-28.16,-24.95,-19.89,-16.74,-12.96,-9.19,-8.35,-2.31,-8.19,-8.78,-6.73,-11.75,-15.2,-24.71,-29.75,-31.05,-33.15,-35.33,-30.09,-30.52,-30.33,-21.95,-18.87,-11.7,-13.17,-7.66,-5.48,-5.06,-8.33,-10.86,-14.97,-12.92,-17.39,-30.43,-35.66,-35.4,-38.62,-35.21,-43.4,-34.44,-33.88,-35.25,-32.94,-28.72,-26.02,-25.15,-17.74,-23.04,-13.19,-19.16,-25.86,-28.67,-38.53,-35.63,-40.57,-51.68,-54.64,-56.7,-60.44,-55.13,-50.68,-56.01,-50.63,-38.71,-37.92,-30.16,-34.85,-33.25,-27.03,-40.56,-29.99,-43.09,-39.2,-47.96,-59.01,-64.59,-53.98,-61.62,-68.14,-54.65,-54.83,-49.29,-41.06,-42.74,-41.87,-28.51,-30.77,-39.66,-27.22,-31.06,-34.58,-29.55,-43.82,-52.28,-56.79,-52.76,-46.58,-50.38,-46.25,-50.18,-53.32,-48.56,-44.2,-37.35,-24.69,-31.06,-15.75,-19.11,-27.26,-19.7,-32.97,-25.26,-38.02,-41.12,-47.06,-43.9,-44.22,-40.7,-47.89,-51.99,-49.82,-36.4,-39.89,-30.62,-23.47,-17.83,-26.06,-23.41,-12.37,-24.69,-17.36,-25.95,-31.32,-34.59,-42.42,-39.73,-47.48,-44.51,-45.63,-46.02,-39.61,-46.62,-34.54,-28.43,-31.12,-20.9,-16.89,-15.87,-23.24,-21.42,-27.45,-25.64,-29.61,-39.42,-46.76,-43.99,-46.76,-52.54,-51.31,-46.48,-43.44,-36.84,-34.48,-29.3,-27.86,-18.35,-16.59,-13.86,-18.3,-14.76,-19.76,-24.07,-26.58,-28.46,-35.63,-40.02,-39.71,-39.76,-37.08,-35.96,-31.43,-29.58,-22.82</v>
       </c>
     </row>
     <row r="44">
@@ -880,7 +880,7 @@
         <v>[L_02_标记]</v>
       </c>
       <c r="C44" t="str">
-        <v>a: 19.6ms -109.5uv b: 40.6ms 489.4uv</v>
+        <v>a: 17.3ms -29.6uv b: 37.8ms 48.6uv</v>
       </c>
     </row>
     <row r="45">
@@ -891,7 +891,7 @@
         <v>[R_03_名字]</v>
       </c>
       <c r="C45" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="46">
@@ -913,7 +913,7 @@
         <v>[R_03_闪光]</v>
       </c>
       <c r="C47" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="48">
@@ -924,7 +924,7 @@
         <v>[R_03_闪光背景]</v>
       </c>
       <c r="C48" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="49">
@@ -935,7 +935,7 @@
         <v>[R_03_采样]</v>
       </c>
       <c r="C49" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="50">
@@ -946,7 +946,7 @@
         <v>[R_03_分析时间]</v>
       </c>
       <c r="C50" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="51">
@@ -968,7 +968,7 @@
         <v>[R_03_详细数据(uv)]</v>
       </c>
       <c r="C52" t="str">
-        <v>-4.81,-3.75,-4.26,-6.03,-8.05,-9.19,-8.8,-7.05,-4.85,-3.38,-3.44,-5.05,-7.42,-9.39,-10.02,-9.11,-7.29,-5.65,-5.21,-6.3,-8.44,-10.52,-11.44,-10.65,-8.48,-5.91,-4.1,-3.76,-4.79,-6.33,-7.27,-6.82,-4.98,-2.56,-0.74,-0.49,-2.05,-4.8,-7.6,-9.39,-9.73,-9,-8.19,-8.34,-9.91,-12.54,-15.18,-16.62,-16.1,-13.72,-10.34,-7.17,-5.11,-4.33,-4.2,-3.71,-2.04,0.91,4.42,7.23,8.21,6.87,3.61,-0.5,-4.27,-7,-8.79,-10.41,-12.79,-16.42,-21,-25.46,-28.43,-28.93,-26.75,-22.6,-17.66,-13.04,-9.2,-5.84,-2.14,2.62,8.55,14.89,20.32,23.44,23.46,20.51,15.52,9.73,4.1,-1.14,-6.46,-12.6,-19.97,-28.26,-36.31,-42.59,-45.79,-45.38,-41.8,-36.15,-29.66,-23.08,-16.41,-9.11,-0.58,9.23,19.56,28.96,35.79,38.92,38.15,34.17,28.21,21.38,14.19,6.44,-2.46,-12.86,-24.48,-36.15,-46.21,-53.1,-55.94,-54.86,-50.81,-45.01,-38.39,-31.18,-22.98,-13.25,-1.85,10.57,22.58,32.45,38.79,41.08,39.77,35.99,30.86,25.06,18.5,10.64,0.98,-10.39,-22.5,-33.78,-42.58,-47.81,-49.33,-47.9,-44.7,-40.69,-36.19,-30.85,-23.98,-15.18,-4.78,6.07,15.75,22.81,26.54,27.19,25.76,23.37,20.73,17.81,13.97,8.45,0.99,-7.88,-16.85,-24.39,-29.37,-31.47,-31.32,-30.01,-28.56,-27.33,-25.95,-23.56,-19.4,-13.39,-6.26,0.63,5.91,8.8,9.42,8.65,7.62,7.11,7.14,7.01,5.74,2.67,-2.07,-7.57,-12.49,-15.69,-16.77,-16.22,-15.11,-14.49,-14.85,-15.85,-16.55,-15.94,-13.56,-9.76,-5.62,-2.39,-0.93,-1.24,-2.55,-3.69,-3.8,-2.72,-1.1,-0.02,-0.41,-2.49,-5.65,-8.72,-10.58,-10.7,-9.43,-7.77,-6.86,-7.31,-8.94,-10.85,-11.91,-11.39,-9.34,-6.61,-4.41,-3.65,-4.51,-6.33,-7.99,-8.48,-7.47,-5.48,-3.57,-2.82,-3.7,-5.84,-8.21,-9.67,-9.55,-8.01,-5.97,-4.57,-4.62,-6.12,-8.28,-9.95,-10.22,-8.91,-6.68,-4.67,-3.91,-4.75,-6.71,-8.7,-9.64,-9.01,-7.13,-5,-3.75,-4.05,-5.76,-7.99,-9.55,-9.65,-8.24,-6.08,-4.35,-3.97,-5.15,-7.27,-9.2,-9.92,-9.03,-7.01,-4.93,-3.89,-4.44,-6.27,-8.42,-9.72,-9.5,-7.85,-5.66,-4.09,-3.98,-5.39,-7.56,-9.35,-9.8,-8.68,-6.58,-4.62,-3.85,-4.68,-6.66,-8.75,-9.83,-9.32,-7.51,-5.34,-3.98,-4.15,-5.76,-7.95,-9.55,-9.72,-8.36,-6.19,-4.38,-3.88,-4.96,-7.04,-9.03,-9.85,-9.08,-7.12,-5.02,-3.89,-4.34,-6.13,-8.3,-9.7,-9.58,-8.01,-5.82,-4.18,-3.96,-5.28,-7.43,-9.28,-9.83,-8.8,-6.73,-4.72,-3.85,-4.58,-6.51,-8.62,-9.8,-9.4,-7.64,-5.47,-4.03,-4.09,-5.62,-7.81,-9.48,-9.76,-8.49,-6.34,-4.47,-3.86,-4.85,-6.9,-8.92,-9.84,-9.17,-7.26,-5.14,-3.92,-4.26,-5.98,-8.17,-9.65,-9.64,-8.15,-5.97,-4.25,-3.92,-5.15,-7.28,-9.18,-9.84,-8.91,-6.88,-4.83,-3.86,-4.48,-6.36,-8.5,-9.76,-9.47,-7.79,-5.6,-4.08,-4.03,-5.49,-7.66,-9.41,-9.79,-8.61,-6.49,-4.56,-3.85,-4.74,-6.75,-8.81,-9.83,-9.26,-7.41,-5.26,-3.96,-4.19,-5.84,-8.03,-9.59,-9.69,-8.28,-6.11,-4.33,-3.89,-5.03,-7.14,-9.09,-9.85,-9.01,-7.03,-4.95,-3.88,-4.39,-6.21,-8.38,-9.72,-9.54,-7.93,-5.74,-4.14,-3.99,-5.35,-7.52,-9.33,-9.82,-8.73,-6.64,-4.66,-3.85,-4.63,-6.6,-8.7,-9.81,-9.35,-7.56,-5.39,-4,-4.12,-5.7,-7.89,-9.53,-9.74,-8.41,-6.25,-4.42,-3.87,-4.91,-6.99,-8.99,-9.85,-9.11,-7.18,-5.06,-3.9,-4.31,-6.07,-8.25,-9.68,-9.61,-8.07,-5.88,-4.21,-3.94,-5.23,-7.37,-9.24,-9.84,-8.84,-6.79,-4.77,-3.85,-4.54,-6.45,-8.58,-9.78,-9.43,-7.7,-5.52,-4.05,-4.07,-5.57</v>
+        <v>-4.59,0.82,0.63,-5.22,-13.18,-18.39,-17.69,-11.65,-4.2,-0.16,-2.16,-9.03,-16.5,-19.9,-17.14,-9.98,-2.96,-0.52,-4.17,-11.6,-18.06,-19.44,-14.78,-6.96,-0.81,-0.13,-5.21,-12.74,-17.81,-17.09,-10.88,-2.93,1.9,0.74,-5.5,-12.7,-16.12,-13.42,-6.1,1.4,4.53,1.52,-5.56,-12.05,-13.67,-9.23,-1.37,5.12,6.28,1.53,-6,-11.43,-11.23,-5.42,2.42,7.42,6.47,0.21,-7.34,-11.45,-9.47,-2.73,4.54,7.68,4.62,-2.74,-9.97,-12.42,-8.83,-1.68,4.53,5.41,0.64,-7.43,-13.97,-14.58,-10.23,-2.53,1.94,0.21,-5.68,-14.3,-20.22,-18.43,-12.51,-6.87,-3.39,-8.31,-15.43,-23,-28.65,-23.84,-20.72,-14.16,-12.53,-19.29,-27.73,-33.78,-39.83,-36.3,-29.28,-21.03,-24.84,-31.93,-41.66,-49.83,-41.28,-41.78,-31.35,-35.72,-27.65,-38.04,-45.39,-53.34,-50.24,-43.35,-37.72,-35.57,-34.29,-38.45,-50.09,-51.62,-39.52,-32.76,-19.57,-22.23,-18.56,-23.19,-33.62,-30.63,-14.21,-12.09,7.64,1.35,1.07,1.57,-2.42,3.84,13.03,27.55,31.61,33.62,25.87,31.48,31.23,38.72,45.6,58.43,73.63,72.92,62.03,57.76,69.23,83.39,93.76,90.13,106.33,94.33,96.31,108.86,98.47,107.41,120.65,148.78,149.01,140.19,140.75,125.53,144.51,160.94,162.62,167.67,180.06,157.66,173.63,170.51,181.91,155.6,202.68,191.25,190.27,151.61,176.83,190.53,170.93,168.92,195.34,203.26,182.62,184.85,188.64,158.89,190.52,197.5,195.89,189.24,174.73,175.57,168.54,169.98,165.61,171.5,165.29,161.88,162.94,135.21,132.68,136.83,140.03,135.03,143.39,141.03,115.87,102.88,122.88,125.5,112.24,123.99,116.5,95.96,82.09,75.77,91.92,85.61,94.18,82.29,86.68,74.18,55.42,59.58,57.4,65.67,69.44,60.65,50.65,39.73,32.33,34.81,35.47,43.62,46.02,34.79,28.52,16.56,18.32,19.77,24.13,29.82,26.42,19.68,11.48,4.21,2.18,7.35,13.15,14.47,11.87,4.68,-4.79,-8.03,-8.04,-0.85,5.02,6.3,2.84,-5.96,-13.55,-15.75,-12.64,-5.45,-0.01,0.78,-5.2,-13.45,-19.07,-19.49,-14.49,-6.86,-2.48,-3.2,-10.13,-17.83,-22.34,-20.48,-13.51,-5.77,-2.95,-6.18,-13.61,-20.3,-22.85,-18.99,-11.29,-5.35,-2.8,-7.69,-15.04,-21.62,-21.59,-15.1,-8.65,-2.01,-2.85,-8.58,-17.35,-21.74,-19.17,-11.75,-5.72,0.61,-3.86,-8.81,-17.36,-19.49,-16.76,-10.79,-3.44,0.81,-6.73,-12.34,-19.3,-19.28,-13.2,-6.19,-1.87,-2.51,-6.44,-16.15,-22.69,-19.75,-13.44,-8.73,-4.15,-4.6,-13.54,-22.05,-26.69,-25.54,-17.49,-7.98,-11.37,-12.65,-17.02,-23.98,-33.23,-21.65,-16.01,-11.79,-9.56,-22.6,-31.98,-34.04,-33.86,-30.46,-18.38,-14.87,-21.63,-29.14,-37.82,-39.57,-36.87,-28.31,-19.03,-22.83,-21.74,-31.35,-42.89,-42.76,-39.09,-32.13,-24.83,-25.11,-31.66,-41.25,-38.67,-41.66,-41.12,-35.6,-19.68,-21.05,-40.17,-39.1,-39.59,-41.83,-34.84,-27.67,-19.07,-29.31,-38.58,-42.82,-40.09,-44.73,-29.69,-27.47,-18.71,-26.34,-34.9,-44.82,-46.76,-38.11,-34.18,-29.83,-34.88,-24.96,-32.87,-50.66,-50.32,-33.03,-28.97,-33.94,-33.47,-32.51,-34.19,-40.29,-42.35,-40.32,-25.2,-18.61,-27.76,-31.39,-39.97,-40.25,-35.11,-36.56,-33.65,-30.65,-42.88,-44.8,-54.21,-53.59,-42.13,-37.23,-25.76,-32.06,-46.38,-39.92,-45.91,-52.86,-40.47,-38.59,-29.37,-40.01,-48.24,-42.39,-41.22,-40.58,-40.39,-30.18,-25.01,-31.02,-36.08,-50.29,-42.96,-45.96,-32.04,-35.52,-34.3,-37.14,-45.26,-43.98,-48.2,-36.63,-35.44,-21.73,-25.75,-33.6,-46.49,-45.62,-37.73,-28.33,-20.77,-23.47,-30.3,-30.81,-38.44,-34.2,-27.94,-27.07,-12.64,-16.47,-28.01,-35.2,-30.24,-34.02,-20.89,-15.11,-10.22,-14.13,-22.37,-26.31,-26.97,-23.19,-19.08,-13.4,-8.28,-15.28,-19.5,-24.12,-24.62,-17.05</v>
       </c>
     </row>
     <row r="53">
@@ -979,7 +979,7 @@
         <v>[R_03_标记]</v>
       </c>
       <c r="C53" t="str">
-        <v>91.1uv</v>
+        <v>a: 19.5ms -30.1uv b: 41.6ms 123.4uv</v>
       </c>
     </row>
     <row r="54">
@@ -990,7 +990,7 @@
         <v>[L_03_名字]</v>
       </c>
       <c r="C54" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="55">
@@ -1012,7 +1012,7 @@
         <v>[L_03_闪光]</v>
       </c>
       <c r="C56" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="57">
@@ -1023,7 +1023,7 @@
         <v>[L_03_闪光背景]</v>
       </c>
       <c r="C57" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="58">
@@ -1034,7 +1034,7 @@
         <v>[L_03_采样]</v>
       </c>
       <c r="C58" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="59">
@@ -1045,7 +1045,7 @@
         <v>[L_03_分析时间]</v>
       </c>
       <c r="C59" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="60">
@@ -1067,7 +1067,7 @@
         <v>[L_03_详细数据(uv)]</v>
       </c>
       <c r="C61" t="str">
-        <v>-3.74,-3.97,-6.84,-9.01,-7.92,-4.67,-2.82,-4.36,-7.52,-8.75,-6.71,-3.78,-3.4,-6.19,-9.25,-9.43,-6.81,-4.63,-5.62,-8.91,-10.98,-9.63,-6.37,-4.78,-6.43,-9.14,-9.44,-6.46,-2.95,-2.21,-4.44,-6.52,-5.6,-2.32,-0.13,-1.46,-5.01,-7.22,-6.27,-4.1,-4.21,-7.67,-11.86,-13.35,-11.64,-9.68,-10.43,-13.51,-15.52,-13.86,-9.59,-6.3,-6.05,-7.19,-6.26,-2,3.07,5.4,4.17,2.14,2.39,4.77,6.02,3.4,-2.21,-7.22,-9.25,-9.63,-11.73,-16.93,-22.85,-25.79,-24.66,-22.02,-21.08,-21.99,-21.67,-17.31,-9.67,-2.39,1.82,3.92,7.15,13.02,19.29,22.18,20.36,16.24,13.2,11.76,9.1,2.44,-7.58,-17.23,-23.47,-26.9,-30.62,-36.31,-41.96,-43.77,-40.26,-33.77,-27.9,-23.58,-18.34,-9.44,2.57,13.92,21.3,24.98,28.02,32.34,36.21,35.98,30.07,20.81,12.03,5.12,-2.08,-12.27,-25.05,-36.72,-43.79,-46.34,-47.44,-49.33,-50.69,-48.06,-39.82,-28.28,-17.47,-9.14,-1.42,8.45,20.34,30.73,36.12,36.45,34.88,34.01,32.97,28.51,18.93,6.43,-4.86,-12.92,-19.47,-27.41,-37,-45.01,-48,-45.84,-41.78,-38.75,-36.27,-31.24,-21.82,-9.99,0.18,6.51,10.66,15.74,22.42,27.87,28.68,24.65,19.03,15,12.39,8.16,0.26,-9.7,-17.76,-21.68,-23.08,-25.28,-29.38,-32.86,-32.37,-27.53,-21.51,-17.63,-15.93,-13.41,-7.7,-0.06,5.76,7.45,6.56,6.56,8.92,11.38,10.58,5.9,0.33,-2.74,-3.08,-3.7,-7.26,-12.87,-16.94,-17.11,-14.75,-13.45,-14.92,-17.16,-16.73,-12.75,-7.96,-5.82,-6.71,-7.65,-5.76,-1.57,1.49,0.89,-2.15,-4.06,-2.9,-0.47,-0.25,-3.44,-7.5,-8.96,-7.26,-5.27,-6.08,-9.46,-12.09,-11.3,-8.07,-5.93,-7.02,-9.75,-10.58,-8.06,-4.48,-3.33,-5.44,-8.01,-7.84,-4.89,-2.33,-2.99,-6.18,-8.43,-7.38,-4.43,-3.12,-5.17,-8.51,-9.6,-7.4,-4.52,-4.3,-7.05,-9.69,-9.25,-6.17,-3.84,-4.79,-7.85,-9.49,-7.77,-4.54,-3.35,-5.48,-8.5,-8.99,-6.4,-3.63,-3.82,-6.78,-9.22,-8.43,-5.35,-3.46,-4.92,-8.12,-9.48,-7.49,-4.4,-3.67,-6.13,-9,-9.06,-6.22,-3.66,-4.25,-7.3,-9.39,-8.16,-4.98,-3.42,-5.23,-8.37,-9.32,-7.01,-4.04,-3.75,-6.46,-9.15,-8.78,-5.79,-3.53,-4.54,-7.69,-9.44,-7.83,-4.66,-3.49,-5.64,-8.69,-9.21,-6.63,-3.83,-3.96,-6.88,-9.3,-8.51,-5.39,-3.45,-4.86,-8.04,-9.42,-7.45,-4.34,-3.59,-6.04,-8.93,-9.03,-6.22,-3.65,-4.22,-7.28,-9.4,-8.19,-5.02,-3.44,-5.23,-8.37,-9.35,-7.06,-4.07,-3.75,-6.44,-9.14,-8.8,-5.81,-3.53,-4.51,-7.66,-9.44,-7.85,-4.68,-3.48,-5.61,-8.67,-9.22,-6.65,-3.84,-3.95,-6.85,-9.29,-8.53,-5.42,-3.46,-4.84,-8.02,-9.42,-7.47,-4.36,-3.58,-6.01,-8.92,-9.04,-6.24,-3.66,-4.2,-7.25,-9.39,-8.21,-5.04,-3.44,-5.2,-8.35,-9.35,-7.08,-4.09,-3.73,-6.42,-9.13,-8.82,-5.84,-3.53,-4.49,-7.64,-9.44,-7.87,-4.7,-3.48,-5.59,-8.65,-9.23,-6.68,-3.86,-3.94,-6.83,-9.28,-8.55,-5.44,-3.46,-4.82,-8,-9.43,-7.5,-4.38,-3.57,-5.98,-8.9,-9.06,-6.27,-3.67,-4.18,-7.23,-9.39,-8.24,-5.07,-3.44,-5.18,-8.33,-9.36,-7.11,-4.1,-3.72,-6.39,-9.11,-8.83,-5.86,-3.54,-4.47,-7.61,-9.43,-7.89,-4.72,-3.48,-5.56,-8.63,-9.24,-6.7,-3.87,-3.92,-6.8,-9.27,-8.56,-5.47,-3.46,-4.8,-7.98,-9.43,-7.52,-4.4,-3.57,-5.96,-8.89,-9.07,-6.29,-3.68,-4.17,-7.2,-9.38,-8.26,-5.09,-3.44,-5.16,-8.31,-9.37,-7.13,-4.12,-3.71,-6.37,-9.1,-8.85,-5.89,-3.55,-4.45,-7.59,-9.43,-7.92,-4.74,-3.47,-5.54,-8.61,-9.25,-6.73,-3.88,-3.91,-6.77,-9.27,-8.58</v>
+        <v>-35.24,-32.97,-27.18,-20.61,-16.33,-16.39,-20.88,-27.89,-34.37,-37.51,-35.98,-30.57,-23.77,-18.73,-17.76,-21.36,-27.95,-34.59,-38.33,-37.49,-32.46,-25.48,-19.69,-17.65,-20.24,-26.25,-32.92,-37.17,-37.02,-32.44,-25.39,-18.95,-15.89,-17.46,-22.84,-29.46,-34.21,-34.8,-30.82,-23.9,-16.99,-13.05,-13.67,-18.43,-25,-30.28,-31.72,-28.52,-21.95,-14.82,-10.18,-9.98,-14.15,-20.71,-26.55,-28.94,-26.7,-20.73,-13.61,-8.47,-7.54,-11.19,-17.74,-24.18,-27.59,-26.43,-21.21,-14.29,-8.91,-7.41,-10.42,-16.92,-23.91,-28.6,-28.43,-24.4,-17.76,-12.08,-10.17,-12.74,-19.13,-26.5,-32.24,-33.51,-30,-25.35,-19.88,-17.09,-19.44,-25.19,-34.63,-39.88,-43,-42.04,-34.22,-28.17,-28.76,-30.12,-35.11,-41.07,-52.74,-53.59,-55.71,-50.89,-38.8,-36.64,-40.06,-42.94,-56.37,-60.06,-66.76,-58.24,-57.15,-46.27,-48.54,-44.78,-51.07,-52.87,-57.11,-67,-60.55,-57.01,-47.98,-34.27,-33.57,-37.55,-44,-47.64,-48.47,-47.66,-41.65,-28.52,-15.98,-10.47,-7.44,-15.75,-13.77,-14.27,-8.62,-8.3,-1.07,14.62,30.26,25.7,24.49,29.38,23.49,29.94,33.14,46.74,61,54.19,67.55,78.99,60.94,66.81,74.5,80.23,85.97,102.84,93.28,96.64,101.17,112.88,101.91,91.57,103.07,129.69,118.52,144.07,131.59,154.11,133.74,124.02,127.88,133.07,153.72,148.34,178.25,172.12,182.38,148.38,146.59,157.02,172.32,161.61,149.49,159.8,165.16,181.9,193.92,182.9,162.22,170.39,151.14,173.07,170.25,165.59,195.55,189.03,173.18,133.37,132.53,165.69,169.56,165.94,155.38,172.33,150.02,146.33,130.84,136.11,125.99,105.14,127.56,116.48,108.93,124.4,95.39,87.42,87.19,80,97.59,95.43,94.32,100.7,95.68,81.07,74.68,53.26,45.7,59.98,64.68,56.91,56.45,61.54,44.55,38.83,34.92,27.5,23.44,29.74,37.56,32.73,33.54,25.22,15.65,11.93,3.23,8.15,8.75,17.19,17.39,14.91,10.67,2.49,-4.6,-7.87,-9.72,-6.01,1.39,5.89,4.41,1.04,-6.39,-15.23,-19.14,-19.54,-15.88,-8.85,-4.58,-2.52,-6.11,-12.65,-19.41,-24.87,-26.11,-22.13,-15.55,-9.62,-7.28,-9.12,-14.74,-22.72,-27.75,-28.61,-25.96,-19.08,-12.84,-9.58,-10.49,-14.76,-21.25,-27.59,-28.79,-25.9,-20.06,-13.08,-8.77,-9.43,-11.84,-18.49,-25.42,-27.82,-25.36,-19.35,-13.38,-6.48,-6.54,-10.22,-15.92,-21.7,-25.25,-26.29,-19.29,-14.21,-6.96,-4.68,-6.35,-13.48,-20.6,-24.04,-23.42,-19.74,-11.38,-6.85,-5.06,-8.28,-11.75,-19.49,-26.21,-27.8,-24.9,-15.96,-10.03,-6.73,-9.88,-11.25,-22.93,-26.83,-30.62,-30.05,-21.33,-17.94,-13.12,-12.5,-13.29,-25.27,-30.08,-32.57,-31.59,-26.55,-23.11,-19.16,-21.11,-22.93,-25.73,-34.13,-35.04,-40.26,-32.23,-25.94,-21.73,-18.2,-28.01,-36.7,-43.1,-47.24,-45.09,-35.96,-34.06,-24.43,-25.51,-29.48,-33.43,-42.63,-42.46,-42.75,-46.8,-36.29,-36.14,-27.16,-25.92,-32.13,-38.33,-53.19,-52.64,-43.44,-45.1,-36.31,-24.56,-36.48,-34.37,-42.96,-53.65,-48.09,-38.82,-36.74,-30.99,-19.99,-22.62,-36.74,-37.67,-46.26,-54.69,-49.52,-34.3,-39.98,-20.57,-19.14,-25.83,-29.37,-35.33,-45,-38.79,-37.33,-39.91,-27.07,-25.63,-35.59,-35.59,-40.44,-45.95,-45.95,-42.83,-42.8,-30.21,-31.69,-30.9,-28.98,-32.95,-40.98,-43.75,-50,-31.32,-22.47,-30.41,-23.13,-34.25,-43.11,-52.13,-50.63,-45.94,-40.37,-35.81,-29.2,-33.48,-30.42,-30.72,-43.85,-52.87,-50.49,-46.2,-40.14,-19.79,-26.84,-36.88,-42.74,-46.79,-38.94,-39.65,-39.11,-30.11,-28.47,-27.17,-29.93,-27.5,-34.44,-38.81,-46.22,-30.68,-33.46,-22.18,-18.71,-18.49,-22.97,-28.8,-32.32,-34.72,-31.82,-21.26,-21.18,-13.42,-13.94,-19.62,-23.96,-33.59,-27.96,-23.61,-23.06,-14.66,-8.34,-10.55,-11.28,-17.31,-26.38,-21.56,-22.33,-18.4,-4.86</v>
       </c>
     </row>
     <row r="62">
@@ -1078,7 +1078,7 @@
         <v>[L_03_标记]</v>
       </c>
       <c r="C62" t="str">
-        <v>87.2uv</v>
+        <v>a: 19.3ms -28.1uv b: 41.6ms 119.5uv</v>
       </c>
     </row>
     <row r="63">
@@ -1089,7 +1089,7 @@
         <v>[R_04_名字]</v>
       </c>
       <c r="C63" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="64">
@@ -1111,7 +1111,7 @@
         <v>[R_04_闪光]</v>
       </c>
       <c r="C65" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="66">
@@ -1122,7 +1122,7 @@
         <v>[R_04_闪光背景]</v>
       </c>
       <c r="C66" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="67">
@@ -1133,7 +1133,7 @@
         <v>[R_04_采样]</v>
       </c>
       <c r="C67" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="68">
@@ -1144,7 +1144,7 @@
         <v>[R_04_分析时间]</v>
       </c>
       <c r="C68" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="69">
@@ -1166,7 +1166,7 @@
         <v>[R_04_详细数据(uv)]</v>
       </c>
       <c r="C70" t="str">
-        <v>2.7,2.36,-0.62,-2.91,-1.93,1.22,3,1.41,-1.76,-2.96,-0.83,2.22,2.78,0.22,-2.59,-2.49,0.41,2.85,2.09,-1.01,-2.98,-1.6,1.58,2.98,1.04,-2.07,-2.86,-0.43,2.48,2.61,-0.19,-2.78,-2.25,0.8,2.94,1.77,-1.4,-3.01,-1.26,1.89,2.89,0.61,-2.4,-2.77,-0.1,2.59,2.26,-0.75,-3.09,-2.18,0.91,2.66,1.02,-2.24,-3.56,-1.58,1.35,1.77,-0.97,-4.01,-4.19,-1.59,0.55,-0.55,-4.06,-6.52,-5.68,-3.07,-2.27,-4.89,-8.77,-10.4,-8.89,-6.92,-7.79,-11.66,-15.4,-16.1,-14.32,-13.46,-15.94,-20.47,-23.49,-23.15,-21.38,-21.71,-25.29,-29.58,-31.19,-29.66,-27.98,-29.18,-32.95,-35.94,-35.51,-32.71,-31.03,-32.52,-35.45,-36.25,-33.5,-29.55,-27.83,-29.05,-30.35,-28.56,-23.72,-19.09,-17.45,-18.02,-17.33,-13.14,-6.95,-2.35,-0.97,-0.71,1.94,7.91,14.51,18.43,19.46,20.7,25.08,32.05,38.21,41.1,41.97,44.37,50.15,57.4,62.57,64.45,65.56,69.28,76.07,82.94,86.83,88,89.78,94.79,102.02,107.94,110.47,111.3,113.99,119.97,126.91,131.35,132.56,133.35,136.92,143.23,149.07,151.62,151.62,152.54,156.66,162.49,166.46,166.9,165.9,166.98,171.1,175.6,177.16,175.54,173.82,174.97,178.48,180.94,179.88,176.53,174.44,175.49,177.8,177.81,174.32,169.81,167.68,168.43,169.11,166.63,161.26,156.3,154.42,154.66,153.5,148.86,142.41,137.73,136.29,135.82,132.87,126.68,120.08,116.29,115.33,114.01,109.52,102.6,96.72,94.19,93.59,91.35,85.79,79,74.51,73.33,72.82,69.67,63.62,57.74,55.02,54.98,54.25,50.31,44.39,40.01,39.09,39.78,38.51,34.04,28.83,26.27,26.9,27.76,25.76,21.11,17.09,16.39,18.05,18.56,15.78,11.37,8.88,9.79,11.85,11.57,8.18,4.44,3.6,5.68,7.5,6.21,2.51,-0.15,0.55,3.21,4.25,1.96,-1.61,-2.94,-0.99,1.61,1.53,-1.53,-4.5,-4.41,-1.69,0.28,-1.03,-4.44,-6.42,-5.03,-2.1,-1.2,-3.6,-6.87,-7.6,-5.22,-2.66,-3.05,-6.2,-8.82,-8.23,-5.33,-3.64,-5.31,-8.72,-10.31,-8.55,-5.69,-5.21,-7.92,-11.05,-11.37,-8.8,-6.51,-7.37,-10.7,-13.06,-12.11,-9.21,-7.93,-10.03,-13.45,-14.69,-12.67,-9.99,-9.99,-13.01,-15.99,-15.93,-13.24,-11.29,-12.62,-16.09,-18.16,-16.87,-14.02,-13.18,-15.65,-19.03,-19.88,-17.63,-15.16,-15.63,-18.87,-21.62,-21.16,-18.38,-16.77,-18.51,-22.02,-23.72,-22.08,-19.3,-18.87,-21.64,-24.85,-25.26,-22.76,-20.51,-21.38,-24.75,-27.16,-26.26,-23.38,-22.08,-24.15,-27.58,-28.83,-26.8,-24.08,-24.01,-26.96,-29.9,-29.8,-27.04,-24.98,-26.18,-29.54,-31.52,-30.12,-27.14,-26.13,-28.43,-31.65,-32.36,-29.93,-27.26,-27.5,-30.52,-33.07,-32.41,-29.39,-27.51,-28.98,-32.22,-33.68,-31.77,-28.7,-27.94,-30.39,-33.31,-33.43,-30.61,-28.01,-28.52,-31.53,-33.62,-32.38,-29.14,-27.46,-29.13,-32.19,-33.08,-30.69,-27.57,-27.09,-29.63,-32.18,-31.72,-28.57,-26.09,-26.87,-29.82,-31.42,-29.65,-26.26,-24.82,-26.7,-29.53,-29.87,-27.07,-23.99,-23.81,-26.44,-28.62,-27.61,-24.23,-21.96,-23.03,-25.92,-27.04,-24.81,-21.39,-20.28,-22.38,-24.98,-24.81,-21.71,-18.79,-18.98,-21.69,-23.53,-22.05,-18.55,-16.59,-18,-20.82,-21.52,-18.94,-15.6,-14.89,-17.23,-19.62,-19.01,-15.72,-13.07,-13.68,-16.5,-18,-16.14,-12.65,-11.09,-12.87,-15.63,-15.93,-13.09,-9.96,-9.72,-12.3,-14.49,-13.49,-10.11,-7.83,-8.89,-11.8,-12.98,-10.81,-7.43,-6.34,-8.48,-11.16,-11.1,-8.09,-5.24,-5.49,-8.3,-10.26,-8.92,-5.54,-3.68,-5.19,-8.14,-9,-6.58,-3.38,-2.78,-5.26,-7.82,-7.4,-4.27,-1.77,-2.51,-5.5,-7.19,-5.53,-2.21,-0.8,-2.73,-5.68,-6.18,-3.54,-0.57,-0.48,-3.23,-5.62,-4.83</v>
+        <v>-2.34,4.63,13.19,12.63,3.65,-2.46,2,11.53,14.32,7,-1.12,0.3,9.66,15.47,10.68,1.53,-0.28,7.79,15.92,14.23,5.13,0.33,6.13,15.61,17.22,9.26,2.02,4.87,14.55,19.26,13.39,4.58,4.13,12.86,20.11,17.02,7.69,3.97,10.69,19.58,19.66,10.88,4.34,8.31,17.77,20.9,13.79,5.19,5.76,14.7,20.57,16.03,6.26,3.38,10.8,18.37,16.8,7.47,1.16,5.74,14.89,16.69,7.68,-0.73,0.86,9.71,13.83,8.45,-1.84,-4.48,4.07,10.48,6.32,-4.86,-7.45,-4.08,4.93,2.89,-6.67,-13.57,-9.28,-2.44,0.92,-8.71,-16.96,-15.21,-10.89,-5.66,-9.06,-18.7,-25.94,-12.27,-11.54,-4.25,-17.31,-22.82,-16.28,-8.2,-4.31,-16.13,-19.58,-15.24,-14,-7.27,-10.94,-16.65,-19.43,-11.92,-2.16,-1.89,-12.16,-11.71,0.01,6.66,9.7,3.48,2.2,7.32,26.82,25.31,18.85,13.16,18.34,28.53,42.07,43.58,40.53,39,55.84,62.42,55.43,52.48,60.67,72.5,84.54,91.02,83,76.8,80.75,96.18,97.05,105.83,98.4,106.38,111.65,125.12,131.49,130.62,114.05,115.67,160.68,163.84,150.94,124.79,160.61,153.65,160.28,155.67,162.61,141.78,156.33,195.14,171.44,180.24,193.29,189.99,199.19,190.55,194.37,165.06,190.08,183.69,222.79,203.47,172.2,186.27,206.61,185.93,185.18,206.55,183.93,175.42,228.79,199.79,206.04,182.65,195.67,218.24,218.93,177.88,201.92,172.01,196.91,184.42,204.54,186.16,182.31,165.01,168.42,161.01,168.92,144.29,165.57,180.76,157.1,143.06,142.39,156.89,161.98,148.94,151.43,125.38,128.39,145.11,135.02,120.28,115.18,99.32,112.38,107.56,118.93,103.25,87.23,103.03,101.13,97.61,96.27,71.64,82.78,78.67,78.01,74.31,70.12,57.46,68.11,66.34,59,50.66,48.86,49.14,50.44,53.49,45.21,33,30.72,42.32,41.38,33.05,22.42,23.38,31.38,34.04,27.58,18.47,14.89,16.88,25.57,23.96,14.16,6.7,9.3,17.84,20.56,11.59,4,3.55,11.35,16.66,12.27,2.49,-0.92,6.4,13.25,12.24,2.17,-3.72,1.45,9.58,12.08,3.94,-3.43,-2.18,7.69,12.16,6.58,-3.32,-4.3,4.27,12.49,9.46,-1.06,-4.82,1.29,9.79,11.16,3.68,-5.12,-0.18,8.43,12.04,5.53,-4.11,-3.43,4.51,10.69,8.07,-2,-5,1.91,8.65,7.42,-0.55,-7.21,-3.88,6.04,10.6,-0.63,-6.24,-3.81,1.68,9.32,3.17,-5.16,-11.93,-2.78,4.22,-0.35,-5.8,-11.73,-8.53,2.02,2.22,-11.21,-15.97,-10.7,-5.69,-3.66,-5.14,-21.01,-17.47,-6.99,-0.95,-5.46,-15.38,-26.37,-13.94,-10.41,-3.99,-17.17,-26.66,-17.76,-17.41,-10.93,-20.82,-27.18,-29.54,-13.13,-12.31,-20.03,-22.41,-27.84,-15.58,-13.98,-14.65,-29.55,-33.17,-20.9,-14.87,-7.1,-17.53,-23.59,-21.99,-14.46,-8.68,-23.13,-28.97,-37.59,-22.5,-16.48,-15.01,-32.52,-38.91,-25.09,-10.98,-7.19,-24.5,-28.42,-29.79,-23.88,-6.83,-18.35,-22.83,-21.31,-17.28,-10.42,-26.33,-19.7,-30.76,-16.85,-19.12,-17.26,-17.44,-27.7,-30,-20.04,-16.33,-21.09,-34.47,-34.55,-21.04,-22.67,-26.09,-23.53,-37.6,-18.86,-9.46,-26.71,-25.93,-28.09,-20.07,-26.82,-26.97,-36.5,-39.72,-25.12,-17.03,-22,-24.39,-35.75,-30.75,-31.18,-17.41,-29.67,-33.07,-32.15,-21.9,-27.47,-25.14,-24.73,-32.82,-27.9,-16.96,-13.8,-26.64,-26.15,-34.34,-20.86,-20.45,-27.28,-36.84,-27.92,-17.52,-10.39,-12.47,-19.81,-25.16,-22.4,-18.8,-13.69,-20.51,-31.56,-20.88,-19.32,-8.61,-16.67,-17.59,-25.59,-9,-6.25,-7.2,-18.42,-22.67,-11.24,-0.53,-4.12,-13.3,-16.17,-15.95,-7.3,3.96,-6.6,-10.99,-13.41,-6.46,-0.66,-1.42,-13.36,-13.52,-3.26,1.54,5.37,-5.59,-9.33,-7.1,1.6,3.89,-1.06,-10.4,-6.31,1.05</v>
       </c>
     </row>
     <row r="71">
@@ -1177,7 +1177,7 @@
         <v>[R_04_标记]</v>
       </c>
       <c r="C71" t="str">
-        <v>a: 23.6ms -41.1uv b: 48.6ms 178.1uv</v>
+        <v>a: 20.8ms -34.3uv b: 45.3ms 214.8uv</v>
       </c>
     </row>
     <row r="72">
@@ -1188,7 +1188,7 @@
         <v>[L_04_名字]</v>
       </c>
       <c r="C72" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="73">
@@ -1210,7 +1210,7 @@
         <v>[L_04_闪光]</v>
       </c>
       <c r="C74" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="75">
@@ -1221,7 +1221,7 @@
         <v>[L_04_闪光背景]</v>
       </c>
       <c r="C75" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="76">
@@ -1232,7 +1232,7 @@
         <v>[L_04_采样]</v>
       </c>
       <c r="C76" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="77">
@@ -1243,7 +1243,7 @@
         <v>[L_04_分析时间]</v>
       </c>
       <c r="C77" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="78">
@@ -1265,7 +1265,7 @@
         <v>[L_04_详细数据(uv)]</v>
       </c>
       <c r="C79" t="str">
-        <v>2.99,0.5,-2.91,-0.99,2.74,1.45,-2.5,-1.87,2.18,2.23,-1.81,-2.54,1.38,2.77,-0.92,-2.92,0.43,2.99,0.07,-2.98,-0.57,2.89,1.06,-2.71,-1.51,2.45,1.92,-2.13,-2.28,1.75,2.57,-1.32,-2.8,0.84,2.93,-0.36,-3.01,-0.16,2.96,0.63,-2.89,-1.16,2.63,1.52,-2.48,-2.07,1.97,2.19,-1.86,-2.83,0.99,2.5,-1.16,-3.42,-0.29,2.32,-0.59,-3.93,-1.86,1.5,-0.38,-4.49,-3.8,-0.14,-0.85,-5.35,-6.19,-2.72,-2.3,-6.78,-9.16,-6.38,-4.96,-9.03,-12.78,-11.1,-8.93,-12.22,-17.01,-16.68,-14.07,-16.26,-21.58,-22.66,-19.9,-20.74,-25.97,-28.3,-25.65,-24.96,-29.44,-32.66,-30.31,-28.06,-31.16,-34.78,-32.85,-29.15,-30.38,-33.86,-32.43,-27.56,-26.65,-29.47,-28.58,-22.97,-19.92,-21.65,-21.3,-15.47,-10.51,-10.86,-10.97,-5.46,0.98,2.18,1.76,6.49,13.87,16.67,16.2,19.85,27.56,31.92,31.72,34.18,41.69,47.44,47.87,49.21,56.04,62.92,64.33,64.79,70.57,78.2,80.82,80.75,85.23,93.14,97.07,96.85,99.9,107.58,112.72,112.72,114.33,121.23,127.32,127.84,128.11,133.74,140.35,141.58,140.71,144.66,151.27,153.26,151.54,153.54,159.58,162.26,160.02,159.97,164.87,168.05,165.64,163.63,166.92,170.3,168.02,164.32,165.65,168.86,166.99,161.99,161.19,163.85,162.54,156.75,153.85,155.58,154.9,148.87,144.09,144.59,144.48,138.75,132.47,131.52,131.83,126.87,119.61,117.12,117.61,113.76,106.11,102.14,102.53,99.97,92.55,87.28,87.26,86.02,79.38,73.14,72.44,72.38,66.99,60.18,58.6,59.44,55.61,48.71,46.13,47.5,45.37,38.88,35.31,36.77,36.32,30.68,26.27,27.39,28.4,24.01,18.99,19.42,21.55,18.66,13.38,12.85,15.66,14.39,9.24,7.63,10.62,10.94,6.33,3.66,6.33,8.07,4.37,0.79,2.73,5.56,3.08,-1.12,-0.23,3.27,2.18,-2.25,-2.61,1.09,1.45,-2.8,-4.43,-1,0.69,-2.95,-5.73,-3.02,-0.23,-2.91,-6.57,-4.92,-1.39,-2.85,-7.02,-6.65,-2.81,-2.92,-7.17,-8.15,-4.46,-3.24,-7.12,-9.38,-6.28,-3.89,-7,-10.31,-8.17,-4.92,-6.94,-10.96,-10.05,-6.31,-7.04,-11.35,-11.8,-8.03,-7.42,-11.56,-13.35,-10,-8.13,-11.67,-14.63,-12.1,-9.23,-11.8,-15.63,-14.23,-10.7,-12.05,-16.34,-16.26,-12.5,-12.5,-16.82,-18.1,-14.56,-13.25,-17.13,-19.66,-16.77,-14.33,-17.38,-20.91,-19.02,-15.74,-17.65,-21.81,-21.17,-17.46,-18.05,-22.41,-23.11,-19.42,-18.65,-22.75,-24.76,-21.52,-19.5,-22.92,-26.03,-23.64,-20.63,-23.02,-26.91,-25.66,-22.03,-23.13,-27.4,-27.45,-23.63,-23.35,-27.54,-28.92,-25.34,-23.74,-27.41,-29.97,-27.08,-24.34,-27.09,-30.58,-28.7,-25.16,-26.7,-30.74,-30.09,-26.16,-26.33,-30.47,-31.15,-27.27,-26.07,-29.86,-31.79,-28.41,-25.96,-28.99,-31.97,-29.45,-26.05,-27.97,-31.66,-30.3,-26.32,-26.92,-30.9,-30.85,-26.72,-25.93,-29.76,-31.01,-27.19,-25.08,-28.32,-30.72,-27.63,-24.44,-26.7,-29.97,-27.94,-24,-25.03,-28.79,-28.02,-23.75,-23.41,-27.22,-27.78,-23.65,-21.95,-25.35,-27.17,-23.6,-20.71,-23.31,-26.15,-23.52,-19.74,-21.22,-24.73,-23.31,-19.04,-19.2,-22.96,-22.88,-18.56,-17.35,-20.92,-22.16,-18.24,-15.78,-18.72,-21.1,-18,-14.52,-16.47,-19.71,-17.73,-13.59,-14.31,-18,-17.34,-12.97,-12.34,-16.05,-16.74,-12.6,-10.67,-13.94,-15.88,-12.41,-9.34,-11.78,-14.73,-12.27,-8.4,-9.71,-13.3,-12.1,-7.82,-7.82,-11.63,-11.8,-7.56,-6.22,-9.79,-11.29,-7.54,-4.99,-7.89,-10.51,-7.65,-4.15,-6.03,-9.47,-7.79,-3.7,-4.34,-8.18,-7.84,-3.6,-2.9,-6.7,-7.72,-3.79,-1.8,-5.11,-7.36,-4.15,-1.09,-3.52,-6.73,-4.59,-0.77,-2.03,-5.83,-4.98,-0.82,-0.76,-4.7,-5.22,-1.17,0.22</v>
+        <v>14.35,11.36,13.73,18.97,21.71,19.11,13.75,11.01,13.64,18.96,21.59,18.87,13.58,11.1,13.98,19.36,21.87,19.03,13.81,11.57,14.69,20.11,22.46,19.49,14.32,12.32,15.63,21.05,23.22,20.09,14.96,13.14,16.63,22.01,23.96,20.63,15.49,13.84,17.46,22.71,24.44,20.87,15.66,14.13,17.74,22.91,24.28,20.59,15.31,13.77,17.59,22.31,23.24,19.19,13.65,12.07,15.82,20.12,21.04,16.01,11.45,9.23,13.58,17.73,18.01,13.03,5.49,5.23,9.08,12.78,12.88,6.68,1.18,-0.95,1.72,6.9,5.78,-3.46,-4.39,-8.81,-8.15,1.99,-1.06,-11.73,-10.22,-14.68,-13.59,-8.35,-11.08,-12.1,-13.03,-18.04,-14.7,-10.93,-15.27,-9.66,-20.3,-18.48,-18.78,-2.37,-1.83,-6.35,-16.04,-14.4,2.24,4.26,8.5,2.79,7.17,1.18,12.14,21.88,22.22,16.31,14.66,23.52,29.49,37.14,44.72,46.37,45.61,53.82,59.45,71.59,75.19,62.52,70.74,77.13,78.45,102.09,104.89,89.89,102.46,111.5,109.35,118.31,134.76,127.68,125.32,120.74,134.99,162.06,157.27,156.66,132.62,161.69,169.6,162.2,160.22,165.87,186.62,185.53,195.01,209.85,192.93,198.27,172.99,192.51,192.72,223.97,220.01,203.13,187.57,179.75,192,199.21,209.32,217.38,191.26,199.5,229.79,200.98,209.47,200.75,195.76,207.69,183.01,207.6,221.32,199,187.56,172.06,178.21,180.51,200.3,186.76,165.81,192.06,163.51,174.25,185.65,142.5,163.65,157,142.36,142.02,154.64,122.65,123.11,119.36,136.71,138.95,118.81,106.12,107.31,102.71,113.54,100.32,95.41,102.53,95.64,97.09,95.14,87.76,77.61,75.27,71.5,66.5,72.39,71.69,62.14,55.04,58,54.06,54.91,54.39,49.5,40.23,37.83,44.59,46.44,44.71,41.01,32.66,31.16,32.63,34.03,33.79,29.03,21.49,20.79,25.66,27.8,28.65,21.19,16.44,14.99,19.98,23.4,22.75,15.92,11.5,10.47,15.52,18.59,18.22,12.1,7.28,7.16,12.26,15.39,14.28,8.45,4.58,4.99,9.64,13.39,12.23,6.34,2.78,3.13,8.49,11.1,9.87,5.66,0.86,2.97,7.2,11.09,8.91,4.07,-0.02,2.07,7.86,10.14,7.91,3.83,-0.64,2.35,5.56,9.44,7.83,4.36,0.49,1.91,6.62,8.48,8.72,2.86,-1.32,0.2,7.2,8.35,5.4,3.69,-0.36,1.74,7.12,9.21,6.92,1.49,-1.34,1.99,4.92,5.72,6.86,-0.85,-6.58,-1.08,5.58,1.81,3.19,-0.42,-3.82,-0.49,-0.41,5.95,1.45,-6.7,-7.04,-5.7,-5.65,-0.2,-8.12,-12.07,-16.15,-13.43,-3.24,-0.62,-9.11,-10.08,-10.61,-12.26,-13.2,-10.46,-10.59,-12.36,-16.26,-21.23,-12.9,-11.56,-13.24,-24.06,-19.19,-20.61,-19.75,-17.66,-15.65,-27.2,-17.69,-27.48,-18.26,-13.23,-24.42,-22.68,-19.25,-28,-24.45,-22.49,-20.74,-24.09,-19.73,-26.03,-15.48,-16.68,-16.11,-33.22,-28.08,-27.37,-26.17,-11.85,-24.58,-24.21,-23.21,-24.12,-21.81,-10.05,-24.46,-22.16,-22.35,-20.1,-18.8,-15.07,-19.05,-35.65,-20.28,-17.49,-25.87,-12.37,-29.46,-36.13,-29.3,-26.97,-24.82,-13.85,-29.82,-33.69,-28.8,-22.95,-18.31,-25.65,-24.24,-35.26,-28.03,-27.68,-10.36,-19.53,-31.13,-34.14,-31.83,-19.32,-24.25,-22.91,-17.12,-20.21,-18.39,-26.12,-23.99,-14.04,-17.42,-21.01,-24.53,-15.9,-23.75,-16.89,-22.48,-33.29,-31.06,-14.03,-13.1,-11.51,-24.88,-24.45,-24.37,-22.96,-9.25,-13.53,-25.48,-22.11,-19.29,-15.03,-7.07,-13.01,-14.78,-22.14,-15.57,-16.66,-7.85,-15.65,-17.37,-16.15,-21.32,-12.96,-7.88,-13.62,-10.5,-16.12,-14.6,-9.64,-2.62,-7.71,-9.65,-11.61,-8.3,-6.25,-3.99,-3.63,-9.1,-9.88,-6.83,-2.16,0.63,-3.5,-6.02,-10.73,-4.71,1.65,1.21,0.23,-3.28,-8.18,-3.17,0.26,3.2,-0.07,-7.11,-9.48,-3.5,2.42,5.37</v>
       </c>
     </row>
     <row r="80">
@@ -1276,7 +1276,7 @@
         <v>[L_04_标记]</v>
       </c>
       <c r="C80" t="str">
-        <v>a: 23.6ms -38.6uv b: 48.6ms 167.4uv</v>
+        <v>a: 20.9ms -31.8uv b: 45.4ms 208.1uv</v>
       </c>
     </row>
     <row r="81">
@@ -1287,7 +1287,7 @@
         <v>[R_05_名字]</v>
       </c>
       <c r="C81" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="82">
@@ -1298,7 +1298,7 @@
         <v>[R_05_放大器]</v>
       </c>
       <c r="C82" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="83">
@@ -1309,7 +1309,7 @@
         <v>[R_05_闪光]</v>
       </c>
       <c r="C83" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="84">
@@ -1320,7 +1320,7 @@
         <v>[R_05_闪光背景]</v>
       </c>
       <c r="C84" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="85">
@@ -1331,7 +1331,7 @@
         <v>[R_05_采样]</v>
       </c>
       <c r="C85" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="86">
@@ -1342,7 +1342,7 @@
         <v>[R_05_分析时间]</v>
       </c>
       <c r="C86" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="87">
@@ -1364,7 +1364,7 @@
         <v>[R_05_详细数据(uv)]</v>
       </c>
       <c r="C88" t="str">
-        <v>-15.2,-18.28,-22.24,-20.85,-17.62,-19.4,-23.82,-23.67,-20.1,-20.55,-25.1,-26.36,-23,-22.19,-26.49,-29.13,-26.44,-24.56,-28.19,-31.98,-30.31,-27.61,-30.19,-34.71,-34.26,-31.01,-32.23,-36.93,-37.68,-34.19,-33.83,-38.11,-39.89,-36.44,-34.43,-37.68,-40.16,-37,-33.43,-35.15,-37.9,-35.25,-30.35,-30.2,-32.77,-30.75,-24.94,-22.77,-24.71,-23.41,-17.18,-13.11,-14.07,-13.51,-7.43,-1.77,-1.54,-1.65,3.71,10.42,11.93,11.25,15.38,22.48,25.19,24.09,26.6,33.37,37.03,35.71,36.39,42.13,46.4,45.05,43.88,48.01,52.46,51.3,48.46,50.55,54.74,53.94,49.79,49.68,53.18,52.87,47.93,45.65,48.11,48.37,43.21,39.06,40.24,41.05,36.28,30.73,30.49,31.78,27.91,21.58,19.93,21.52,18.96,12.5,9.58,11.23,10.2,4.26,0.31,1.74,2.23,-2.64,-7.31,-6.4,-4.56,-7.98,-13,-12.87,-10.08,-11.83,-16.83,-17.69,-14.44,-14.53,-19.15,-21.09,-17.95,-16.56,-20.47,-23.47,-20.99,-18.46,-21.41,-25.31,-23.91,-20.69,-22.5,-27.01,-26.99,-23.55,-24.12,-28.83,-30.27,-27.08,-26.4,-30.83,-33.61,-31.03,-29.19,-32.83,-36.62,-34.91,-32.07,-34.46,-38.76,-38.04,-34.43,-35.21,-39.43,-39.66,-35.56,-34.51,-38.05,-39.07,-34.79,-31.88,-34.2,-35.73,-31.6,-27,-27.68,-29.41,-25.74,-19.82,-18.63,-20.22,-17.28,-10.56,-7.51,-8.65,-6.65,0.24,4.92,4.46,5.41,11.79,17.68,18.04,17.92,23.16,29.67,30.9,29.78,33.37,39.84,41.85,39.93,41.52,47.29,49.92,47.46,46.93,51.4,54.4,51.73,49.19,51.91,54.99,52.46,48.23,48.95,51.81,49.73,44.33,43,45.36,44,38.06,34.84,36.45,35.97,30.16,25.41,26.09,26.53,21.47,15.71,15.33,16.6,12.81,6.61,5.15,7.03,4.84,-1.21,-3.69,-1.54,-2.01,-7.37,-10.75,-8.71,-7.57,-11.8,-15.87,-14.37,-11.93,-14.75,-19.24,-18.62,-15.36,-16.65,-21.27,-21.81,-18.27,-18.09,-22.5,-24.32,-21.09,-19.62,-23.5,-26.55,-24.13,-21.68,-24.72,-28.78,-27.55,-24.48,-26.43,-31.1,-31.26,-27.96,-28.61,-33.41,-34.93,-31.75,-31.03,-35.36,-38.04,-35.28,-33.19,-36.5,-39.93,-37.81,-34.46,-36.27,-39.95,-38.57,-34.21,-34.17,-37.54,-36.9,-31.88,-29.83,-32.37,-32.39,-27.1,-23.13,-24.4,-24.93,-19.82,-14.23,-13.95,-14.79,-10.31,-3.59,-1.67,-2.62,0.86,8.05,11.51,10.66,12.83,19.79,24.47,23.9,24.6,30.62,36.08,35.91,35.13,39.6,45.28,45.6,43.47,45.95,51.28,52.1,48.92,49.18,53.6,54.88,51.05,49.11,52.18,53.83,49.82,45.93,47.36,49.21,45.52,40.15,39.79,41.68,38.72,32.5,30.4,32.12,30.23,23.83,20.22,21.55,20.91,15.02,10.25,10.98,11.6,6.79,1.31,1.28,2.98,-0.31,-6.01,-6.94,-4.48,-6.04,-11.47,-13.35,-10.59,-10.41,-15.15,-17.96,-15.38,-13.69,-17.4,-21.02,-19.12,-16.29,-18.76,-22.98,-22.16,-18.7,-19.83,-24.36,-24.88,-21.34,-21.16,-25.64,-27.57,-24.47,-23.12,-27.14,-30.37,-28.14,-25.82,-29,-33.19,-32.1,-29.1,-31.06,-35.75,-35.89,-32.5,-32.98,-37.57,-38.86,-35.37,-34.24,-38.11,-40.29,-36.98,-34.22,-36.81,-39.5,-36.59,-32.37,-33.25,-36,-33.67,-28.3,-27.21,-29.56,-27.91,-21.85,-18.77,-20.31,-19.38,-13.17,-8.3,-8.73,-8.51,-2.72,3.51,4.35,3.94,8.77,15.75,17.87,16.97,20.37,27.42,30.64,29.42,31.1,37.47,41.51,40.17,39.99,45.05,49.5,48.25,46.28,49.5,53.93,52.95,49.47,50.55,54.5,53.95,49.39,48.25,51.32,51.31,46.22,43.03,44.92,45.47,40.45,35.58,36.1,37.17,32.78,26.79,25.87,27.33,24.05,17.58,15.29,16.94,15.09,8.79,5.33,6.9,6.6,1.1,-3.26,-2.06,-0.9,-5.13,-10.03,-9.48,-7.15,-9.79,-14.87,-15.21,-12.15,-13.1,-17.97,-19.35,-16.1,-15.45</v>
+        <v>-8.28,-24.43,-14.17,3.05,-5.92,-22.53,-13.15,4.61,-3.39,-20.45,-12.01,6.21,-0.82,-18.32,-10.87,7.71,1.63,-16.28,-9.88,8.98,3.84,-14.46,-9.16,9.9,5.69,-12.97,-8.81,10.37,7.08,-11.9,-8.9,10.34,7.97,-11.28,-9.45,9.77,8.34,-11.12,-10.47,8.69,8.21,-11.39,-11.91,7.16,7.64,-12.02,-13.68,5.26,6.73,-12.91,-15.67,3.11,5.59,-13.93,-17.76,0.84,4.36,-14.95,-19.81,-1.42,3.16,-15.86,-21.69,-3.53,2.11,-16.52,-23.29,-5.44,1.29,-16.86,-24.64,-7.03,0.71,-16.92,-25.49,-8.46,0.28,-16.67,-26.25,-9.39,0.18,-16.7,-27.23,-11.07,-0.9,-16.07,-28.54,-12.91,-0.56,-15.99,-30.5,-14.74,-1.95,-18.16,-30.81,-16.28,-6.3,-22.07,-35.88,-20.21,-10.04,-20.69,-35.38,-28.48,-13.37,-22.4,-37.96,-29.77,-20.94,-26.16,-49.05,-29.87,-23.4,-29.24,-45.15,-41.79,-24.45,-36.09,-41.44,-37.32,-19.54,-26.45,-51.49,-29.13,-14.63,-19.16,-38.6,-32.34,-5.45,-8.96,-25.88,-19.58,-2.83,-2.76,-15.44,-7.79,10.51,7.99,-8.61,6.84,24.31,28.82,13.02,12.95,38.92,34.77,22.38,26.23,59.44,49.01,49.9,41.51,64.64,81.45,57.85,67.75,91.79,98.93,77.22,89.31,99.19,110.81,112.37,105.65,120.89,142.22,134,105.31,159.36,145.31,132.21,157.79,164.81,156.03,168.33,143.52,192.73,183.79,187.88,170.14,191.03,208.95,172.41,169.85,201.46,227.5,174.99,179.25,234.26,210.55,219.43,196.77,208.81,217.69,186.13,193.32,196.07,207.84,203.17,207.7,193.54,195.24,188.18,173.64,180.13,181.05,176.94,170.06,192.3,165.9,171.42,136.82,138.32,164.62,162.48,125.86,130.03,152.58,112.95,116.94,104.86,112.93,98.24,93.67,87.64,111.92,96.09,60.64,81.72,85.77,70.84,48.14,57.09,63.84,52.38,35.1,46.13,59.25,48.1,18.09,26.19,38.39,31.15,15.06,17.13,31.22,24.52,2.46,6.43,25.96,18.43,-2.64,1.56,16.72,12.71,-7.3,-5.47,13.21,8.91,-10.5,-8.17,11.05,8.83,-10.53,-10.09,9.56,7.63,-11.82,-10.89,8.7,8.6,-10.39,-10.62,9.14,10.01,-8.73,-9.89,9.56,11.65,-6.99,-9.47,9.83,12.89,-5.38,-9.13,10.72,14.69,-3.72,-8.68,10.96,14.82,-2.89,-8.88,10.03,16.62,-2.34,-9.23,9.99,16.56,-1.66,-9.41,7.18,15.3,-2.25,-11.92,5.63,13.8,-2.06,-14.07,3.76,11.49,-5.29,-13.7,-0.42,11.62,-6.69,-16.41,-2.35,6.8,-6.08,-18.91,-7.3,4.18,-10.47,-24.26,-7.81,5.72,-10.5,-26.47,-12.31,2.24,-11.28,-27.07,-14.52,-1.34,-11.38,-26.71,-20.92,-5.15,-13.87,-30.11,-16.27,-4.14,-13.98,-30.72,-21.53,-6.97,-17.5,-31.78,-24.62,-7.43,-18.62,-28.82,-18.94,-2.14,-18.56,-33.3,-22.98,-7.62,-9.19,-26.73,-19.8,-9.69,-12.41,-32.37,-23.38,-6.34,-12.77,-31.59,-23.05,-9.62,-10.62,-22.85,-26.3,-2.28,-11.47,-23.91,-19.84,-6.83,-11.6,-29.05,-19.96,-8.08,-1.75,-24.11,-33.86,-14.95,-2.55,-31.91,-24.33,-10.99,-7.36,-37.12,-29.89,-18.99,-12.81,-33.6,-42.07,-18.71,-5.19,-34.59,-42.34,-25.94,-13.12,-43.45,-49.11,-30.34,-14.98,-29.49,-51.64,-22.06,-24.78,-38.47,-52.35,-29.72,-16.18,-43.05,-53.99,-29.59,-24.76,-41.32,-40.5,-33.47,-14.07,-39.99,-58.19,-25.3,-20.81,-30.45,-53.7,-25.29,-27.49,-38.16,-50.39,-26.3,-29.07,-31.96,-47.12,-27.87,-12.16,-28.12,-39.67,-35.89,-12.15,-24.42,-41.59,-32.08,-18.5,-21.95,-36.06,-27.17,-14.1,-15.63,-32.43,-31,-16.04,-23.69,-28.02,-16.72,-0.45,-15.56,-31.66,-26.32,3,-9.73,-28.46,-17.57,-4.3,-4.9,-19.6,-13.32,6.57,-0.61,-23.84,-14.97,2.1,1.52,-26.86,-11.47,4.88,-1.03,-23.86,-16.4,8.03,-0.17,-21.9,-16.24,5.42,-3.56,-15.52,-17.55,2.79,-1.46,-16.48,-18.39,2.17,4.33,-15.19,-16.25,0.04</v>
       </c>
     </row>
     <row r="89">
@@ -1375,7 +1375,7 @@
         <v>[R_05_标记]</v>
       </c>
       <c r="C89" t="str">
-        <v>幅值: 39.7uv 相位: 51.5°</v>
+        <v>a: 22.7ms -28.8uv b: 48.6ms 174.2uv</v>
       </c>
     </row>
     <row r="90">
@@ -1386,7 +1386,7 @@
         <v>[L_05_名字]</v>
       </c>
       <c r="C90" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="91">
@@ -1397,7 +1397,7 @@
         <v>[L_05_放大器]</v>
       </c>
       <c r="C91" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="92">
@@ -1408,7 +1408,7 @@
         <v>[L_05_闪光]</v>
       </c>
       <c r="C92" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="93">
@@ -1419,7 +1419,7 @@
         <v>[L_05_闪光背景]</v>
       </c>
       <c r="C93" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="94">
@@ -1430,7 +1430,7 @@
         <v>[L_05_采样]</v>
       </c>
       <c r="C94" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="95">
@@ -1441,7 +1441,7 @@
         <v>[L_05_分析时间]</v>
       </c>
       <c r="C95" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="96">
@@ -1463,7 +1463,7 @@
         <v>[L_05_详细数据(uv)]</v>
       </c>
       <c r="C97" t="str">
-        <v>-20.76,-25.61,-26.23,-21.79,-24.31,-27.88,-23.82,-22.96,-27.9,-26.34,-22.65,-26.67,-28.49,-23.88,-25.14,-29.56,-26.39,-24.38,-29.36,-29.28,-25.11,-28.34,-31.51,-27.31,-27.33,-32.31,-30.24,-27.12,-31.57,-32.68,-27.99,-29.75,-33.51,-29.49,-27.66,-32.12,-30.6,-25.87,-28.64,-30.08,-24.43,-23.79,-27.06,-22.76,-18.47,-21.38,-19.87,-13.3,-13.67,-14.85,-8.33,-5.04,-7.35,-3.02,3.4,2.18,3.36,10.95,12.62,11.28,17.58,22.56,20.6,23.76,30.85,30.41,30.08,36.95,39.36,36.75,41.08,46.11,43.38,43.88,49.84,49,46.01,50.51,52.39,47.72,48.82,52.66,48.64,45.78,49.59,47.97,42.25,43.8,44.91,38.56,36.48,39.08,34.45,28.92,30.87,29.28,22.03,21.37,22.55,16.03,11.98,14.25,10.51,3.94,5.07,4.83,-2.18,-3.81,-1.48,-6.53,-11.12,-8.33,-9.89,-16.09,-15.03,-13.13,-18.67,-20.56,-16.78,-19.57,-24.06,-20.76,-19.93,-25.26,-24.44,-20.74,-24.64,-27,-22.49,-23.3,-27.88,-24.95,-22.43,-27.16,-27.38,-22.9,-25.59,-28.96,-24.81,-24.27,-29.26,-27.57,-24.17,-28.47,-30.18,-25.69,-27.32,-31.71,-28.43,-26.7,-31.74,-31.36,-27.21,-30.52,-33.29,-28.76,-28.75,-33.29,-30.56,-27.15,-31.16,-31.39,-26.06,-27.33,-30.14,-25.14,-22.68,-26.24,-23.51,-17.95,-19.92,-20.12,-13.44,-12.08,-14.27,-8.83,-3.84,-5.97,-3.37,3.88,3.98,3.61,10.79,14.26,12.33,17.16,23.55,22.23,23.59,31.01,32.13,30.53,36.49,40.61,37.86,40.46,46.5,44.83,43.6,49.36,50.22,46.35,49.51,52.9,48.58,47.83,52.22,49.6,45.26,48.38,48.51,42.37,42.3,44.63,39.12,35.25,37.94,34.97,28.35,29.2,29.27,22.14,19.72,21.74,16.5,10.88,12.77,10.84,3.64,3.35,4.57,-1.79,-5.19,-2.46,-5.91,-11.74,-9.78,-9.55,-15.86,-16.45,-13.44,-17.88,-21.43,-17.74,-18.76,-24.09,-22.03,-19.59,-24.53,-25.49,-21.14,-23.6,-27.38,-23.48,-22.49,-27.46,-26.1,-22.3,-26.18,-28.16,-23.53,-24.56,-29.02,-25.93,-23.71,-28.6,-28.66,-24.39,-27.44,-30.74,-26.6,-26.45,-31.49,-29.63,-26.44,-30.88,-32.29,-27.71,-29.45,-33.49,-29.78,-27.98,-32.68,-31.59,-27.05,-29.98,-31.89,-26.61,-26.11,-29.78,-25.98,-21.89,-25.08,-24.1,-17.84,-18.37,-20,-13.87,-10.68,-13.27,-9.35,-3.04,-4.32,-3.48,3.98,5.75,4.27,10.42,15.6,13.74,16.82,24.12,24.01,23.75,30.82,33.71,31.4,35.92,41.48,39.27,40.02,46.47,46.29,43.7,48.61,51.19,47.06,48.51,52.98,49.63,47.12,51.4,50.47,45.15,47.01,48.7,42.83,40.93,43.92,39.76,34.38,36.48,35.28,28.18,27.48,28.86,22.51,18.31,20.54,16.95,10.19,11.08,10.87,3.73,1.72,3.9,-1.24,-6.23,-3.77,-5.41,-11.93,-11.32,-9.57,-15.31,-17.67,-14.15,-17.04,-21.9,-18.96,-18.17,-23.71,-23.28,-19.66,-23.59,-26.25,-21.9,-22.62,-27.35,-24.63,-22.01,-26.7,-27.11,-22.58,-25.1,-28.58,-24.47,-23.7,-28.67,-27.1,-23.53,-27.68,-29.52,-25,-26.42,-30.89,-27.74,-25.86,-30.9,-30.75,-26.6,-29.85,-32.88,-28.55,-28.5,-33.28,-30.91,-27.58,-31.74,-32.43,-27.35,-28.75,-31.99,-27.42,-25.11,-29.01,-26.81,-21.5,-23.69,-24.4,-18.09,-16.87,-19.45,-14.45,-9.59,-11.92,-9.74,-2.65,-2.57,-3.22,3.76,7.34,5.35,10.01,16.56,15.42,16.72,24.28,25.78,24.31,30.41,35.01,32.63,35.41,41.93,40.83,39.9,46.07,47.62,44.21,47.73,51.79,48.08,47.68,52.64,50.72,46.77,50.3,51.1,45.43,45.63,48.48,43.5,39.82,42.82,40.34,33.91,34.85,35.28,28.36,25.87,28.03,22.99,17.25,19.03,17.23,9.92,9.33,10.53,4.1,0.32,2.83,-0.68,-6.87,-5.3,-5.18,-11.74,-12.8,-10,-14.58,-18.57,-15.22,-16.31,-21.95,-20.29,-17.94,-23.01,-24.35,-20.14,-22.58,-26.63</v>
+        <v>-16.59,-20.52,-6.67,1.69,-9.32,-20.46,-12.25,1.78,-1.8,-16.34,-16.46,-1.38,3.75,-9.24,-17.56,-6.4,5.8,-1.18,-14.82,-11.23,4.04,5.49,-8.8,-13.91,-0.6,8.88,-1.2,-13.21,-6.25,8.15,5.73,-9.11,-10.79,3.74,9.82,-2.81,-12.54,-2.75,9.81,3.62,-10.92,-9.12,5.66,7.97,-6.57,-13.42,-1.44,8.6,-1.1,-14.37,-9.34,4.99,3.27,-12.41,-16.07,-2.61,4.49,-8.16,-19.41,-11.02,1.22,-4.08,-19.38,-19.3,-5.23,-2.85,-16.81,-25.04,-14.8,-5.18,-14.74,-29.45,-26.88,-12.94,-10.97,-29.78,-32.18,-22.98,-12.85,-26.1,-37.47,-31.4,-18.67,-20.85,-39.61,-36.83,-25.28,-20.94,-38.62,-49.21,-34.89,-22.36,-31.94,-48.64,-46.57,-28.08,-21.67,-41.59,-51.03,-28.21,-23.37,-28.95,-39.69,-43.23,-19.22,-18.13,-34.92,-30.94,-14.42,-0.48,-17.18,-22.89,-14.3,6.24,3.18,-19.7,-15.44,9.28,11.92,7.2,1.44,10.35,33.45,31.19,15.26,28.68,48.11,42.32,38.49,39.66,58.89,67.39,58.65,56.77,76.9,85.63,96.32,90.61,71.46,94.39,95.27,87.49,92.21,116.97,112.71,134.1,102.02,107.7,153.91,155.9,133.91,115.98,139.82,164.08,166.5,158.43,174.92,152.86,154.15,173.51,176.97,180.49,205.14,162.59,190.36,172.15,218.68,207.21,170.06,194.99,205.13,201.46,168.56,161.85,176.04,200.2,219.21,191.66,173.38,182.25,182.96,183.85,169.88,209.29,180.42,175.79,175.88,160.09,175.05,189.2,171.55,172.8,177.61,200.73,174.33,137.67,144.61,159.97,168.02,159.99,154.98,164.28,148.37,125.29,120.65,149.99,134.61,132.27,106.18,127.83,119.43,115.08,108.84,83.78,97.43,102.02,78.76,75.57,89.41,94.95,77.54,61.23,63.03,67.09,74.32,54.12,49.94,53.8,67.53,51.84,29.35,39.39,46.3,43.56,22.98,19.25,35.72,33.55,19.33,10.08,17.56,28.18,16.56,3.12,3.52,16.88,19.44,2.39,-5.53,4.46,14.66,3.18,-10.38,-5.69,7.53,4.98,-12.44,-14.66,-1.64,4.79,-8.67,-18.09,-9.84,1.64,-3.45,-17.41,-18.15,-3.57,0.55,-13.88,-21,-9.86,1.02,-7.83,-20.55,-15.65,-0.97,-1.96,-16.14,-20.37,-7.01,2.67,-9.11,-20.47,-13.11,1.86,-2.37,-16.34,-16.68,-2.87,2.56,-10.92,-18.57,-9.66,2.91,-5.02,-17.17,-13.67,-1.1,2.21,-15.37,-19.27,-7.85,3.22,-9.34,-21.25,-16.44,0.29,-4.96,-20.08,-21.72,-8.42,-1.49,-14.72,-25.79,-17.99,-1.73,-10.23,-27.22,-22.65,-7.22,-9.02,-21.35,-32.25,-16.72,-10.53,-16.95,-32.86,-25.96,-11.27,-12.62,-32.06,-31.35,-25.92,-17.72,-24.68,-35.01,-28.87,-19.48,-25.58,-38.06,-36.15,-19.54,-16.47,-34.21,-44.6,-35.55,-22.63,-35.63,-41.36,-39.15,-29.38,-23.79,-38.81,-48.74,-29.91,-28.78,-35.69,-51.78,-35.1,-18.68,-27.8,-37.31,-49.86,-36.57,-22.97,-36.2,-40.16,-34.84,-24.36,-36.7,-51.37,-44.22,-24.96,-24.6,-47.87,-41.2,-29.89,-18.04,-31.83,-52.8,-45.5,-27.79,-26.84,-37.66,-38.17,-31.54,-16.64,-33.39,-55.73,-34.44,-19.03,-27.74,-53.57,-53.52,-28.48,-34.28,-39.16,-54.13,-43.05,-25.08,-42.46,-47.78,-48.23,-36.51,-32.3,-53.52,-60.11,-40.93,-35.93,-50.93,-44.16,-45.5,-31.2,-27.63,-51.53,-53.34,-36.45,-36.22,-48.1,-53.79,-39.63,-34.92,-35.73,-55.43,-49.16,-37.7,-33.67,-48.23,-56.25,-39.63,-32.02,-44.2,-56.42,-51.02,-34.59,-31.55,-43.09,-51.65,-42.37,-27.66,-38.88,-49.57,-38.62,-32.09,-31.8,-43.22,-50.31,-33.91,-27.29,-41.57,-45.24,-26.32,-20.36,-33.53,-44.41,-38.39,-24.84,-23.59,-31.43,-32.98,-19.71,-11.24,-26.11,-40.42,-24.18,-18.09,-18.61,-30.25,-35.78,-14.33,-12.42,-24.95,-36.35,-20.39,-8.8,-21.38,-28.37,-22.32,-9.57,-6.49,-24.04,-30.63,-16.53,-4.07,-15.69,-24.86,-16.41,-5.93,-12.5,-27.36,-26.11,-8.02,-5.63,-20.32,-30.44,-18.15,-6.85,-14.91,-28.59</v>
       </c>
     </row>
     <row r="98">
@@ -1474,12 +1474,3774 @@
         <v>[L_05_标记]</v>
       </c>
       <c r="C98" t="str">
-        <v>幅值: 37.3uv 相位: 51.5°</v>
+        <v>a: 22.9ms -28.5uv b: 48.8ms 234.4uv</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B99" t="str">
+        <v>[R_06_名字]</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B100" t="str">
+        <v>[R_06_放大器]</v>
+      </c>
+      <c r="C100" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B101" t="str">
+        <v>[R_06_闪光]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B102" t="str">
+        <v>[R_06_闪光背景]</v>
+      </c>
+      <c r="C102" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B103" t="str">
+        <v>[R_06_采样]</v>
+      </c>
+      <c r="C103" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B104" t="str">
+        <v>[R_06_分析时间]</v>
+      </c>
+      <c r="C104" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B105" t="str">
+        <v>[R_06_数据长度]</v>
+      </c>
+      <c r="C105" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B106" t="str">
+        <v>[R_06_详细数据(uv)]</v>
+      </c>
+      <c r="C106" t="str">
+        <v>-1.74,11.15,11.61,-1.04,7.85,14.8,1.53,4.28,16.03,5.45,1.41,15.1,9.83,0.01,12.28,13.64,0.47,8.3,15.96,2.69,4.13,16.19,6.09,0.78,14.24,9.76,-1.01,10.5,12.72,-0.9,5.78,14.11,0.95,1.11,13.44,3.94,-2.52,10.71,7.15,-4.4,6.42,9.61,-4.23,1.43,10.54,-2.26,-3.2,9.5,0.86,-6.52,6.6,4.17,-7.87,2.37,6.73,-7.05,-2.26,7.76,-4.46,-6.29,6.86,-0.77,-8.88,4.21,3,-9.44,0.28,5.9,-7.8,-3.87,7.06,-4.74,-7.58,5.87,-0.72,-9.97,3.34,3.03,-10.4,-1.29,5.74,-8.11,-6.68,5.72,-5.59,-11.01,2.46,-4.04,-14.4,-2.42,-0.31,-14.34,-7.81,0.77,-13.39,-12.27,-2.28,-15.77,-20.18,-6.31,-9.76,-21.42,-11.2,-7.52,-28.82,-23.13,-10.01,-27.21,-25.18,-13.16,-22.92,-33.14,-10.67,-14.65,-36.87,-24.16,-15.01,-36.37,-25.54,-10.21,-28.48,-30.16,-5.77,-20.97,-22.12,-4.46,-3.74,-17.9,-8.11,-5.11,-15.88,-2.18,12.47,7.67,8.18,25.49,9.65,9.06,24.84,26.38,27.74,26.89,37.76,39.87,49.4,62.54,42.47,56.33,72.97,62.94,65.6,82.74,92.54,79.8,77.08,90.69,86.41,109.43,102.29,117.71,103.62,115.28,132.99,120.1,130.91,140.05,148.84,139.06,140.63,160.5,149.65,150.01,176.99,152.58,165.39,187.27,170.08,193.94,169.92,170.37,173.72,176.72,180.85,181.68,220.02,180.66,196.19,190.92,205.82,209.22,220.04,219.7,209.68,207.15,188.96,188.53,192.58,208.47,177.73,179.02,200.49,199.69,180.68,167.29,162.56,185.95,167.09,156.09,164.29,141.81,182.87,167.85,152.05,148.29,138.25,116.94,125.91,145.35,113.12,123.82,127.46,98.53,113.93,112.48,107.96,90.12,105.28,96.36,76.02,73.53,93.98,68.86,61.67,78.06,62.09,57.58,67,47.4,41.09,51.66,50.49,31.96,44.65,47.7,27.66,27.16,42.48,22.43,21.91,30.44,26.9,12.78,20.93,25.36,7.76,15.15,20.34,5.93,6.12,20.09,8.6,2.67,13.93,10.35,-1.23,9.17,11.15,-2.56,3.83,11.61,-0.2,-1.87,10.51,1.51,-4.77,7.55,4.44,-6.77,3.91,7.68,-7.08,-1.83,8.28,-4.75,-6.23,6.61,-2.14,-9.73,3.38,1.4,-11.09,-0.56,3.19,-10.75,-6.45,3.31,-8.39,-11.57,1.01,-6.84,-15.58,-1.38,-3.29,-16.55,-8.23,-0.91,-15.04,-13.75,-2.4,-14.51,-18.36,-5.67,-11.81,-21.09,-9.79,-10.28,-23.47,-13.16,-7.9,-21.39,-17.32,-8.55,-17.81,-21.67,-8.55,-17.22,-27.06,-15.05,-13.57,-26.6,-17.87,-10.44,-24.48,-25.98,-11.85,-20.24,-28.93,-12.5,-17.55,-31.62,-17.6,-14.17,-28.72,-21.29,-13.37,-26.62,-29.22,-12.45,-19.26,-25.18,-12.75,-17.43,-25.44,-18.2,-11.72,-30.34,-20.3,-14.02,-30.3,-27.34,-14.27,-22.27,-32.18,-14.34,-23.77,-35.94,-27.11,-22.69,-31.14,-32.97,-18.03,-32.78,-29.08,-24.45,-25.49,-41.53,-17.25,-23.24,-43.27,-31.84,-27.14,-40.21,-35.82,-23.19,-32.85,-45.56,-17.88,-35.48,-48.72,-30.46,-36.88,-35.3,-30.91,-22.71,-49.95,-39.7,-31.39,-45.81,-45.31,-40.31,-46.37,-54.56,-32.07,-31.72,-57.49,-37.49,-37.71,-48.14,-54.64,-28.29,-48.6,-55.82,-41.48,-42.28,-49.2,-46.83,-44.6,-50.92,-36.23,-37.48,-44,-40.44,-43.24,-47.93,-53.44,-45.72,-37.57,-57.65,-39.52,-35.73,-40.8,-49.79,-32.31,-44.8,-47.88,-30.66,-37.66,-44.89,-29.73,-42.53,-48.94,-30.65,-23.58,-51.86,-44.07,-35,-35.93,-39.04,-26.11,-42.03,-42.72,-26.18,-28.68,-39.93,-31.74,-24.59,-44.17,-41.3,-29.73,-30.4,-35.38,-26.3,-31.95,-37.93,-23.45,-28.28,-39.86,-29.98,-24.63,-40.79,-26.19,-20.25,-32.02,-33.76,-26.96,-31.95,-40.92,-29.02,-26.99,-39.08,-30.08,-18.86,-31.52,-33.59,-22.45,-33.89,-36.89,-20.94,-23.85,-37.97,-20.74,-21.54,-34.81,-28.82,-16.85,-33.05,-35.04,-18.93,-25.09,-33.3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B107" t="str">
+        <v>[R_06_标记]</v>
+      </c>
+      <c r="C107" t="str">
+        <v>a: 23.7ms -22.4uv b: 51.4ms 219.3uv</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B108" t="str">
+        <v>[L_06_名字]</v>
+      </c>
+      <c r="C108" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B109" t="str">
+        <v>[L_06_放大器]</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B110" t="str">
+        <v>[L_06_闪光]</v>
+      </c>
+      <c r="C110" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B111" t="str">
+        <v>[L_06_闪光背景]</v>
+      </c>
+      <c r="C111" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B112" t="str">
+        <v>[L_06_采样]</v>
+      </c>
+      <c r="C112" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B113" t="str">
+        <v>[L_06_分析时间]</v>
+      </c>
+      <c r="C113" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B114" t="str">
+        <v>[L_06_数据长度]</v>
+      </c>
+      <c r="C114" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B115" t="str">
+        <v>[L_06_详细数据(uv)]</v>
+      </c>
+      <c r="C115" t="str">
+        <v>15.46,-3.55,-3.79,16.27,8.57,-7.17,8.4,18.12,-0.9,-1.39,18.63,11,-4.94,10.38,20.14,1.03,0.21,20.09,12.47,-3.76,11.27,20.99,1.74,0.55,20.27,12.6,-3.92,10.78,20.46,1.06,-0.51,19.04,11.36,-5.45,8.95,18.62,-0.88,-2.79,16.64,8.99,-8.04,6.14,15.82,-3.68,-5.89,13.56,5.97,-11.22,2.87,12.68,-6.8,-9.2,10.16,2.81,-14.41,-0.64,9.49,-9.88,-12.21,7.06,-0.12,-17.15,-3.56,6.34,-12.66,-15.05,4.37,-2.17,-19.39,-6.81,4.14,-14.39,-18.17,0.89,-4.38,-22.06,-8.49,0.87,-17.41,-20.11,0.04,-7.51,-23.78,-13.64,0.43,-22.54,-26.13,-3.47,-12.67,-29.31,-17.1,-7.65,-19.64,-26.12,-7.49,-12.04,-31.29,-19.11,-4.82,-20.27,-27.95,-2.47,-9.91,-27.98,-15.04,-7.51,-21.86,-19.81,3.88,-0.27,-25.4,-7.28,8.24,-6,-8.27,9.44,-0.47,-9.41,-0.89,17.73,8.08,0.83,32.03,24.62,8.23,22.15,41.13,27.94,29.4,46.46,52.11,38.44,45.41,68.47,58.62,40.87,72.04,67.63,54.97,64.63,81.4,81.39,73.31,96.61,108.75,81.19,107.65,114.06,111.69,103.4,120.11,120.66,99.64,131.88,140.18,141.25,141.3,160.62,156.11,122.26,150.99,186.1,148.3,162.83,191.36,157.98,159.69,162.72,171.91,172.15,179.38,181.47,202.74,157.49,177.22,209.83,171.36,198.61,197.53,188.38,192.2,195.3,181.08,165.64,164.1,188.7,179.09,170.42,172.27,211.77,170.95,171.7,189.91,203.08,160.76,189.86,191.96,165.81,161.9,185.22,158.02,155.65,140.81,168.8,150.85,131.94,149.89,149.23,116.29,126.87,149,116.82,113.55,112.92,117.23,97.87,95.16,111.79,80.83,82.21,95.25,101.33,64.56,77.43,83.49,73.27,51.04,77.11,66.45,41.31,49.36,63.75,41.78,32.17,53.3,49.76,26.81,31.17,47.09,26.56,16.38,34.62,28.98,11.42,21.85,33.3,13.67,5.91,21.62,18.97,2.67,8.51,22.31,4.74,-3.39,15.72,15.41,-4.46,5.14,17.27,1.15,-6.54,13.71,10.49,-7.84,1.29,15.74,-0.94,-7.92,11.22,10.39,-9.53,0.66,15.34,-0.76,-8.58,11.32,9.76,-9.32,0.5,14.69,-1.4,-9.4,11.46,9.73,-10.66,0.09,13.54,-3.22,-11.03,9.07,8.11,-11.15,-2.49,12.95,-3.92,-13.96,5.91,5,-15.8,-6.62,7.47,-9.1,-17.72,3.45,1.27,-17.04,-11.18,5.38,-11.73,-20.02,-2.91,-3.32,-22.39,-15,-2.09,-16.56,-23.1,-7.31,-8.43,-24.89,-20.28,-2.17,-18.4,-31.15,-12.52,-10.15,-29.62,-22.62,-8.21,-20.69,-32.45,-15.93,-15.07,-30.65,-26.92,-7.36,-23.52,-35.94,-15.85,-11.86,-35.16,-24.07,-8.87,-27.26,-38.85,-12.51,-12.4,-32.07,-23.34,-10.78,-27.83,-31.34,-17.65,-19.05,-30.55,-31.6,-9.25,-26.51,-40.06,-9.81,-13.45,-33.21,-23.69,-8.45,-24.04,-38.99,-20.52,-18.71,-30.71,-24.51,-4.87,-30.92,-31.6,-22.77,-17.35,-28.65,-32.04,-10.4,-29.35,-35.89,-21.07,-25.51,-33.34,-26.85,-11.51,-34.16,-38.2,-23.73,-21.86,-34.63,-34.02,-16.66,-31.53,-52.26,-25.3,-25.69,-42.56,-45.52,-23.27,-36.03,-45.39,-34.16,-34.61,-55.25,-38.67,-21.09,-42.87,-44.83,-36.42,-23.54,-57.43,-52.14,-21.91,-36.55,-48.8,-37.87,-34.89,-52.69,-45.68,-31.9,-47.07,-54.29,-31.47,-30.81,-53.49,-46.11,-32.85,-42.91,-52.43,-36.37,-31.63,-48.48,-33.99,-31.2,-36.13,-40.14,-25.1,-25.34,-41.86,-32.85,-13.6,-39.54,-36.99,-25.45,-19.62,-47.25,-36.02,-14.78,-24.51,-39.83,-24.63,-22.35,-29.65,-31.17,-5.83,-26.38,-31.1,-10,-6.53,-35.07,-29.92,-11.57,-24.56,-32.05,-10.81,-6.87,-33.37,-26.71,-3.12,-15.2,-30.26,-15.54,-8.88,-24.04,-24.06,-8.93,-17.5,-28.45,-12.56,-8.95,-26.56,-19.77,-7.71,-18.22,-27.39,-15.59,-8.54,-31.65,-23.89,-8.31,-17.33,-30.82,-14.65,-10.18,-28.5,-22.61,-6.85,-19.1,-32.15</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B116" t="str">
+        <v>[L_06_标记]</v>
+      </c>
+      <c r="C116" t="str">
+        <v>a: 23.6ms -24.7uv b: 51.4ms 171.3uv</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B117" t="str">
+        <v>[R_07_名字]</v>
+      </c>
+      <c r="C117" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B118" t="str">
+        <v>[R_07_放大器]</v>
+      </c>
+      <c r="C118" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B119" t="str">
+        <v>[R_07_闪光]</v>
+      </c>
+      <c r="C119" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B120" t="str">
+        <v>[R_07_闪光背景]</v>
+      </c>
+      <c r="C120" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B121" t="str">
+        <v>[R_07_采样]</v>
+      </c>
+      <c r="C121" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B122" t="str">
+        <v>[R_07_分析时间]</v>
+      </c>
+      <c r="C122" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B123" t="str">
+        <v>[R_07_数据长度]</v>
+      </c>
+      <c r="C123" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B124" t="str">
+        <v>[R_07_详细数据(uv)]</v>
+      </c>
+      <c r="C124" t="str">
+        <v>2.77,-6.18,-1.08,1.09,-6.94,1.47,-1.8,-6.03,2.66,-4.89,-3.83,2,-7.14,-1.2,-0.36,-7.87,0.79,-3.7,-6.91,1.29,-6.96,-4.83,-0.06,-9.17,-2.43,-2.93,-9.77,-1.03,-6.67,-8.68,-1.01,-9.78,-6.58,-2.95,-12.19,-4.69,-6.56,-12.48,-3.63,-10.62,-11.84,-4.63,-14.78,-10.64,-7.69,-15.91,-8.37,-12.81,-17.31,-8.35,-15.67,-18.26,-13.66,-22,-16.53,-17.69,-26.96,-15.56,-24.59,-27.91,-20.15,-32.98,-27.18,-25.41,-33.9,-27.31,-29.8,-33.73,-35.4,-42.71,-36.8,-28.19,-39.54,-47.06,-43.3,-38.63,-37.36,-44.73,-45.04,-44.89,-36.86,-43.2,-40.93,-51.53,-36.29,-28.25,-47.41,-24.35,-27.59,-22.7,-14.49,-17.65,-33.01,1.9,-17.58,15.59,18.8,18.15,19.66,35.19,16.67,40.59,36.91,49.97,74.59,55.65,85.48,95.23,87.89,104.4,125.26,118.32,128.82,120.13,148.99,179.29,188.03,200.76,194.66,216.48,244.34,219.14,206.97,249.66,225.92,295.78,272.99,257.61,273.64,288.09,324.88,294.25,324.33,336.07,378.11,312.56,355.23,376.13,342.75,342.36,362.38,343.66,342.92,392.84,384.26,440.49,361.67,403.22,366.13,440.9,421.03,360.76,361.83,389.35,423.81,431.28,407.4,360.78,400.08,406.04,403.64,433.72,383.21,396.17,427.83,374.2,395.79,345.43,380.7,390.76,388.63,357.81,319.41,317.84,363.94,339.43,324.49,344.66,341.26,335.11,294.99,279.65,326.31,289.11,306.48,283.71,259.71,232.13,274.35,243.91,231.61,243.76,238,238.17,204.69,222.67,207.15,204.63,198.78,169.07,182.8,165.97,193.76,186.35,150.39,187.59,173.2,143.82,166.74,150.82,126.03,123.47,113.05,119.57,132.54,123.78,109.99,122.26,115.39,104.56,80.33,96.85,94.74,88.12,95.23,75.18,71.09,86.41,72.07,78.41,82.13,70.13,64.96,48.6,53.64,50.67,43.88,54.62,55.73,50.44,40.3,48.94,34.2,33.86,35.05,23.3,33.4,21.8,26.8,18.7,11.28,23.13,20.43,14.27,21.93,6.64,10.69,9.29,1.55,3.86,8.63,-6.25,5.04,3.33,-9.43,2,-6.34,-6.32,-2.41,-9.74,-5.22,-4.73,-12.85,-7.57,-9.26,-16.53,-9.23,-17.32,-16.33,-12.34,-18.27,-16.23,-13.43,-24.83,-15.59,-20.63,-24.75,-17.59,-23.06,-22.03,-19.34,-28.73,-20.57,-19.96,-32.68,-19.7,-23.43,-27.04,-19.96,-35.47,-32.69,-25.74,-38.14,-32.49,-27.31,-33.16,-29.95,-33.57,-39.43,-33.92,-39.95,-33.81,-33.17,-36.53,-39.21,-30.35,-45.31,-29.67,-41.1,-40.39,-39.33,-45.2,-45.5,-32.69,-45.87,-32.82,-37.24,-51.82,-40.35,-42,-50.57,-38.64,-50,-37.33,-40.88,-44.99,-42.9,-40.33,-54.45,-34.53,-42.7,-51.29,-40.16,-55.28,-37.54,-51.69,-59.8,-37.53,-45.01,-49.5,-37.67,-51.9,-54.4,-44.34,-53.67,-49.62,-48,-55.45,-45.9,-45.48,-47.98,-51.63,-46.83,-52,-40.85,-53.51,-47.55,-53.81,-61.87,-52.79,-59.25,-53.73,-54.31,-62.72,-67.55,-48.86,-72.16,-59.83,-61.23,-53.21,-57.09,-69.94,-68.38,-64.7,-61.36,-48.58,-66.26,-68.77,-54.57,-51.04,-68.6,-63.28,-54.69,-67.36,-61.02,-74.6,-48.54,-51.46,-77.16,-46.44,-74.59,-67.23,-60.99,-60.98,-56.01,-46.89,-68.86,-57.63,-54.8,-69.14,-65.39,-62.37,-70.24,-63.97,-53.34,-63.6,-57.95,-71.56,-55.27,-52.68,-60.94,-50.46,-52.39,-56.26,-45.99,-49.68,-59.92,-47.76,-65.72,-43.7,-47.28,-54.81,-53.49,-44.9,-59.19,-53,-51.96,-42.16,-50.47,-53.3,-46.87,-46.18,-50.97,-42.78,-55.95,-43.15,-36.99,-42.2,-43.92,-35.17,-40.16,-36.52,-49.53,-42.71,-42.87,-46.63,-38.18,-33.71,-47.24,-36.21,-33.44,-45.06,-30.64,-44.92,-39.68,-35.91,-44.02,-41.06,-33.55,-40.64,-30.82,-39.75,-43.06,-31.8,-34.12,-34.53,-30.64,-42.41,-30.5,-36.71,-42.28,-28.19,-37.73,-34.17,-30.42,-36.33,-35.42,-32.29,-34.77,-28.14,-29.73,-35.85,-24.53,-33.01,-34.46,-25.99,-35.11,-28.17,-28.12,-32.8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B125" t="str">
+        <v>[R_07_标记]</v>
+      </c>
+      <c r="C125" t="str">
+        <v>a: 26.4ms -80.0uv b: 55.5ms 264.9uv</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B126" t="str">
+        <v>[L_07_名字]</v>
+      </c>
+      <c r="C126" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B127" t="str">
+        <v>[L_07_放大器]</v>
+      </c>
+      <c r="C127" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B128" t="str">
+        <v>[L_07_闪光]</v>
+      </c>
+      <c r="C128" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B129" t="str">
+        <v>[L_07_闪光背景]</v>
+      </c>
+      <c r="C129" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B130" t="str">
+        <v>[L_07_采样]</v>
+      </c>
+      <c r="C130" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B131" t="str">
+        <v>[L_07_分析时间]</v>
+      </c>
+      <c r="C131" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B132" t="str">
+        <v>[L_07_数据长度]</v>
+      </c>
+      <c r="C132" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B133" t="str">
+        <v>[L_07_详细数据(uv)]</v>
+      </c>
+      <c r="C133" t="str">
+        <v>-3.85,-3.04,-16.22,-1.83,-4.33,-15.58,-0.22,-5.92,-14.75,0.92,-7.73,-13.75,1.54,-9.68,-12.64,1.63,-11.69,-11.45,1.16,-13.66,-10.24,0.18,-15.51,-9.05,-1.28,-17.15,-7.93,-3.14,-18.52,-6.93,-5.34,-19.54,-6.1,-7.76,-20.17,-5.45,-10.3,-20.39,-5.03,-12.87,-20.19,-4.86,-15.34,-19.61,-4.95,-17.66,-18.62,-5.38,-19.67,-17.37,-6.07,-21.38,-16,-7.22,-22.86,-14.66,-8.91,-24.54,-13.18,-10.27,-25.79,-13.13,-13.73,-26.88,-12.54,-15.96,-28.89,-13.73,-21.84,-31.29,-14.91,-25.51,-33.4,-20.73,-28.64,-32.53,-21.2,-39.41,-35.06,-31.12,-40.77,-43.73,-33.8,-58.13,-44.22,-40.56,-66.71,-45.68,-57.98,-65.33,-60.78,-47.38,-66.9,-58.86,-51.62,-71.19,-61.53,-55.82,-64.46,-54.07,-76.59,-75.12,-52.5,-60.83,-60.02,-34.33,-46.68,-45.02,-23.77,-23.14,-28.53,-9.49,-26.45,-14.32,12.93,2.47,26.71,35.52,34.47,54.6,56.22,60.08,68.53,93.05,105,133.6,105.85,114.02,169.81,153.16,141.64,205.74,184.63,175.2,223.8,234.11,240.29,229.48,254.53,272.61,254.01,292.89,269.18,313.51,289.72,347.39,302.6,299.06,311.67,350.27,343.55,341.48,336.16,386.26,412.69,409.83,409.77,427.95,375.58,364.14,446.18,357.02,390.25,437.98,400.8,398.81,387.31,363.51,376.49,450.36,344.85,368.7,435.7,382.9,361.72,404.32,347.2,342.4,343.87,322.03,369.57,308.45,297.63,320.22,322.22,320.35,308.25,312.02,284.03,283.96,262.67,234.54,244.53,255.51,246.91,215.07,217.34,210.21,228.7,197.32,165.79,197.64,174.36,177.95,189.67,168.9,151.24,155.62,148.63,147.63,125.45,113.94,146.18,144.41,91.11,133.65,95.47,98.41,109.62,112.64,108.63,88.94,98,89.22,109.45,88.56,64.57,93.5,91.61,88.8,73.49,81,84.68,73.84,69.65,48.71,82.22,56.61,61.04,51.23,33.35,64.86,55.94,42.45,41.16,53.32,30.86,39.66,34.41,22.45,53.26,41.76,26.03,37.64,19.66,14.51,28.92,27.05,24.43,31.72,16.85,15.06,21.97,6.01,21.44,22.55,9.24,15.91,22.42,4.93,17.11,13.91,3.02,11.24,9.93,-8.88,12.59,4.38,-6.3,7.91,-0.78,-13.34,6.6,-8.8,-14.41,1.65,-9.64,-9.6,-1.07,-15.66,-10.8,0.35,-20.09,-13.66,-4.55,-23.21,-13.02,-8.53,-24.69,-17.99,-16,-28.65,-19.27,-17.2,-27.17,-14.63,-19.17,-33.32,-20.62,-21.22,-33.97,-16,-26.19,-29.27,-20.87,-29.62,-33.63,-17.59,-35.89,-36.81,-21.11,-38.58,-31.68,-19.18,-35.46,-31.5,-27.88,-39.84,-32.69,-27.99,-43.91,-30.28,-35.06,-41.08,-27.71,-25.07,-44.57,-28.2,-36.1,-48.01,-21.72,-36.49,-48.89,-32.88,-35.43,-41.15,-30.15,-40.81,-33.43,-29.34,-43.39,-31.83,-20.35,-40.1,-38.13,-37.46,-49,-43.07,-36.98,-56.62,-27.29,-25.58,-39.93,-38.4,-46.14,-44.55,-26.85,-44.45,-47.96,-43.66,-46.5,-49.31,-30.11,-40.95,-59,-41.67,-51.4,-55.02,-41.26,-50.66,-59.96,-48.68,-62.24,-60.21,-34.26,-58.19,-58.36,-43.55,-68.04,-42.76,-40.1,-71.71,-44.61,-38.6,-57.38,-52.58,-60.06,-65.06,-50.88,-50.16,-68.92,-41.64,-52.74,-58.34,-39.63,-53.85,-71.63,-54.92,-55.38,-58.16,-34.89,-59.5,-51.24,-44.25,-56.43,-56.89,-42.29,-55.63,-53.4,-43.63,-53.41,-45.08,-52.7,-65.73,-38.67,-44.96,-63,-32.53,-45.74,-63.07,-45.62,-53.17,-52.97,-29.21,-40.51,-46.91,-26.57,-54.4,-41.65,-29.23,-46.93,-46.84,-38.25,-39.06,-37.93,-31.03,-40.83,-31.15,-26.35,-45.43,-34.42,-31.63,-35.12,-32.77,-34.83,-35.06,-25.28,-29.95,-33.91,-19.5,-32.16,-38.97,-27.03,-25.52,-37.31,-23.8,-35.46,-30.24,-25.87,-37.74,-34.07,-17.02,-33.21,-27.46,-15.73,-34.74,-21.7,-18.06,-40.07,-22.67,-17.34,-34.24,-21.31,-22.43,-37.94,-21.74,-25.91,-34.33,-17.31,-19.77,-29.67,-19.18,-22.62,-34.18,-16.51,-27.66,-24.93,-10.95,-22.8,-27.29</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B134" t="str">
+        <v>[L_07_标记]</v>
+      </c>
+      <c r="C134" t="str">
+        <v>a: 26.4ms -78.7uv b: 55.5ms 302.4uv</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B135" t="str">
+        <v>[R_08_名字]</v>
+      </c>
+      <c r="C135" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B136" t="str">
+        <v>[R_08_放大器]</v>
+      </c>
+      <c r="C136" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B137" t="str">
+        <v>[R_08_闪光]</v>
+      </c>
+      <c r="C137" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B138" t="str">
+        <v>[R_08_闪光背景]</v>
+      </c>
+      <c r="C138" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B139" t="str">
+        <v>[R_08_采样]</v>
+      </c>
+      <c r="C139" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B140" t="str">
+        <v>[R_08_分析时间]</v>
+      </c>
+      <c r="C140" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B141" t="str">
+        <v>[R_08_数据长度]</v>
+      </c>
+      <c r="C141" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B142" t="str">
+        <v>[R_08_详细数据(uv)]</v>
+      </c>
+      <c r="C142" t="str">
+        <v>22.76,6.05,15.47,14.52,6.05,21.1,1.17,19.38,4.57,10.23,12.38,0.41,16.87,-3.57,13.95,1.38,4.72,10.52,-3.95,15.11,-4.05,12.13,4.17,4.08,13.99,-1.34,18.24,-0.56,13.55,7.87,3.68,15.89,-2.9,15.69,-2.68,6.62,3.44,-5.64,8.6,-11.67,7.26,-6.95,-0.6,2.52,-8.21,10.33,-7.56,12.78,2.82,9.82,16.73,6.51,26.91,8.87,24.04,16.37,17.4,23.16,6.94,23.79,3.33,14.44,4.88,-1.11,6.47,-9.86,5.14,-10.88,0.74,-1.99,-6.97,10.73,-4.2,18.57,7.62,21.34,25.97,19.35,42.33,20.47,40.61,31.82,30.06,35.8,19.29,32.59,8.06,18.32,1.82,-4.41,1.53,-20.92,-5.36,-28.78,-12.27,-16.73,-19.57,-2.89,-14.81,10.68,-0.24,19.82,23.86,23.68,38.79,21.24,49.75,26.56,44.7,35.81,24.2,33.13,4.52,14.09,-6.8,-12.23,-11.86,-30.23,-19.49,-42.58,-29.7,-36.4,-30.27,-19.31,-26.99,2.16,-8.41,14.99,15.8,26.15,41.8,27.61,44.49,32.14,46.36,38.91,29.67,36.46,7.08,19.04,-6.23,-2.49,-13.69,-23.94,-9.34,-35.38,-16.3,-26.76,-21.92,-14.62,-19.01,9.64,-4.83,21.43,19.04,29.14,39.65,27.87,50.24,26.98,42.76,35.54,30.03,36.37,12.97,26.58,1.27,10.34,-4.57,-13.19,-2.45,-21.15,-3.63,-17.93,-7.24,-8.18,-8.94,10.79,-4.64,20.23,9.83,19.88,26.52,15.06,33.91,13.33,34.66,20.85,23.28,22.45,4.75,20.45,-3.69,8.36,-4.87,-7.55,-0.8,-17.78,0.04,-19.16,-1.44,-7.54,-6.91,6.08,-9.18,12.51,-2.6,10.74,8.72,5.44,18.66,1.23,18.57,3.05,11.38,10.17,-0.39,14.26,-6.76,10.41,-3.88,0.48,3.14,-7.88,8.61,-9.48,7.5,-2.26,0.67,9.7,-4.29,16.15,-1.75,14.13,7.84,6.7,17.85,1.64,21.5,3.27,15.6,11.53,6.12,18.98,0.18,19.46,2.98,12.19,11.56,2.94,18.68,-0.22,18.32,4.66,11.17,14.21,3.04,20.78,1.23,18.81,7.51,10.24,16.48,2.22,20.78,1.24,16.57,7.85,6.73,15.95,-0.89,18.28,-0.53,12.27,6.78,2.26,14.48,-4.03,15.36,-1.79,8.24,6.43,-1.4,13.39,-6.05,12.79,-2.21,4.75,6.49,-4.45,12.42,-7.44,10.28,-2.1,1.56,6.88,-6.73,11.75,-7.83,8.3,-0.94,-0.65,8.16,-7.61,11.91,-6.69,7.34,1.52,-1.54,10.42,-7.04,12.89,-4.22,7.22,4.96,-1.43,13.26,-5.39,14.22,-0.88,7.53,8.84,-0.72,16.15,-3.14,15.47,2.8,7.85,12.62,0.13,18.59,-0.79,16.15,6.26,7.72,15.76,0.68,20.07,1.17,15.84,9,6.78,17.76,0.55,20.21,2.38,14.29,10.69,4.85,18.43,-0.37,18.93,2.74,11.52,11.3,2.06,17.81,-1.94,16.42,2.43,7.83,11.05,-1.26,16.21,-3.8,13.08,1.81,3.73,10.33,-4.58,14.12,-5.44,9.48,1.36,-0.21,9.65,-7.33,12.07,-6.35,6.2,1.54,-3.4,9.43,-9,10.51,-6.13,3.68,2.67,-5.45,9.98,-9.29,9.71,-4.59,2.16,4.84,-6.2,11.32,-8.18,9.69,-1.84,1.63,7.88,-5.76,13.25,-5.9,10.23,1.8,1.81,11.38,-4.48,15.35,-2.89,10.91,5.78,2.27,14.78,-2.86,17.09,0.28,11.23,9.5,2.52,17.5,-1.41,17.95,3.05,10.75,12.43,2.15,19.08,-0.53,17.57,5.04,9.21,14.21,0.95,19.27,-0.42,15.84,6.07,6.58,14.76,-1.06,18.08,-1.04,12.89,6.23,3.1,14.23,-3.58,15.8,-2.07,9.12,5.84,-0.77,13.01,-6.15,12.91,-3.07,5.09,5.36,-4.45,11.61,-8.22,9.97,-3.54,1.39,5.27,-7.36,10.51,-9.3,7.5,-3.07,-1.47,5.93,-9.08,10.07,-9.05,5.83,-1.42,-3.21,7.5,-9.41,10.4,-7.42,5.06,1.34,-3.78,9.85,-8.42,11.37,-4.6,5.04,4.92,-3.41,12.66,-6.45,12.64,-1.03,5.39</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B143" t="str">
+        <v>[R_08_标记]</v>
+      </c>
+      <c r="C143" t="str">
+        <v>82.1uv</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B144" t="str">
+        <v>[L_08_名字]</v>
+      </c>
+      <c r="C144" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B145" t="str">
+        <v>[L_08_放大器]</v>
+      </c>
+      <c r="C145" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B146" t="str">
+        <v>[L_08_闪光]</v>
+      </c>
+      <c r="C146" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B147" t="str">
+        <v>[L_08_闪光背景]</v>
+      </c>
+      <c r="C147" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B148" t="str">
+        <v>[L_08_采样]</v>
+      </c>
+      <c r="C148" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B149" t="str">
+        <v>[L_08_分析时间]</v>
+      </c>
+      <c r="C149" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B150" t="str">
+        <v>[L_08_数据长度]</v>
+      </c>
+      <c r="C150" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B151" t="str">
+        <v>[L_08_详细数据(uv)]</v>
+      </c>
+      <c r="C151" t="str">
+        <v>-15.34,-20.76,-6.16,-25.08,-9.03,-16.9,-20.5,-7.33,-26.11,-9.27,-19.04,-20.91,-9.35,-27.86,-10.46,-22.03,-21.99,-12.04,-30.02,-12,-24.92,-23.03,-14.48,-31.28,-12.83,-26.78,-22.5,-15.46,-30.98,-11.98,-27.26,-20.52,-15.46,-30.31,-11.45,-27.9,-19.79,-17.3,-30.86,-13.01,-30.82,-21.68,-20.84,-33.86,-16.03,-33.78,-23.7,-23.07,-34.18,-15.11,-32.85,-19.09,-20.21,-27.06,-8.95,-25.52,-9.28,-13.79,-19.34,-2.96,-20.4,-5.62,-10.41,-18.08,-3.68,-24.91,-10.37,-20.86,-25.64,-14.68,-36,-18.72,-31.33,-30.98,-20.5,-34.37,-15.52,-23.32,-19.88,-5.66,-18.45,2.67,-7.23,2.3,11.94,-5.86,17.43,-0.83,3.16,7.01,-12.02,0.79,-20.4,-19.34,-21.56,-40.09,-24.78,-44.22,-42.92,-39.73,-47.03,-27.05,-46.1,-26.11,-22.27,-26.51,-1.05,-15.27,1.84,6.75,4.95,21.45,5.07,15,7.8,-0.47,7.86,-18.05,-13.32,-26.12,-39.6,-34.2,-58.95,-53.35,-53.99,-59.32,-47.98,-58.38,-43.69,-43.8,-36.07,-15.71,-26.03,-0.38,-5.04,3.19,20.45,6.66,23.53,15.39,4.49,12.64,-12.74,3.68,-19.43,-23.63,-21.28,-46.92,-36.07,-53.49,-44.33,-37.07,-57.56,-37.03,-44.55,-30.68,-21.22,-27.83,-1.93,-12.85,1.79,6.8,-1.45,17.78,7.55,11.64,13.28,-1.9,14.63,-11.97,-3.62,-10.91,-24.41,-13.71,-32.95,-21.62,-31.15,-37.61,-18.17,-35.74,-20.78,-22.8,-26.5,-7.73,-22.82,-4.19,-7.39,-9.08,4.48,-13.46,2.83,-5.46,-10.34,1.59,-19.61,-5.03,-17.73,-20.25,-11.81,-30.92,-14.9,-28.82,-28.71,-17.58,-35.01,-16.12,-30.29,-24.61,-16.04,-31.08,-11.04,-24.9,-18.23,-11.5,-26.25,-6.82,-22.71,-16.15,-11.93,-25.86,-8.45,-25.81,-16.85,-15.5,-28.21,-10.35,-27.83,-17.45,-17.43,-27.92,-9.84,-27.3,-14.68,-16.07,-24.48,-6.98,-25.06,-10.72,-14.07,-20.96,-4.46,-23.07,-7.61,-13.09,-18.47,-3.37,-22.05,-5.81,-13.25,-16.79,-3.12,-21.59,-4.46,-13.68,-15.24,-3.02,-21.04,-3.21,-14.06,-13.73,-3.09,-20.67,-2.33,-14.81,-12.67,-3.82,-20.73,-2.17,-16.18,-12.25,-5.3,-21.35,-2.74,-18.1,-12.39,-7.35,-22.32,-3.81,-20.28,-12.81,-9.69,-23.37,-5.11,-22.5,-13.3,-12.09,-24.32,-6.47,-24.56,-13.7,-14.4,-25.03,-7.74,-26.31,-13.88,-16.45,-25.32,-8.77,-27.6,-13.69,-18.08,-25.09,-9.42,-28.28,-13.04,-19.18,-24.24,-9.62,-28.31,-11.9,-19.73,-22.78,-9.37,-27.7,-10.3,-19.76,-20.79,-8.74,-26.54,-8.37,-19.37,-18.4,-7.88,-24.98,-6.25,-18.71,-15.78,-6.93,-23.19,-4.14,-17.97,-13.14,-6.09,-21.38,-2.24,-17.33,-10.69,-5.55,-19.72,-0.74,-16.94,-8.6,-5.44,-18.38,0.22,-16.95,-7,-5.89,-17.47,0.55,-17.42,-5.98,-6.92,-17.03,0.21,-18.36,-5.54,-8.52,-17.02,-0.73,-19.69,-5.62,-10.58,-17.37,-2.18,-21.3,-6.09,-12.96,-17.94,-3.96,-23.01,-6.8,-15.46,-18.53,-5.9,-24.63,-7.55,-17.88,-18.98,-7.79,-25.97,-8.17,-20.02,-19.11,-9.44,-26.85,-8.49,-21.71,-18.77,-10.71,-27.15,-8.41,-22.85,-17.9,-11.52,-26.8,-7.87,-23.37,-16.46,-11.84,-25.8,-6.9,-23.3,-14.53,-11.72,-24.23,-5.57,-22.73,-12.2,-11.27,-22.23,-4.03,-21.79,-9.65,-10.64,-19.96,-2.46,-20.67,-7.08,-10,-17.63,-1.05,-19.54,-4.69,-9.56,-15.43,0.02,-18.6,-2.66,-9.46,-13.55,0.58,-17.98,-1.16,-9.82,-12.1,0.54,-17.78,-0.26,-10.71,-11.17,-0.14,-18.04,0,-12.12,-10.73,-1.44,-18.7,-0.33,-13.97,-10.74,-3.25,-19.67,-1.14,-16.12,-11.06,-5.42,-20.8,-2.26,-18.41,-11.52,-7.77,-21.9,-3.52,-20.62,-11.95,-10.08,-22.78,-4.73,-22.55,-12.17,-12.17,-23.27,-5.7,-24.04,-12.01,-13.87,-23.23,-6.31,-24.95,-11.4,-15.07,-22.58,-6.48,-25.22,-10.28,-15.72,-21.3,-6.2,-24.85,-8.69,-15.86,-19.47,-5.54,-23.91,-6.73,-15.57,-17.19,-4.6,-22.53</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B152" t="str">
+        <v>[L_08_标记]</v>
+      </c>
+      <c r="C152" t="str">
+        <v>74.9uv</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B153" t="str">
+        <v>[R_09_名字]</v>
+      </c>
+      <c r="C153" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B154" t="str">
+        <v>[R_09_放大器]</v>
+      </c>
+      <c r="C154" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B155" t="str">
+        <v>[R_09_闪光]</v>
+      </c>
+      <c r="C155" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B156" t="str">
+        <v>[R_09_闪光背景]</v>
+      </c>
+      <c r="C156" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B157" t="str">
+        <v>[R_09_采样]</v>
+      </c>
+      <c r="C157" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B158" t="str">
+        <v>[R_09_分析时间]</v>
+      </c>
+      <c r="C158" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B159" t="str">
+        <v>[R_09_数据长度]</v>
+      </c>
+      <c r="C159" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B160" t="str">
+        <v>[R_09_详细数据(uv)]</v>
+      </c>
+      <c r="C160" t="str">
+        <v>-10.83,-8.96,-12.07,-8.22,-13.22,-7.56,-14.24,-7.01,-15.07,-6.6,-15.7,-6.35,-16.09,-6.27,-16.22,-6.36,-16.1,-6.62,-15.72,-7.05,-15.11,-7.61,-14.28,-8.28,-13.27,-9.03,-12.12,-9.82,-10.87,-10.61,-9.57,-11.35,-8.28,-12.02,-7.04,-12.59,-5.89,-12.98,-4.9,-13.23,-4.09,-13.32,-3.49,-13.14,-3.17,-12.84,-2.99,-12.53,-3.33,-11.9,-3.74,-11.08,-4.72,-10.8,-5.9,-10.17,-7.36,-9.13,-8.35,-9.52,-9.77,-8.86,-11.95,-10.28,-16.16,-11.45,-18.98,-12.51,-20.52,-11.61,-24.37,-16.54,-25.14,-22.14,-34.21,-20.75,-34.46,-30.06,-34.75,-28.96,-36.33,-40.71,-48.54,-36.97,-46.66,-47.54,-48.37,-56.75,-54.76,-54.27,-56.48,-49.42,-50.58,-58.69,-58.81,-68.82,-40.64,-50.84,-46.66,-48.37,-41.19,-59.97,-37.94,-47.58,-25.17,-34.42,-15,-20.84,-14.55,-13.79,-14.7,7.17,-3.68,-0.82,24.12,37.78,29.24,44.56,63.65,74.63,85.01,69.89,72.81,107.64,122.77,125.08,143.23,142.71,135.9,189,173.76,197.35,182.23,223.43,228.08,219.07,209.61,264.77,277.93,299.04,268.1,279.08,307.66,321.36,333.89,346.25,287.39,357.87,347.45,377.62,314.65,313.09,349.68,357.03,347.72,393.49,355.3,410.79,352.72,424.13,374.16,397.39,353.93,404.53,426.42,341.32,400.13,370.68,371.55,408.74,422.78,371.98,393.03,326.01,331.62,356.82,383.82,346.87,357.27,344.44,309.02,342.15,307.66,320.25,281.08,318.22,297.8,305.58,283.95,265.96,257.53,274.41,269.06,231.84,255.71,236.02,217.94,253.39,211.91,233.54,192.99,208.92,182.32,212.03,200.79,185.31,164.87,183.59,163.97,160.35,163.07,160.74,149.09,153.45,146.7,142.17,156.52,131.36,137.02,108.76,123.66,102.91,127.07,114.52,93.8,92.76,118.22,110.83,106.61,94.75,93.6,74.1,88.56,67.39,100.36,70.24,86.76,59.96,60.76,75.57,73.55,52.68,49.34,68.66,61.47,60.02,62.41,66.63,35.59,42.34,42.73,38.08,27.03,45.9,31.86,36.36,28.78,28.31,20.57,34.56,15.59,28.97,22.95,24.2,15.41,18.1,16.19,16.97,15.57,10.8,12.79,6.37,12.36,3.15,11.21,4.54,4.71,-3.47,6.4,-7.36,5.05,-7.68,4.18,-7.77,0.34,-9.09,-2.56,-7.99,1.09,-9.27,-2.97,-11.04,-7.03,-10.64,-4.72,-15.09,-6.71,-11.03,-9.42,-10.44,-10.67,-8.57,-12.63,-13.3,-11.68,-8.53,-13.14,-7.6,-15.53,-11.43,-16.09,-11.52,-18.03,-12.44,-20.11,-9.3,-21.26,-11.18,-18.6,-13.99,-18.15,-8.59,-19.76,-9.38,-22.68,-11.89,-21.04,-12.95,-24.2,-21.14,-15.05,-15.52,-21.92,-23.53,-24.31,-29.94,-12.82,-28.92,-15.38,-29.69,-14.79,-32.83,-14.13,-35.51,-23.56,-37.1,-29.11,-33.8,-21.91,-39.8,-21.44,-28.24,-26.39,-38.69,-25.61,-27.49,-22.87,-33.56,-29.35,-41.01,-26.93,-31.38,-44.91,-39.44,-34.31,-37.73,-33.97,-35.44,-48.72,-30.47,-48.73,-30.54,-48.61,-30.45,-42.34,-25.6,-45.07,-36.97,-49.88,-46.62,-39.01,-28.14,-50.36,-31.17,-39.33,-49.09,-53.53,-36.98,-43.31,-41.53,-47.43,-41.41,-35.01,-44.57,-42.89,-40.2,-43.62,-53.28,-34.18,-33.39,-45.23,-47.14,-29.98,-33.93,-31.89,-39.91,-26.89,-49.2,-35.6,-46.88,-38.15,-33.9,-35.46,-40.17,-42.48,-30.42,-27.86,-29.86,-36.76,-36.91,-27.68,-44.69,-41.6,-27.14,-38.95,-39.96,-37.19,-30.44,-32.43,-27.75,-29.92,-21.62,-42.91,-31.98,-32.26,-33.27,-30.58,-36.9,-32.38,-23.39,-39.21,-28.83,-28.29,-30.31,-38.71,-36.43,-38.07,-35.26,-34.94,-32.35,-21.57,-29.31,-33.87,-35.69,-19.94,-36.3,-30,-36.53,-16.14,-26.76,-28.16,-25.04,-25.31,-33.26,-15.98,-23.58,-12.93,-32.09,-15.4,-31.48,-21.38,-19.34,-12,-27.45,-14.05,-15.16,-16,-15.63,-16.17,-17.76,-20.28,-11.27,-10.18,-7.12,-11.1,-5.93,-10.67,-3.42,-10.42,-8.21,-14.51,-7.67,-15.1,-3.72,-8.52,-2.56,-8.98,-3.53,-12.01,-3.27</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B161" t="str">
+        <v>[R_09_标记]</v>
+      </c>
+      <c r="C161" t="str">
+        <v>a: 28.7ms -77.9uv b: 62.7ms 339.8uv</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B162" t="str">
+        <v>[L_09_名字]</v>
+      </c>
+      <c r="C162" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B163" t="str">
+        <v>[L_09_放大器]</v>
+      </c>
+      <c r="C163" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B164" t="str">
+        <v>[L_09_闪光]</v>
+      </c>
+      <c r="C164" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B165" t="str">
+        <v>[L_09_闪光背景]</v>
+      </c>
+      <c r="C165" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B166" t="str">
+        <v>[L_09_采样]</v>
+      </c>
+      <c r="C166" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B167" t="str">
+        <v>[L_09_分析时间]</v>
+      </c>
+      <c r="C167" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B168" t="str">
+        <v>[L_09_数据长度]</v>
+      </c>
+      <c r="C168" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B169" t="str">
+        <v>[L_09_详细数据(uv)]</v>
+      </c>
+      <c r="C169" t="str">
+        <v>-13.37,-23.86,-14.49,-22.76,-16.61,-20.85,-19.3,-18.61,-22.03,-16.58,-24.24,-15.27,-25.5,-15.01,-25.55,-15.91,-24.45,-17.79,-22.46,-20.27,-20.03,-22.82,-17.75,-24.92,-16.13,-26.09,-15.52,-26.08,-16.15,-24.85,-17.72,-22.85,-20.01,-20.29,-22.39,-17.92,-24.92,-16.41,-26.32,-15.89,-26.35,-16.26,-26.05,-18.72,-24.51,-20.93,-23.07,-25.46,-20.91,-29.07,-20.06,-30.35,-20.96,-32.69,-26.43,-38.08,-30.53,-34.57,-30.94,-33.57,-41.43,-33.64,-41.78,-39.94,-50.74,-47.57,-56.65,-47.04,-60.06,-56.79,-59.16,-53.54,-52.48,-54.62,-56.17,-60.66,-52.17,-78.29,-60.91,-74.75,-66.03,-75.6,-67.76,-66.22,-67.08,-54.21,-59.5,-48.69,-57.87,-35.93,-54.59,-29.15,-23.28,-25.78,-21.68,-2.25,-18.59,-4.25,0.48,15.83,26.74,28.65,42.21,56.4,59.88,71.04,101.44,107.29,104.55,113.05,137.61,137.87,128.29,131.23,152.14,175.58,194.91,218.09,214.2,190.93,201.31,257.39,238.24,271.68,273.96,251.97,272.79,251.89,291.47,304.65,291.62,295.06,350.9,350.72,331.46,330,371.07,354.55,314.81,318.85,388.2,373.92,398.56,362.56,354.9,422.05,341.1,421.69,336.73,402.7,413.22,338.98,346.46,373.26,377.42,325.24,381.77,322.77,335.07,326.58,335.76,371.01,299.92,296.65,326.91,301.08,337.08,316.74,322.74,267.18,295.41,295.33,257.27,258.71,236.93,254.63,265.32,222.94,196.6,232.55,213.95,204.62,215.23,207.46,200.35,185.49,190.23,178.62,153.6,152.19,158.53,152.16,164.69,144.41,143.34,139.07,107.96,151.47,131.72,108.51,121.58,97.75,90.05,101.32,104.47,90.52,88.65,97.45,75.76,94.54,81.25,63.85,77.76,77.99,63.35,51.21,65.43,77.14,67.82,79.31,54.98,62.43,48.33,62.4,55.96,65.56,35.06,60.07,35.86,50.25,48.8,47.9,42.86,40.56,44.14,18.98,33.71,18.53,32.38,19.01,24.48,24.63,23.2,23.09,22.11,14.35,9.45,14.83,3.53,12.97,-0.36,12.41,-0.9,8.28,-1.6,2.99,-2.86,-0.87,-5.96,-6.56,-3.16,-11.35,-3.81,-14.35,-1.93,-13.94,-7.16,-14.97,-11.59,-14.54,-15.68,-14.47,-18.03,-14.57,-21.9,-12.67,-23.12,-16.17,-28.07,-18.42,-25.42,-17.62,-23.37,-23.51,-22.88,-27.52,-19.36,-27.77,-19.04,-31.11,-21.83,-32.07,-25.15,-28.51,-27.74,-26.98,-27.32,-28.57,-27.19,-28.72,-32.17,-24.83,-34.04,-26.55,-34.08,-26.82,-32.2,-27.8,-34.35,-26.34,-34.47,-31.72,-35.23,-36.11,-26.39,-33.74,-26.57,-38.3,-27.3,-43.36,-24.09,-34.15,-35.79,-33.95,-39.99,-31.06,-44.14,-29.9,-35.67,-38.32,-45.77,-39.09,-36.66,-26.38,-34.53,-41.81,-32.89,-44.88,-33.26,-51.41,-38.66,-40.16,-36.62,-44.32,-43.51,-45.31,-30.04,-45.75,-46.47,-44.44,-41.68,-48.12,-46.94,-35.9,-49.56,-40.18,-44.68,-40.98,-60.04,-46.2,-63.04,-38.68,-61.23,-51.61,-57.73,-45.46,-42.66,-47.27,-40.12,-65.91,-46.51,-55.17,-38.84,-47.95,-50.88,-55.25,-60.35,-55.38,-52.99,-56.4,-47.37,-42.57,-61.87,-54.43,-67.23,-56.67,-64.75,-53.21,-54.59,-47.51,-54.97,-52.49,-50.7,-46.67,-36.23,-58.41,-56.04,-49.35,-39.92,-46.28,-53.59,-40.92,-51.11,-44.79,-55.44,-42.54,-50.44,-49.64,-43.22,-49.6,-43.55,-45.76,-51.57,-33.57,-53.45,-36.9,-37.48,-51.02,-45.27,-48.98,-32.36,-54.39,-35.17,-50.22,-36.7,-36.37,-36.26,-45.81,-41.98,-32.74,-31.27,-35.1,-33.2,-34.75,-41.63,-24.03,-39.2,-37.09,-35.3,-39.32,-31.05,-28.89,-38.79,-32.23,-33.64,-31.91,-35.38,-38.65,-21.85,-31.95,-28.78,-41.93,-23.15,-35.36,-25.88,-29.01,-30.82,-27.93,-34.65,-27.46,-38.15,-26.39,-32.21,-27.75,-33.69,-20.18,-31.52,-24.3,-29.15,-27.84,-24.14,-30.76,-18.02,-27.42,-19.23,-27.08,-16.46,-29.73,-16.41,-20.8,-15.08,-21.65,-21.97,-16.09,-22.1,-15.2,-21.12,-11.68,-23.1,-9.92,-20.13,-12.64,-15.98,-9.82,-15.67,-12.22,-10.38,-15.83,-10.39,-18.03</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B170" t="str">
+        <v>[L_09_标记]</v>
+      </c>
+      <c r="C170" t="str">
+        <v>a: 28.7ms -75.4uv b: 62.7ms 388.2uv</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B171" t="str">
+        <v>[R_10_名字]</v>
+      </c>
+      <c r="C171" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B172" t="str">
+        <v>[R_10_放大器]</v>
+      </c>
+      <c r="C172" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B173" t="str">
+        <v>[R_10_闪光]</v>
+      </c>
+      <c r="C173" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B174" t="str">
+        <v>[R_10_闪光背景]</v>
+      </c>
+      <c r="C174" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B175" t="str">
+        <v>[R_10_采样]</v>
+      </c>
+      <c r="C175" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B176" t="str">
+        <v>[R_10_分析时间]</v>
+      </c>
+      <c r="C176" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B177" t="str">
+        <v>[R_10_数据长度]</v>
+      </c>
+      <c r="C177" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B178" t="str">
+        <v>[R_10_详细数据(uv)]</v>
+      </c>
+      <c r="C178" t="str">
+        <v>-14.46,-1.71,-16.37,-0.88,-15.82,-1.96,-12.97,-4.95,-9.35,-8.72,-5.11,-12.54,-2.12,-15.52,-0.93,-16.6,-1.94,-15.71,-5.01,-12.8,-9.46,-8.52,-12.93,-4.44,-15.04,-0.85,-15.47,0.93,-12.79,1.23,-8.49,-0.27,-2.79,-2.81,2.31,-5.1,6.31,-8.11,6.06,-9.97,3.41,-10.27,-1.48,-9.03,-8.9,-8.26,-13.29,-5.54,-18.64,-2.71,-18.19,-0.38,-14.27,0.1,-7.07,0.77,1.45,-0.21,7.97,-1.17,13.18,-2.8,13.79,-1.87,8.33,-6.02,0.15,-8.67,-10.76,-12.64,-20.52,-16.84,-30.62,-19.53,-32.75,-15.25,-27.48,-15.13,-20.79,-12.47,-9.17,-8.57,3.14,-3.03,10.66,0.16,17.36,5.45,15.27,1.35,8.86,-3.32,-7.75,-8.5,-23.43,-17.71,-34.42,-25.17,-42.18,-33.29,-43.74,-37.88,-41.19,-30.3,-26.76,-22.73,-7.93,-11.26,10.21,-1.06,18.51,15.34,27.03,16.56,22.36,16.62,16.13,12.5,-2.86,0.4,-20.33,-15.48,-32.8,-22.57,-43,-33.26,-42.87,-36.53,-37.04,-32.85,-23.32,-24.71,-3.32,-10.23,13.6,3.86,22.65,24.47,27.83,25.75,18.97,30.62,9.03,20.39,-2.46,5.35,-18.04,-11.64,-30.22,-24.11,-36.64,-38.11,-40.06,-47.37,-27.05,-37.03,-21.01,-29.87,-7.76,-15.3,2.06,2.89,7.23,13.95,8.08,22.06,8,15.21,-2.27,11.31,-10.97,-2.25,-19.15,-18.9,-27.09,-32.61,-26.69,-38.29,-28.36,-41.02,-24.74,-38.27,-19.13,-30.57,-15.49,-17.6,-11.38,-4.6,-8.39,4.76,-7.76,6.55,-7.8,9.13,-8.99,0.11,-11.38,-8.54,-13.23,-18.39,-14,-27.32,-14.72,-28.94,-15.35,-28.27,-16.26,-25.25,-15.1,-17.3,-14.43,-9.34,-14.24,-1.47,-12.86,3.27,-11,3.86,-9.38,1.77,-7.55,-4.85,-6.07,-11.11,-4.68,-16.72,-4.4,-19.85,-5.56,-20.19,-7.39,-18.79,-10.61,-14.8,-14.2,-9.36,-16.94,-5.21,-18.44,-2.93,-17.99,-3.37,-16.13,-6.56,-13.45,-10.93,-9.99,-15.9,-7.73,-20.26,-6.89,-22.71,-7.99,-23,-10.99,-20.81,-15.19,-17.45,-19.63,-13.89,-23.15,-11.13,-25.3,-10.01,-25.27,-11.08,-23.14,-14.05,-19.67,-18.17,-15.76,-22.09,-12.36,-25.07,-10.63,-26.06,-10.92,-24.83,-13.15,-21.72,-16.73,-17.53,-20.53,-13.41,-23.6,-10.42,-24.92,-9.29,-24.08,-10.27,-21.22,-12.96,-17.01,-16.53,-12.51,-19.87,-8.83,-21.97,-6.87,-22.1,-7.09,-20.16,-9.31,-16.58,-12.83,-12.27,-16.62,-8.35,-19.57,-5.83,-20.83,-5.39,-20,-7.12,-17.32,-10.53,-13.52,-14.7,-9.66,-18.51,-6.84,-20.94,-5.9,-21.41,-7.17,-19.84,-10.37,-16.78,-14.74,-13.17,-19.18,-10.13,-22.6,-8.62,-24.19,-9.21,-23.65,-11.87,-21.28,-16.01,-17.87,-20.64,-14.52,-24.63,-12.28,-27.02,-11.9,-27.28,-13.62,-25.46,-17.08,-22.17,-21.43,-18.41,-25.56,-15.31,-28.41,-13.78,-29.24,-14.28,-27.87,-16.72,-24.7,-20.43,-20.61,-24.39,-16.7,-27.48,-14.02,-28.81,-13.27,-27.96,-14.59,-25.1,-17.53,-20.93,-21.22,-16.52,-24.52,-12.97,-26.44,-11.17,-26.34,-11.5,-24.14,-13.76,-20.34,-17.23,-15.88,-20.85,-11.89,-23.53,-9.39,-24.44,-8.98,-23.27,-10.71,-20.28,-14.06,-16.24,-18.05,-12.24,-21.58,-9.37,-23.66,-8.42,-23.75,-9.69,-21.84,-12.86,-18.52,-17.12,-14.76,-21.38,-11.7,-24.54,-10.26,-25.85,-10.96,-25.07,-13.72,-22.53,-17.93,-19.07,-22.56,-15.79,-26.47,-13.74,-28.74,-13.62,-28.89,-15.62,-27.02,-19.32,-23.78,-23.84,-20.19,-28.05,-17.36,-30.92,-16.18,-31.74,-17.06,-30.38,-19.84,-27.29,-23.82,-23.36,-27.94,-19.71,-31.09,-17.37,-32.42,-16.98,-31.54,-18.63,-28.68,-21.82,-24.57,-25.63,-20.29,-28.95,-16.96,-30.78,-15.39,-30.53,-15.94,-28.17,-18.34,-24.25,-21.84,-19.74,-25.37,-15.79,-27.83,-13.36,-28.46,-13.03,-26.98,-14.79,-23.7,-18.08,-19.46,-21.9,-15.33,-25.15,-12.42,-26.88,-11.47,-26.58,-12.73,-24.32,-15.84,-20.72,-19.96,-16.8,-23.98,-13.66,-26.83,-12.24</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B179" t="str">
+        <v>[R_10_标记]</v>
+      </c>
+      <c r="C179" t="str">
+        <v>71.9uv</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B180" t="str">
+        <v>[L_10_名字]</v>
+      </c>
+      <c r="C180" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B181" t="str">
+        <v>[L_10_放大器]</v>
+      </c>
+      <c r="C181" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B182" t="str">
+        <v>[L_10_闪光]</v>
+      </c>
+      <c r="C182" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B183" t="str">
+        <v>[L_10_闪光背景]</v>
+      </c>
+      <c r="C183" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B184" t="str">
+        <v>[L_10_采样]</v>
+      </c>
+      <c r="C184" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B185" t="str">
+        <v>[L_10_分析时间]</v>
+      </c>
+      <c r="C185" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B186" t="str">
+        <v>[L_10_数据长度]</v>
+      </c>
+      <c r="C186" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B187" t="str">
+        <v>[L_10_详细数据(uv)]</v>
+      </c>
+      <c r="C187" t="str">
+        <v>-34.59,-21.78,-33.23,-23.43,-31.54,-25.48,-29.84,-28.08,-28.09,-31.02,-26.77,-33.75,-25.59,-35.94,-24.15,-37.64,-23.04,-38.64,-22.48,-38.17,-20.83,-36.55,-19.84,-33.98,-18.78,-30.67,-18.26,-26.47,-19.29,-24.07,-19.65,-20.99,-23.02,-19.84,-25.62,-19.33,-29.46,-19.32,-32.98,-19.42,-35.2,-20.98,-37.88,-20.71,-35.28,-18.03,-33.07,-16.54,-27.85,-13.31,-22.2,-10.81,-14.7,-8.05,-11.05,-10.03,-6.51,-12.69,-8.54,-17.57,-10.13,-24.6,-14.88,-31.87,-19.99,-40.63,-25.95,-42.1,-30.43,-44.74,-30.13,-41.31,-24.69,-35.44,-19.78,-24.8,-14.85,-14.98,-6.79,-2.55,-7.72,0.82,-8.45,0.23,-13.93,-4.56,-21.43,-12.36,-33.89,-23.34,-46.19,-34.42,-53.3,-38.45,-58.12,-40.39,-54.8,-46.22,-46.68,-35.56,-34.49,-23.41,-18.36,-13.27,-3.45,-5.3,4.17,3.55,16.48,-5.74,9.8,-11.7,-3.04,-24.42,-14.25,-37.07,-27.08,-50.17,-37.8,-60.67,-52.01,-61.14,-47.16,-48.45,-37.4,-37.93,-28.41,-19.3,-13.94,0.94,-0.4,14.85,3.96,27.52,14.13,24.43,-1.74,16.08,-7.18,1.64,-22.35,-14.38,-34.14,-25.89,-49.32,-40.87,-47.89,-42.24,-47.33,-37.46,-35.24,-32.68,-23.67,-23.2,-9.19,-10.66,6.77,-5.54,12.59,-0.07,14.54,1.02,12.33,-5.46,4.42,-18.03,-8.68,-28.48,-21.86,-38.57,-30.37,-38.88,-36.65,-42.71,-43.26,-37.97,-37.22,-29.19,-32.88,-19.09,-26.81,-8.48,-21.13,-1.03,-14.82,4.42,-11.78,0.39,-16,-4.63,-19.74,-9.3,-24.02,-17.43,-28.41,-25.26,-31.7,-29.97,-29.45,-34.03,-28.35,-31.8,-23.94,-31.47,-16.64,-27.39,-10.65,-23.82,-5.77,-20.12,-2.16,-17.24,-1.38,-17.57,-2.28,-15.92,-5.47,-16.22,-10.07,-16.58,-14.25,-16.28,-17.9,-15.13,-20.93,-13.02,-21.72,-11.21,-22.18,-8.19,-22.31,-5.62,-21.02,-3.74,-19.69,-3.2,-18.35,-3.21,-16.88,-4.6,-15.7,-7.19,-14.93,-10.52,-13.76,-13.77,-12.71,-17.07,-11.7,-19.86,-10.38,-21.89,-9.42,-23.8,-8.46,-24.52,-8.23,-24.78,-8.31,-24.4,-9.02,-23.58,-10.42,-22.33,-12.36,-20.78,-14.59,-19.05,-17.12,-17.3,-19.68,-15.49,-22.01,-13.74,-23.97,-12.16,-25.44,-10.93,-26.27,-10.05,-26.37,-9.67,-25.88,-9.76,-24.69,-10.3,-22.95,-11.29,-20.77,-12.64,-18.26,-14.2,-15.56,-15.85,-12.82,-17.42,-10.2,-18.77,-7.86,-19.77,-5.89,-20.31,-4.43,-20.33,-3.54,-19.79,-3.23,-18.71,-3.53,-17.14,-4.39,-15.17,-5.71,-12.9,-7.39,-10.47,-9.29,-8.05,-11.26,-5.78,-13.16,-3.81,-14.85,-2.28,-16.19,-1.28,-17.1,-0.88,-17.52,-1.12,-17.42,-2,-16.83,-3.46,-15.78,-5.41,-14.39,-7.73,-12.75,-10.29,-11,-12.92,-9.29,-15.46,-7.75,-17.75,-6.51,-19.66,-5.67,-21.07,-5.32,-21.89,-5.5,-22.1,-6.2,-21.69,-7.4,-20.69,-9.01,-19.2,-10.94,-17.31,-13.06,-15.17,-15.21,-12.91,-17.25,-10.7,-19.02,-8.67,-20.39,-6.95,-21.26,-5.66,-21.53,-4.85,-21.18,-4.57,-20.21,-4.81,-18.65,-5.52,-16.58,-6.62,-14.13,-8.01,-11.42,-9.56,-8.62,-11.13,-5.89,-12.58,-3.38,-13.77,-1.25,-14.6,0.39,-14.97,1.46,-14.84,1.9,-14.19,1.7,-13.05,0.9,-11.47,-0.43,-9.56,-2.19,-7.43,-4.24,-5.23,-6.44,-3.11,-8.64,-1.21,-10.67,0.32,-12.41,1.38,-13.75,1.88,-14.6,1.77,-14.92,1.04,-14.71,-0.28,-13.99,-2.1,-12.83,-4.33,-11.35,-6.83,-9.65,-9.44,-7.89,-12.01,-6.19,-14.37,-4.71,-16.38,-3.55,-17.91,-2.81,-18.86,-2.55,-19.19,-2.81,-18.87,-3.56,-17.93,-4.76,-16.44,-6.32,-14.48,-8.12,-12.21,-10.03,-9.74,-11.91,-7.26,-13.6,-4.9,-14.97,-2.82,-15.89,-1.13,-16.29,0.08,-16.1,0.75,-15.31,0.86,-13.94,0.45,-12.05,-0.44,-9.75,-1.71,-7.16,-3.23,-4.43,-4.87,-1.73,-6.49,0.79,-7.95,2.98,-9.12,4.7,-9.91,5.87,-10.23,6.4,-10.04,6.29,-9.36,5.54,-8.22</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B188" t="str">
+        <v>[L_10_标记]</v>
+      </c>
+      <c r="C188" t="str">
+        <v>71uv</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B189" t="str">
+        <v>[R_11_名字]</v>
+      </c>
+      <c r="C189" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B190" t="str">
+        <v>[R_11_放大器]</v>
+      </c>
+      <c r="C190" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B191" t="str">
+        <v>[R_11_闪光]</v>
+      </c>
+      <c r="C191" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B192" t="str">
+        <v>[R_11_闪光背景]</v>
+      </c>
+      <c r="C192" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B193" t="str">
+        <v>[R_11_采样]</v>
+      </c>
+      <c r="C193" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B194" t="str">
+        <v>[R_11_分析时间]</v>
+      </c>
+      <c r="C194" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B195" t="str">
+        <v>[R_11_数据长度]</v>
+      </c>
+      <c r="C195" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B196" t="str">
+        <v>[R_11_详细数据(uv)]</v>
+      </c>
+      <c r="C196" t="str">
+        <v>1.48,10.16,1.01,7.54,6.69,2.07,10.92,1.88,8.19,7.7,2.82,11.82,2.88,8.93,8.8,3.63,12.75,3.9,9.68,9.88,4.42,13.62,4.86,10.33,10.84,5.08,14.34,5.66,10.81,11.61,5.54,14.84,6.23,11.03,12.12,5.74,15.05,6.53,10.97,12.34,5.64,14.95,6.51,10.6,12.23,5.24,14.5,6.13,9.86,11.69,4.37,13.7,5.33,8.66,10.65,3.07,11.98,4.13,6.52,8.94,1.11,9.47,1.26,3.62,6.15,-2.1,5.18,-2.21,-0.65,-0.21,-9.58,-1.6,-10.65,-9.65,-7.93,-17.32,-10.38,-20.4,-17.21,-20.55,-34.51,-27.67,-28.44,-34.32,-37.17,-42.31,-34.78,-41.83,-54.55,-44.93,-62.95,-47.2,-63.52,-64.6,-50.44,-64.3,-46.93,-52.02,-61.92,-50.88,-65.99,-60.47,-53.64,-45.76,-34.2,-40.27,-24.78,-27.04,-24.63,-20.36,-11.88,4.92,2.8,22.07,13.82,24.44,37.5,54.84,48.84,66.79,70.38,85.41,107.56,109.42,126.62,140.4,165.68,138.22,170.96,158.41,201.57,201.03,200.95,199.65,229.25,214.17,253.06,280.09,266.09,323.83,321.01,302.18,305.05,350.43,354.61,348.05,345.28,323.59,372.58,391,378.06,390.02,423.34,398.24,415.88,443.8,403.82,461.55,390.49,415.62,454.9,453.38,439.01,396.37,475.72,397.18,407.99,416.11,398.75,392.41,377.29,380.4,433.63,410.25,391.31,376.74,366.98,363.43,412.65,402.37,364.18,329.08,357.87,298.89,321.98,344.88,308.09,325.76,294.6,319.4,260.46,256.69,269.18,250.45,268.93,260.05,222.83,216.31,221.47,229.36,206.8,191.17,197.65,183.83,199.66,165.18,169.06,176.76,164.88,146.18,154.69,159.69,158.54,132.33,146.81,143.17,141.86,150.04,137.19,140.2,114.76,128.14,122.55,110.66,105.24,92.37,95.89,109.78,102.74,107.75,86.37,84.32,108.88,89.45,100.09,70.83,84.74,74.73,82.74,96.63,90.65,68.94,91.57,58.01,87.22,65,69.53,55.93,47.84,60.26,58.83,63.22,65.78,44.03,55.62,55.05,38.09,57.69,43.21,50.27,34.27,30.83,40.76,25.32,32.96,31.21,28.2,35.67,21.62,29.02,23.29,25.81,28.31,15.02,26.49,18.18,19.95,20.09,13.31,18,11.71,13.87,20.41,9.1,18.88,10.09,9.55,14.6,5.93,17.46,8.64,8.85,14.87,1.96,13.87,5.42,5.67,9.51,3.41,9.54,1.65,1.77,9.02,2.61,7.34,0.13,-0.78,6.92,-6,1.51,-1.93,-6.39,6.74,-7.45,2.36,-2.65,-6.6,5.09,-10.24,-0.57,-7.35,-3.75,3.68,-8.65,0.64,-10.2,-12.97,-9.33,-17.48,-13.8,-10.22,-16.96,-9.26,-21.74,-11.91,-13.24,-22.05,-13.35,-15.61,-6.75,-19.02,-19.85,-17.95,-20.14,-13.96,-14.19,-24.4,-12.77,-17.08,-18.9,-28.19,-27.42,-19.17,-23.52,-13.25,-28.84,-23.62,-14.35,-34.1,-23.18,-19.49,-21.39,-9.28,-19.03,-17.21,-17.79,-29.93,-22.22,-37.8,-17.65,-26.38,-24.99,-17.97,-21.43,-29.93,-23.67,-25.91,-12.43,-36.81,-17.1,-19.02,-21.06,-29.73,-22.01,-31.12,-32.35,-31.98,-24.69,-39.26,-26.87,-17.21,-30.15,-29.91,-31.2,-17.89,-17.69,-27,-31.16,-38.49,-38.12,-18,-35.69,-30.91,-43.02,-34.61,-18.41,-28.01,-20.1,-27.21,-33.64,-19.55,-33.75,-24.28,-37.76,-21.05,-36.2,-36.75,-13.74,-34.08,-20.26,-15.26,-35.79,-24.89,-36.69,-23.06,-14.77,-41.99,-23.47,-27.43,-18.68,-32.04,-30.73,-26.33,-20.52,-29.07,-17.48,-21.95,-10.65,-36.5,-23.62,-24.85,-25.44,-21.08,-19.46,-16.81,-9.09,-27.64,-13.27,-14.88,-23.61,-13.2,-20.35,-16.45,-8.89,-11.97,-16.77,-13.74,-12.91,-20.48,-14.13,-10.37,-13.32,-11.3,-14.3,-14.49,-5.72,-11.95,-3.96,-12.95,-10.41,-1.51,-13.83,2.69,0.37,-4.11,5.81,-2.93,1.6,2.98,-2.47,2.92,-5.2,6,-4.32,-0.73,1.69,-3.06,1.88,3.9,1.53,7.46,1.37,5.21,5.62,-1.29,7.86,0.37,6.2,6.87,2.39</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B197" t="str">
+        <v>[R_11_标记]</v>
+      </c>
+      <c r="C197" t="str">
+        <v>a: 32.7ms -102.7uv b: 69.7ms 518.7uv</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B198" t="str">
+        <v>[L_11_名字]</v>
+      </c>
+      <c r="C198" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B199" t="str">
+        <v>[L_11_放大器]</v>
+      </c>
+      <c r="C199" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B200" t="str">
+        <v>[L_11_闪光]</v>
+      </c>
+      <c r="C200" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B201" t="str">
+        <v>[L_11_闪光背景]</v>
+      </c>
+      <c r="C201" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B202" t="str">
+        <v>[L_11_采样]</v>
+      </c>
+      <c r="C202" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B203" t="str">
+        <v>[L_11_分析时间]</v>
+      </c>
+      <c r="C203" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B204" t="str">
+        <v>[L_11_数据长度]</v>
+      </c>
+      <c r="C204" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B205" t="str">
+        <v>[L_11_详细数据(uv)]</v>
+      </c>
+      <c r="C205" t="str">
+        <v>15.64,-6.23,10.99,3.22,0.26,13.96,-6.29,16.38,-2.15,8.7,9.3,-1.46,17.96,-4.11,16.43,3.79,6.67,15.47,-1.62,20.97,-0.06,15.47,10.17,4.85,20.48,-0.43,21.87,4.74,12.55,16.13,2.54,22.68,0.82,19.37,8.67,8,18.08,-1.4,22.02,-0.05,13.88,8.61,-0.08,15.65,-6.9,16.03,-0.71,0.97,9,-7.51,9.57,-11.28,5.09,-10.27,-16.2,-4.91,-25.74,-8.12,-18.13,-16.96,-15.76,-26.03,-15.57,-31.6,-21.01,-31.52,-19.31,-28.01,-41.37,-11.43,-40.2,-25.32,-36.84,-43.14,-30.34,-29.62,-24.31,-19.67,-33.21,-26.94,-35.52,0.78,-15.03,-0.09,-12.64,8.22,11.33,11.89,29.75,23.63,39.38,41.64,30.25,61.61,65.53,91.16,62.02,78.55,95.42,99.19,126.5,122.74,156.19,160.21,128.4,174.35,177,202.54,172.4,220.72,208.77,222.96,257.92,237.73,289.89,277.21,314.07,285.49,304.32,285.15,341.45,296.87,326.82,344.06,363.55,336.03,393.89,347.79,357.46,413.96,372.98,426.28,379.95,457.67,368.69,420.29,420.45,417.88,418.58,435.74,446.3,433,401.41,404.26,459.72,468.55,446.23,464.43,417.69,416.2,452.81,442.41,397.97,429.68,409.39,445.81,422.56,383.6,413.21,430.54,379.77,399.67,445.51,384.73,371.84,337.1,369.65,380.81,331.68,380,333.5,321.59,339.35,357.29,355.37,297.74,310.64,325.44,293.98,272.11,268.36,321.32,257.82,261.61,240.71,267.83,259.76,256.93,230.88,206.17,228.27,228.98,236.3,217.62,200.01,228.41,192.95,219.57,190.83,163.36,190.42,187.63,176.6,179.22,160.55,160.63,163.07,181.37,151.9,172.34,127.85,138.06,136.04,140.49,139.35,130.08,108.45,138.22,120.12,108.09,96.15,115.28,96.05,89.8,111.81,70.07,93.64,76.12,91.8,95.28,77.47,84.65,59.21,83.22,66.22,61.03,76.65,49.73,57.68,46.05,51.24,40.59,32.27,58.2,26.64,42.75,26.03,37.35,38.97,22.32,40.4,12.7,29.56,21.77,17.41,25.02,5.9,26.96,4.72,14.02,11.2,4.44,23.23,-1.06,15.41,1.11,3.67,9.09,-3.78,15.55,-8.89,11.68,4.14,-4.76,11.16,-9.11,14.58,-7.86,6.08,2.23,-7.72,14.84,-13.99,6.48,-2.5,-4.21,5.8,-9.55,13.61,-6.23,7.38,-1.54,-5.84,12.63,-14.29,7.73,-10.04,-4.05,4.66,-14.97,4.92,-10.11,3.13,-9.16,-7.09,1.87,-13.47,11.49,-14.48,-5.82,-2.96,-17.78,9.02,-19.37,3.31,-12.49,-7.98,-1.9,-18.46,4.63,-28.3,-11.32,-21.5,-22.61,-6.53,-34.9,-8.05,-26.07,-19.58,-25.03,-30.85,-6.97,-40.7,-22.38,-33.1,-34.11,-20.69,-36.7,-19.35,-37.94,-21.37,-27.79,-29.99,-15.66,-35.32,-16.7,-33.27,-31.62,-33.59,-51.81,-28.6,-38.26,-31.29,-38.38,-32.43,-33.76,-50.31,-13.35,-49.61,-32.2,-37.07,-48.67,-32.22,-53.25,-30.7,-31.25,-45.74,-26.57,-44.57,-20.15,-48.82,-31.97,-42.61,-38.95,-31.55,-38.05,-26.37,-48.84,-39.6,-37.43,-32.26,-18.48,-50.39,-19.5,-26.69,-27.73,-23.22,-32.79,-17.36,-27.09,-21.09,-38.65,-29.08,-15.35,-44.22,-17.12,-42.95,-15.18,-16.04,-32.8,-5.67,-33.96,-28.22,-28.58,-39.42,-16.72,-39.48,-11.55,-34.54,-27.95,-36.25,-29.95,-17.33,-29.02,-11.72,-29.1,-30.14,-17.62,-30.31,-14.99,-30.69,-13.95,-37.87,-25.56,-25.26,-35.38,-18.47,-44.08,-17.71,-33.11,-31.29,-19.98,-45.59,-17.05,-37.98,-28.71,-18.92,-32.34,-8.86,-27.02,-15.55,-16.4,-23.64,-13.06,-36.25,-8.28,-26.16,-13.04,-17.18,-27.02,-7.45,-22.9,-3.72,-20.12,-11.88,-9.99,-20.95,0.95,-25.14,-7.09,-7.52,-18.72,5.05,-12.2,3.34,-15.13,-1.37,-1.55,-8.82,5.52,-10.25,8.95,-1.15,-1.76,10.89,-9.4,13.71,-4.54,10.69,9.14,-4.17,17.95,-2.46,18.4,3.87,5.18,16.42,-5.7,16.36,1.09,12.5,5.66,2.61,19.74,-4.58,17.74,1.32,8.56,11.27,-3.17</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B206" t="str">
+        <v>[L_11_标记]</v>
+      </c>
+      <c r="C206" t="str">
+        <v>a: 32.6ms -103.7uv b: 69.9ms 455.8uv</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B207" t="str">
+        <v>[R_12_名字]</v>
+      </c>
+      <c r="C207" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B208" t="str">
+        <v>[R_12_放大器]</v>
+      </c>
+      <c r="C208" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B209" t="str">
+        <v>[R_12_闪光]</v>
+      </c>
+      <c r="C209" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B210" t="str">
+        <v>[R_12_闪光背景]</v>
+      </c>
+      <c r="C210" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B211" t="str">
+        <v>[R_12_采样]</v>
+      </c>
+      <c r="C211" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B212" t="str">
+        <v>[R_12_分析时间]</v>
+      </c>
+      <c r="C212" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B213" t="str">
+        <v>[R_12_数据长度]</v>
+      </c>
+      <c r="C213" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B214" t="str">
+        <v>[R_12_详细数据(uv)]</v>
+      </c>
+      <c r="C214" t="str">
+        <v>-19.27,-29.01,-16.1,-19.47,-28.1,-14.84,-19.85,-27.24,-13.84,-20.37,-26.34,-13,-20.97,-25.31,-12.22,-21.4,-24.22,-11.51,-21.69,-22.86,-10.76,-21.82,-21.46,-10.2,-22,-20.35,-10.05,-22.97,-19.53,-10.79,-24.3,-19.68,-12.68,-26.44,-20.6,-15,-28.79,-21.52,-16.91,-30.07,-21.84,-18.38,-30.55,-20.13,-18.04,-29.37,-17.24,-17,-27.17,-14.32,-15.22,-24.76,-13.55,-17.22,-25.41,-14.2,-20.24,-29.59,-18.03,-26.46,-34.41,-24.15,-33.14,-39.1,-26.24,-37.13,-40.03,-26.1,-33.92,-35.33,-19.68,-28.28,-24.56,-9.95,-20.98,-14.68,-2.75,-15.25,-9.45,-1.53,-12.11,-13.52,-7,-23.22,-20.91,-18.99,-37.77,-33.25,-32.41,-50.33,-40.31,-40.25,-51.73,-33.61,-35.35,-41.15,-24.03,-17.37,-21.5,-4.51,0.1,-4.92,15.74,15.13,5.35,19.77,5.75,-0.43,3.57,-5.12,-20.07,-15.01,-30.82,-42.75,-35.89,-47.15,-55.17,-40.1,-50.39,-53.83,-39.25,-44.55,-35.35,-14.83,-19.88,-11.46,5.26,1.51,5.24,13.61,5.71,13.69,19.88,-5.48,-4.6,-2.96,-23.64,-22.71,-23.65,-43.16,-42.75,-44.25,-59.58,-48.04,-45.78,-60.81,-38.96,-35.24,-40.93,-25.17,-19.51,-23.06,-7.61,-3.95,-13.6,2.03,1.43,-6.7,5.29,-4.73,-13.19,-7.88,-18.33,-28.61,-20.01,-33.84,-38.25,-27.45,-40.99,-41.77,-31.76,-38.97,-35.42,-22.49,-32.65,-25.92,-12.79,-21.83,-15.59,-3.88,-16.03,-8.17,-0.48,-13.19,-7.86,-2.71,-17.57,-12.3,-8.49,-23.54,-16.21,-14.44,-28.34,-19.15,-16.59,-29.87,-17.07,-17.84,-27.28,-14.48,-15.81,-25.11,-11.4,-13.52,-22.36,-8.32,-13.3,-21.06,-7.23,-14.41,-20.81,-8.1,-16.51,-22.33,-9.8,-19.44,-23.65,-11.48,-22.12,-24.27,-12.63,-23.77,-24.31,-13.15,-25.14,-23.71,-13.47,-25.89,-22.95,-13.66,-26.6,-22.06,-14.12,-27.36,-21.46,-14.85,-28.31,-20.89,-15.89,-29.09,-20.38,-16.86,-29.63,-19.68,-17.69,-29.82,-18.76,-18.32,-29.64,-17.64,-18.81,-29.08,-16.41,-19.15,-28.28,-15.11,-19.42,-27.29,-13.86,-19.65,-26.13,-12.65,-19.88,-24.88,-11.53,-20.07,-23.5,-10.53,-20.23,-22.06,-9.66,-20.39,-20.58,-8.95,-20.55,-19.11,-8.44,-20.72,-17.69,-8.15,-20.94,-16.36,-8.11,-21.21,-15.16,-8.32,-21.53,-14.1,-8.79,-21.91,-13.21,-9.51,-22.32,-12.5,-10.46,-22.76,-11.97,-11.62,-23.22,-11.61,-12.95,-23.66,-11.41,-14.42,-24.07,-11.37,-15.98,-24.41,-11.45,-17.6,-24.67,-11.64,-19.22,-24.81,-11.92,-20.8,-24.82,-12.25,-22.29,-24.67,-12.61,-23.65,-24.35,-12.99,-24.84,-23.84,-13.35,-25.83,-23.14,-13.68,-26.59,-22.26,-13.97,-27.11,-21.2,-14.22,-27.39,-19.99,-14.43,-27.41,-18.64,-14.59,-27.2,-17.2,-14.72,-26.76,-15.7,-14.84,-26.12,-14.17,-14.94,-25.3,-12.66,-15.07,-24.35,-11.21,-15.22,-23.29,-9.87,-15.43,-22.16,-8.68,-15.7,-21,-7.68,-16.06,-19.85,-6.89,-16.51,-18.73,-6.34,-17.05,-17.67,-6.06,-17.69,-16.71,-6.04,-18.42,-15.84,-6.3,-19.22,-15.1,-6.82,-20.08,-14.47,-7.58,-20.98,-13.96,-8.57,-21.89,-13.57,-9.74,-22.77,-13.27,-11.07,-23.6,-13.06,-12.52,-24.33,-12.92,-14.02,-24.94,-12.82,-15.56,-25.39,-12.74,-17.06,-25.67,-12.68,-18.5,-25.73,-12.61,-19.84,-25.57,-12.51,-21.04,-25.18,-12.38,-22.07,-24.55,-12.22,-22.9,-23.7,-12.01,-23.54,-22.63,-11.78,-23.97,-21.37,-11.53,-24.18,-19.94,-11.27,-24.2,-18.38,-11.02,-24.04,-16.74,-10.8,-23.71,-15.06,-10.64,-23.24,-13.37,-10.57,-22.67,-11.74,-10.59,-22.01,-10.21,-10.73,-21.3,-8.81,-11.01,-20.56,-7.59,-11.44,-19.84,-6.58,-12.02,-19.13,-5.81,-12.75,-18.47,-5.29,-13.63,-17.87,-5.03,-14.65,-17.34,-5.04,-15.77,-16.87,-5.3,-16.98,-16.46,-5.81,-18.25,-16.11,-6.53,-19.53,-15.81,-7.44,-20.79,-15.53,-8.5,-21.98,-15.27,-9.67,-23.07,-15,-10.92,-24.02,-14.7,-12.21,-24.79,-14.37,-13.48,-25.35,-13.99</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B215" t="str">
+        <v>[R_12_标记]</v>
+      </c>
+      <c r="C215" t="str">
+        <v>75.3uv</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B216" t="str">
+        <v>[L_12_名字]</v>
+      </c>
+      <c r="C216" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B217" t="str">
+        <v>[L_12_放大器]</v>
+      </c>
+      <c r="C217" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B218" t="str">
+        <v>[L_12_闪光]</v>
+      </c>
+      <c r="C218" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B219" t="str">
+        <v>[L_12_闪光背景]</v>
+      </c>
+      <c r="C219" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B220" t="str">
+        <v>[L_12_采样]</v>
+      </c>
+      <c r="C220" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B221" t="str">
+        <v>[L_12_分析时间]</v>
+      </c>
+      <c r="C221" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B222" t="str">
+        <v>[L_12_数据长度]</v>
+      </c>
+      <c r="C222" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B223" t="str">
+        <v>[L_12_详细数据(uv)]</v>
+      </c>
+      <c r="C223" t="str">
+        <v>8.23,7.58,0.87,10.64,5.29,2.98,11.85,3.25,5.93,11.58,2.13,9.09,10.1,2.35,11.81,7.9,4.04,13.33,5.54,6.38,13.19,3.54,9.02,11.38,2.59,11.24,8.55,3,12.41,5.46,4.93,12.74,3.4,7.69,11.86,2.77,10.94,10.24,3.67,13.38,7.79,5.41,14.01,5,7.41,12.21,1.81,8.08,7.96,-0.53,8.09,2.62,-2.25,7.18,-0.94,-0.95,5.6,-3.61,2.56,5.82,-1.84,7.97,6.51,2.41,12.62,5.87,5.8,15.01,5.47,9.26,11.88,1.72,8.71,5.97,-2.6,5.21,-2.34,-8.36,-1.57,-10.12,-8.06,-1.32,-11.54,-2.84,-0.44,-7.01,6.36,5.29,4.76,16.9,12.24,17.42,25.5,17.25,22.43,25.99,12.66,23.38,14.38,6.71,11,-0.07,-7.01,-2.84,-14.5,-15.56,-11.83,-22.72,-14.96,-8.23,-12.07,2.52,-0.24,4.33,18.12,16.89,22.9,35.54,24.55,36.19,34.88,29.91,35.52,28.43,19.66,21.77,5.17,-1.75,-0.11,-20.47,-21.08,-19.7,-26.03,-22.17,-29.04,-25,-11.98,-13.73,-7.6,7.56,6.39,16.29,25.78,26.46,33.25,43.55,34.55,42.49,35.72,19.73,27.39,10.06,5.33,2.79,-12.71,-11.51,-15.16,-30.53,-25.12,-26.59,-29.1,-23.5,-19.58,-13.11,-1.66,-6.22,6.82,15.56,15.42,26.18,30.72,26.73,35.37,27.92,20.09,26.39,16.38,12.76,11.76,-2.49,-0.39,-4.07,-13.87,-9.82,-17.98,-20.57,-9.23,-14.38,-10.62,-2.24,-5.12,5.17,9.56,5.87,18.32,16.03,15.51,25.73,15.23,16.97,21.65,13.08,17,14.85,4.06,10.52,4.58,-1.37,5.57,-2.88,-3.19,2.51,-5.37,-0.16,4.66,-3.19,5.38,5.88,0.83,11.55,6.92,5.94,14.08,5.45,8.32,12.76,4.05,10.16,9.13,0.46,9.12,3.32,-0.89,7.36,-1.58,-0.59,5.57,-4.76,1.51,3.4,-4.6,4.43,1.73,-2.83,7.09,0.08,0.36,7.86,-1.44,3.51,6.73,-2.39,5.98,4.27,-2.03,7.44,1.19,-0.57,7.72,-1.33,1.96,6.84,-2.53,4.94,5.11,-2.1,7.59,3.03,0.01,9.25,1.15,3.07,9.45,0.04,6.42,8.23,0.06,9.24,6.03,1.42,10.96,3.64,3.78,11.17,1.76,6.68,9.95,1,9.4,7.68,1.58,11.21,4.97,3.39,11.65,2.55,5.9,10.56,1.04,8.41,8.2,0.81,10.18,5.14,1.84,10.69,2.14,3.8,9.71,-0.08,6.05,7.39,-1.03,7.89,4.27,-0.57,8.69,1.04,1.05,8.13,-1.53,3.28,6.23,-2.88,5.41,3.41,-2.74,6.76,0.32,-1.23,6.9,-2.28,1.15,5.71,-3.75,3.73,3.48,-3.73,5.79,0.79,-2.23,6.76,-1.63,0.36,6.41,-3.11,3.37,4.88,-3.19,6.06,2.64,-1.78,7.78,0.37,0.82,8.15,-1.21,4.02,7.18,-1.58,7.06,5.24,-0.53,9.23,2.95,1.76,10.05,1.04,4.78,9.4,0.11,7.8,7.54,0.49,10.09,5.03,2.14,11.08,2.6,4.66,10.54,0.93,7.38,8.63,0.46,9.57,5.84,1.31,10.61,2.89,3.19,10.17,0.5,5.54,8.28,-0.75,7.63,5.37,-0.63,8.81,2.12,0.72,8.63,-0.73,2.82,7.04,-2.51,4.98,4.34,-2.87,6.52,1.15,-1.82,6.9,-1.79,0.25,5.93,-3.78,2.7,3.78,-4.34,4.8,0.98,-3.4,5.95,-1.76,-1.22,5.81,-3.72,1.59,4.41,-4.36,4.31,2.17,-3.47,6.23,-0.27,-1.25,6.9,-2.18,1.79,6.23,-2.97,4.92,4.48,-2.33,7.39,2.23,-0.32,8.65,0.19,2.62,8.47,-0.98,5.81,7,-0.86,8.49,4.73,0.59,10.03,2.35,3.08,10.07,0.57,5.98,8.67,-0.09,8.56,6.23,0.56,10.13,3.4,2.36,10.26,0.94,4.79,8.88,-0.54,7.15,6.31,-0.71,8.72,3.16,0.41,9.01,0.18,2.4,7.82,-1.94,4.62,5.37,-2.73,6.36,2.19,-2.11,7.03,-0.97,-0.36,6.33</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B224" t="str">
+        <v>[L_12_标记]</v>
+      </c>
+      <c r="C224" t="str">
+        <v>70.6uv</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B225" t="str">
+        <v>[R_13_名字]</v>
+      </c>
+      <c r="C225" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B226" t="str">
+        <v>[R_13_放大器]</v>
+      </c>
+      <c r="C226" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B227" t="str">
+        <v>[R_13_闪光]</v>
+      </c>
+      <c r="C227" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B228" t="str">
+        <v>[R_13_闪光背景]</v>
+      </c>
+      <c r="C228" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B229" t="str">
+        <v>[R_13_采样]</v>
+      </c>
+      <c r="C229" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B230" t="str">
+        <v>[R_13_分析时间]</v>
+      </c>
+      <c r="C230" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B231" t="str">
+        <v>[R_13_数据长度]</v>
+      </c>
+      <c r="C231" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B232" t="str">
+        <v>[R_13_详细数据(uv)]</v>
+      </c>
+      <c r="C232" t="str">
+        <v>-16.19,-6.73,-12.64,-19.6,-10.82,-7.13,-17.25,-16.94,-6.92,-11.12,-19.56,-12.16,-6.71,-16.38,-18.27,-8.09,-10.41,-19.98,-14.28,-7.29,-16.11,-20.1,-10.2,-10.51,-20.82,-17.03,-8.79,-16.42,-22.32,-13.07,-11.53,-22.14,-20.4,-11.39,-17.41,-25.03,-17.21,-13.41,-23.74,-24.77,-15.31,-19.57,-28.99,-22.46,-16.8,-28.73,-32.2,-20.51,-25.75,-35.57,-32.11,-25.66,-32.66,-39.31,-30.22,-35.53,-48.71,-40.3,-36.38,-43.18,-58.14,-51.5,-41.82,-63.85,-61.07,-53.87,-56.13,-68.84,-67.96,-50.96,-65.13,-72.73,-65.43,-71.34,-76.4,-66.37,-72.15,-65.99,-83.19,-62.12,-78.43,-71.93,-62.78,-48.48,-63.91,-71.68,-38.85,-39.49,-36.53,-31.9,-21.72,-32.7,-29.04,-5.7,-11.96,-12.11,19.2,38.46,28.62,32.7,69.43,67.31,52.01,69.94,77.36,108.76,111.11,138.7,157.2,141.98,150.92,189.69,202.31,198.91,209.79,228.27,217.94,213.12,222.35,261.13,280.22,261.09,259.1,305.13,318.86,279.54,348.83,349.7,293.84,351.43,359.73,380.53,350.07,326.56,388.91,328.64,377.4,342.52,344.33,419.75,428.73,370.77,370.92,412.67,389.27,365.53,353.42,399.11,421.22,381.39,344.25,343.11,385.15,360.59,371.74,325.36,317.91,340.42,369.91,303.44,351.07,356.73,317.32,318.44,316.22,328.05,305.42,282.71,320.17,295.98,291.04,269.43,293.15,234.45,251.25,224.82,212.09,224.24,240.44,191.15,216.55,190.62,194.69,188.23,185.46,162.29,166.77,149.88,162.58,155.9,128.96,149.96,127.65,138.51,139.17,141.58,127.23,117.84,99.91,96.59,113.36,106.69,89.55,83.17,102.95,106.57,95.16,105.06,75.05,80.11,84.75,92.63,57.46,66.17,65.47,65.19,66.78,60.94,69.78,52.17,45.4,61.14,68.22,35.67,36.36,35.43,40.12,38.75,26.9,34.2,31.81,26.69,22.9,30.25,12.95,24.62,15.74,17.97,14.89,24.31,9.2,11.27,1.94,14.8,1.06,-4.63,7.09,7.08,-4.49,-8.9,-0.1,0.01,-10.9,-4.8,5.05,-14.63,-16.25,-4.02,-5.48,-18.67,-10.87,-2.96,-15.13,-17.33,-9.68,-9.24,-20.8,-14.94,-12.24,-21.43,-24.82,-14.86,-14.19,-23.01,-20.16,-13.3,-20.55,-30.41,-20.06,-17.7,-28.04,-29.97,-21.01,-25.98,-31.25,-25.53,-22.97,-34.9,-36.42,-22.07,-26.77,-37.49,-28.62,-27.32,-38.19,-39.31,-32.62,-32.62,-37.34,-39.38,-29.09,-35.53,-40.68,-35.8,-35.94,-42.71,-44.34,-37.67,-37.2,-53.59,-36.47,-39.64,-45.32,-52,-38.19,-42.84,-53.9,-49.04,-38.67,-53.19,-57.66,-38.66,-50.81,-61.3,-49.52,-48.42,-55.2,-61.52,-44.19,-52.76,-59.98,-55.15,-43.84,-54.91,-63.16,-39.06,-40.47,-55.85,-46.78,-45.79,-45.96,-58.63,-46.39,-54.48,-54.67,-58.02,-48.95,-43.85,-58.44,-59.71,-40.84,-52.99,-54.16,-44.75,-44.54,-62.58,-63.97,-58.32,-56.46,-71.77,-44.58,-41.36,-51.72,-67.14,-44.57,-54.03,-61.06,-49.94,-56.43,-66.51,-67.79,-55.72,-51.23,-61.34,-55.94,-46.44,-53.71,-68.04,-50.53,-49.31,-66.32,-66.88,-55.49,-66.18,-61.96,-52.5,-50.51,-76.9,-68.23,-59.16,-59.4,-77.84,-48.54,-63.98,-63.22,-57.02,-65.91,-66.81,-63.12,-48.5,-64.65,-71.02,-66.33,-56.87,-52.25,-75.21,-62.56,-55.92,-73.41,-68.96,-45.39,-65.44,-62.1,-64.2,-58.49,-59.71,-62.52,-54.29,-47.26,-53.66,-51.15,-55.46,-56.47,-62.44,-55.8,-56.75,-51.22,-54.87,-49.92,-50.93,-51.43,-39.93,-43.2,-54.77,-51.76,-46.05,-51.19,-57.08,-47.45,-40.02,-53.65,-43.36,-29.62,-35.07,-42.66,-35.62,-37.75,-42.72,-43.02,-40.3,-36.45,-39.65,-35.74,-36.23,-38.24,-42.81,-27.58,-33.95,-42.72,-35.01,-31.86,-32.8,-37.38,-34.81,-30.73,-40.87,-37.6,-30.5,-36.63,-37.06,-33.67,-27.48,-35.51,-38.08,-30.09,-25.99,-39.25,-28.71,-26.02,-33.1,-38.04,-28.48,-23.89,-33.72,-32.94,-23.95,-33.74,-34.4,-24.55,-24.89,-34.14,-29.1,-19.87,-28.3,-36.34,-25.18,-24.44,-31.06,-34.32,-21.37</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B233" t="str">
+        <v>[R_13_标记]</v>
+      </c>
+      <c r="C233" t="str">
+        <v>a: 36.0ms -118.0uv b: 76.8ms 462.5uv</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B234" t="str">
+        <v>[L_13_名字]</v>
+      </c>
+      <c r="C234" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B235" t="str">
+        <v>[L_13_放大器]</v>
+      </c>
+      <c r="C235" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B236" t="str">
+        <v>[L_13_闪光]</v>
+      </c>
+      <c r="C236" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B237" t="str">
+        <v>[L_13_闪光背景]</v>
+      </c>
+      <c r="C237" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B238" t="str">
+        <v>[L_13_采样]</v>
+      </c>
+      <c r="C238" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B239" t="str">
+        <v>[L_13_分析时间]</v>
+      </c>
+      <c r="C239" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B240" t="str">
+        <v>[L_13_数据长度]</v>
+      </c>
+      <c r="C240" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B241" t="str">
+        <v>[L_13_详细数据(uv)]</v>
+      </c>
+      <c r="C241" t="str">
+        <v>-0.12,-2.83,15.19,6.92,-5.16,11.45,13.31,-4.07,5.66,17.08,0.23,-0.13,17.07,6.39,-3.93,13.33,12.37,-4.48,7.07,16.13,-1.67,0.29,16.3,3.43,-4.91,12.66,8.92,-7.03,6.18,12.71,-5.6,-1.28,13.23,-1.48,-7.63,9.95,3.62,-11.06,3.43,7.44,-11.17,-4.27,8.57,-7.7,-12.19,5.21,-3.78,-17.13,-2.14,-0.01,-19.51,-10.94,-1.12,-19.18,-20.81,-3.85,-15.65,-29.41,-13.39,-12.87,-31.42,-22.66,-19.05,-37.91,-35.56,-20.24,-35.34,-50.09,-30.47,-32.88,-61.38,-39.24,-35.04,-58.31,-53.33,-52.69,-53.62,-69.19,-42.28,-59.18,-71.1,-64.78,-45.83,-66.81,-64.75,-31.86,-51.52,-68.9,-40.66,-55.6,-63.74,-44.28,-25.09,-42.47,-24.62,-7.97,-8.99,-2.56,17.49,7.89,26.62,48.56,35.02,35.81,64.91,76.93,69.91,67.48,97.08,106.75,92.7,127.92,165.11,158.02,163.33,170.61,191.49,180.44,206.92,224.39,208.43,220,282.49,280.02,282.92,297.02,266.67,321.14,286.56,304.03,309.74,321.74,356.99,324.58,381.25,343.71,377.48,335.13,352.21,362.59,386.02,452.2,363.37,387.46,450.22,461.36,400,393.75,394.15,372.11,393.88,463.52,416.2,411.23,427.77,430.08,410.39,445.62,363.55,393.66,362.87,405.99,400.61,348,402.89,384.17,290.93,340.55,340.04,321.3,305.34,301.28,321.3,291.89,326.18,278.64,268.54,280.45,261.93,234.36,234.04,217.51,205.34,189.73,219.3,193.46,174.7,192.21,194.5,169.43,181.28,194.11,163.3,170.84,171.7,142.95,140.63,158.74,146.47,135.29,131.99,128.76,132.63,132.09,135.1,107.95,106.81,118.7,121.68,107.3,109.57,105.12,87.06,98.8,94.97,68.97,61.77,78.68,94.21,66.33,95.7,88.39,47.67,53.58,75.43,57.29,44.72,81.6,64.36,56.43,70.29,69.55,27.6,59.91,46.81,48.25,32.16,57.49,36.41,22.5,38.94,33.45,26.06,33.7,38.01,13.4,26.01,37.63,19.11,8.31,24.92,25.84,4.67,19.91,22.43,4.52,9.77,28.1,8.29,3.35,20.93,13.87,-4.76,14,16.1,-3.89,3.93,15.75,-0.13,-3.84,12.64,5.13,-9.87,6.88,8.95,-7.46,-0.63,10.09,-5.35,-5.09,6.72,-3.65,-13.81,1.08,-0.05,-14.1,-2.89,-0.45,-13.72,-16.02,2.96,-14.85,-21.42,1.4,-6.67,-25.24,-12.13,-3.16,-22.43,-15.79,-7.93,-22.41,-25.44,-9.56,-13.39,-30.84,-18.73,-14.44,-31.83,-25.55,-18.82,-29.39,-34.76,-16.6,-30.84,-41.37,-27.84,-18.84,-43.02,-33,-24.78,-43.57,-31.32,-14.87,-34.49,-48.46,-24.07,-25.53,-50.05,-32.76,-25.46,-38.3,-42.78,-25.49,-40.64,-37.74,-26.22,-29.82,-41.06,-27.58,-20.96,-46.75,-34.35,-17.43,-43.5,-37.76,-29.72,-30,-37.35,-36.7,-22.38,-45.3,-48.08,-19.37,-51.26,-47.95,-21.81,-44.02,-48.74,-38.87,-29.22,-41.24,-46.92,-22.34,-41.01,-50.48,-19.79,-42.39,-54.32,-24.53,-28.63,-55.41,-41.92,-18.98,-47.84,-48.65,-25.71,-45.52,-54.66,-41.73,-39.49,-48.59,-33.03,-40.57,-54.81,-38.78,-32.22,-59.13,-64.42,-44.67,-42.29,-48.83,-43.6,-32.26,-51.29,-59.74,-31.88,-41.87,-50.55,-39.33,-54.96,-49.12,-43.09,-39.35,-69.84,-45.83,-33.33,-57.33,-60.17,-33.09,-51.17,-63.72,-48.76,-43.24,-67.01,-37.24,-27.4,-55.66,-55.12,-33.71,-52.23,-62.27,-24.09,-31.97,-42.37,-34.19,-36.29,-41.15,-48.84,-25.06,-46.93,-44.54,-20.83,-30.97,-36.59,-34.09,-15.96,-37.14,-29.25,-17.58,-33.64,-36.93,-25.2,-31.54,-40.57,-15.55,-10.73,-39.14,-18.6,-13.99,-31.48,-33.79,-8.92,-17.42,-31.88,-15.66,-7.22,-27.34,-22.2,-11.2,-27.97,-17.1,-8.06,-19.76,-21.54,-5.18,-11.69,-26.71,-10.48,-4.06,-24.1,-14.74,-7.57,-19.77,-26,-8.01,-11.7,-27.37,-14.62,-7.13,-26.43,-18.67,-6.03,-18.68,-21.23,-6.59,-14.46,-23.09,-9.46,-10.71,-22.1,-15.84,-2.35,-20.21,-21.56,-0.6,-11.9,-26.18,-6.12,-7</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B242" t="str">
+        <v>[L_13_标记]</v>
+      </c>
+      <c r="C242" t="str">
+        <v>a: 35.9ms -116.0uv b: 76.8ms 468.2uv</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B243" t="str">
+        <v>[R_14_名字]</v>
+      </c>
+      <c r="C243" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B244" t="str">
+        <v>[R_14_放大器]</v>
+      </c>
+      <c r="C244" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B245" t="str">
+        <v>[R_14_闪光]</v>
+      </c>
+      <c r="C245" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B246" t="str">
+        <v>[R_14_闪光背景]</v>
+      </c>
+      <c r="C246" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B247" t="str">
+        <v>[R_14_采样]</v>
+      </c>
+      <c r="C247" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B248" t="str">
+        <v>[R_14_分析时间]</v>
+      </c>
+      <c r="C248" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B249" t="str">
+        <v>[R_14_数据长度]</v>
+      </c>
+      <c r="C249" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B250" t="str">
+        <v>[R_14_详细数据(uv)]</v>
+      </c>
+      <c r="C250" t="str">
+        <v>10.01,16.93,6.53,-4.36,1.91,14.6,12.31,-1.62,-4.63,7.73,14.58,4.04,-6.96,-0.78,11.78,9.42,-4.58,-7.69,4.6,11.36,0.79,-10.29,-4.23,8.36,6.09,-7.84,-10.95,1.49,8.43,-1.86,-12.68,-6.28,6.69,4.76,-8.82,-11.37,1.28,8.68,-1.34,-12.3,-5.81,7.24,5.17,-8.49,-11.48,0.9,7.8,-2.43,-13.61,-7.28,6.02,4.08,-9.25,-11.84,0.65,9.25,-0.27,-10.13,-2.54,11.61,11.15,-1.65,-3.03,9.91,18.26,9.48,-1.59,4.71,17.91,14.77,-0.3,-4.57,6.78,12.12,0.16,-11.59,-5.81,4.73,4.32,-10.55,-13.44,2.62,10.7,4.07,-4.2,5.16,21.09,22.94,12.66,8.78,23.04,34.27,22.78,9.9,14.32,20.89,15.65,-2.28,-9.89,-2.91,0.18,-14.91,-27.29,-24.15,-11.66,-17.33,-29.9,-24.16,-11.77,2.24,-1.8,-5.87,3.95,27.27,31.17,17.24,13.64,34.56,34.97,27.24,5.9,12.49,16.17,6.63,-14.11,-27.86,-19.94,-24.16,-39.35,-42.51,-40.24,-34.54,-29.47,-32.08,-33.62,-10.65,3.66,1.54,1.49,13.2,30.9,34.69,33.63,30.66,43.22,46.32,31.14,8.51,9.52,14.74,6.15,-13.63,-22.63,-17.16,-13.22,-24.97,-45.27,-30.25,-15.29,-11.8,-23.74,-16.28,1.88,16.53,12.81,7.14,21.04,34.37,33.37,21.55,22.47,28.15,37.15,19.3,4,5.51,13.37,6.91,-13.29,-20.86,-11.01,-6.66,-16.04,-22.22,-16.28,-3.84,-0.96,-11.61,-11.91,4.29,15.15,7.91,-1.03,5.64,21.67,16.89,3.2,-2.21,10.66,16.25,3.43,-10.14,-6.77,4.12,0.27,-15.28,-19.2,-6.49,-0.71,-9.31,-20.17,-14.08,0.81,-0.39,-12.43,-14.53,-0.96,7.48,-1.96,-12.44,-5.8,7.14,5.73,-7.01,-11.29,1.19,8.4,-1.65,-12.87,-7.05,5.81,4.57,-8.97,-12.14,0.58,8.67,-0.69,-11.29,-4.85,8.77,7.95,-5.05,-7.87,5.06,13.15,3.61,-6.96,-0.94,12.42,11.25,-2.15,-5.46,7.03,14.74,5,-6.04,-0.11,13,11.63,-2,-5.39,7.01,14.62,4.79,-6.39,-0.61,12.37,10.87,-2.91,-6.51,5.68,13.12,3.13,-8.27,-2.69,10.12,8.47,-5.45,-9.22,2.83,10.2,0.13,-11.33,-5.82,6.97,5.34,-8.58,-12.33,-0.25,7.2,-2.79,-14.17,-8.59,4.32,2.84,-10.95,-14.59,-2.36,5.27,-4.53,-15.75,-10.01,3.1,1.84,-11.74,-15.2,-2.77,5.09,-4.48,-15.51,-9.57,3.75,2.72,-10.66,-13.94,-1.34,6.71,-2.67,-13.54,-7.48,5.99,5.1,-8.16,-11.36,1.32,9.47,0.16,-10.68,-4.61,8.88,8.02,-5.26,-8.51,4.11,12.22,2.86,-8.09,-2.14,11.24,10.28,-3.13,-6.56,5.89,13.85,4.33,-6.82,-1.09,12.1,10.96,-2.66,-6.32,5.91,13.68,3.96,-7.41,-1.91,11.08,9.76,-4.05,-7.92,4.12,11.73,1.87,-9.67,-4.33,8.54,7.12,-6.79,-10.78,1.18,8.75,-1.15,-12.73,-7.43,5.43,4.06,-9.83,-13.8,-1.8,5.86,-3.94,-15.43,-10.04,2.95,1.73,-12,-15.83,-3.68,4.18,-5.42,-16.74,-11.17,2.03,1.04,-12.48,-16.12,-3.76,4.32,-5.05,-16.17,-10.42,2.99,2.22,-11.11,-14.59,-2.07,6.2,-2.99,-13.99,-8.13,5.41,4.77,-8.46,-11.89,0.69,9.04,-0.1,-11.09,-5.24,8.3,7.66,-5.61,-9.11,3.39,11.67,2.45,-8.65,-2.95,10.46,9.71,-3.71,-7.4,4.91,13.03,3.64,-7.68,-2.19,11.02,10.07,-3.55,-7.48,4.62,12.54,2.96,-8.58,-3.32,9.7,8.59,-5.22,-9.35,2.57,10.35,0.64,-11.04,-5.93,6.98,5.8,-8.1,-12.31,-0.46,7.3,-2.42,-14.13,-9.03,3.9,2.77,-11.07,-15.25,-3.33,4.55,-5.06,-16.66,-11.45,1.63,0.68,-13,-17.03,-4.94,3.14,-6.25,-17.66,-12.28,1.02,0.3,-13.16,-17,-4.71,3.6,-5.56,-16.79,-11.22,2.27,1.76,-11.52,-15.21,-2.77,5.71,-3.3,-14.41,-8.75</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B251" t="str">
+        <v>[R_14_标记]</v>
+      </c>
+      <c r="C251" t="str">
+        <v>75.3uv</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B252" t="str">
+        <v>[L_14_名字]</v>
+      </c>
+      <c r="C252" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B253" t="str">
+        <v>[L_14_放大器]</v>
+      </c>
+      <c r="C253" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B254" t="str">
+        <v>[L_14_闪光]</v>
+      </c>
+      <c r="C254" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B255" t="str">
+        <v>[L_14_闪光背景]</v>
+      </c>
+      <c r="C255" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B256" t="str">
+        <v>[L_14_采样]</v>
+      </c>
+      <c r="C256" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B257" t="str">
+        <v>[L_14_分析时间]</v>
+      </c>
+      <c r="C257" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B258" t="str">
+        <v>[L_14_数据长度]</v>
+      </c>
+      <c r="C258" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B259" t="str">
+        <v>[L_14_详细数据(uv)]</v>
+      </c>
+      <c r="C259" t="str">
+        <v>15.35,11.36,-0.7,2.03,13.98,11.94,-0.58,0.12,12.29,12.26,-0.3,-1.65,10.5,12.61,0.43,-2.95,8.85,12.97,1.3,-4.03,6.88,12.75,1.59,-5.5,3.83,11.1,1.16,-8.05,-0.19,8.32,-0.14,-10.67,-4.55,6.11,-0.84,-11.77,-5.75,5.44,1.96,-9.22,-5.19,7.79,6.64,-4.86,-2.92,10.52,10.22,-2.29,-3.39,8.46,10.45,-2.7,-7.37,3.16,5.01,-8.72,-14.72,-3.01,0.2,-10.81,-16.15,-5.39,1.58,-5.96,-10.32,0.99,13.3,8.47,1.89,13.08,25.35,19.91,13.43,18.2,30.19,20.68,8.73,8.21,16.44,9.63,-6.66,-12.27,-1.89,-4.02,-20.06,-21.84,-8.36,-10.03,-19.12,-17.53,-0.71,7.36,2.99,5.09,22.21,37.08,31.48,21.78,35.15,42.55,38.12,18.32,22.28,28.05,11.19,-5.34,-7.25,-5.33,-19.18,-34.52,-28.98,-26.28,-24.81,-47.17,-31.68,-16.38,-10.16,-18,-6.98,14.46,21.38,13.73,18.73,41.11,43.43,27.77,27.4,32.23,30.11,11.22,0.92,3.38,0.56,-16.61,-31.72,-26.74,-26.85,-34.22,-39.38,-32.02,-21.79,-25.81,-26.41,-10.15,5.44,4.59,3.07,11.92,27.08,28.99,22.09,23.79,34.16,28.14,15.16,11.2,17.23,11.36,-6.09,-9.44,-3.54,-3.56,-18.3,-23.4,-10.82,-7.15,-14.5,-16.46,0.45,7.68,-0.41,-1.96,11.36,22.24,11.82,5.58,17.3,24.46,14.93,4.54,12.18,19.4,9.86,-2.33,2.25,10.56,3.52,-8.91,-4.9,6.34,1.02,-9.69,-7.99,6.2,3.88,-6.98,-5.25,7.81,8.6,-2.97,-3.79,8.32,10.8,-1.8,-5.22,5.63,9.08,-3.23,-9.06,1.26,6.68,-4.57,-11.9,-2.22,5.22,-4.5,-13.3,-4.2,4.84,-2.9,-12.56,-5.22,5.54,-0.43,-11.18,-5.62,6.02,1.9,-9.78,-6.16,5.94,3.77,-8.38,-6.91,5.63,5.45,-6.75,-7.27,5.28,7.22,-4.69,-7.16,5.04,9.07,-2.28,-6.69,4.84,10.77,0.28,-6,4.49,12.12,2.72,-5.27,3.86,12.96,4.9,-4.6,2.91,13.22,6.74,-3.99,1.69,12.95,8.21,-3.46,0.25,12.14,9.29,-3,-1.37,10.82,9.93,-2.64,-3.13,9.03,10.14,-2.35,-4.94,6.86,9.94,-2.12,-6.73,4.41,9.39,-1.9,-8.38,1.8,8.56,-1.62,-9.78,-0.83,7.54,-1.24,-10.84,-3.35,6.41,-0.72,-11.48,-5.64,5.26,-0.01,-11.64,-7.6,4.14,0.88,-11.28,-9.14,3.12,1.96,-10.39,-10.22,2.22,3.21,-9.01,-10.81,1.48,4.56,-7.18,-10.92,0.87,5.96,-4.99,-10.57,0.37,7.32,-2.55,-9.83,-0.04,8.56,0.01,-8.77,-0.43,9.57,2.58,-7.49,-0.84,10.28,5.01,-6.08,-1.31,10.59,7.19,-4.64,-1.89,10.46,9.01,-3.24,-2.6,9.86,10.38,-1.95,-3.45,8.76,11.24,-0.83,-4.42,7.21,11.58,0.09,-5.49,5.24,11.39,0.82,-6.6,2.95,10.72,1.35,-7.68,0.44,9.62,1.73,-8.65,-2.18,8.18,2,-9.43,-4.77,6.49,2.21,-9.95,-7.21,4.67,2.42,-10.12,-9.37,2.8,2.66,-9.9,-11.14,1,2.97,-9.25,-12.45,-0.66,3.38,-8.17,-13.22,-2.11,3.89,-6.66,-13.44,-3.32,4.47,-4.8,-13.11,-4.26,5.1,-2.64,-12.27,-4.94,5.72,-0.29,-10.99,-5.39,6.27,2.14,-9.34,-5.65,6.67,4.52,-7.45,-5.78,6.85,6.73,-5.41,-5.82,6.75,8.65,-3.34,-5.84,6.31,10.16,-1.36,-5.88,5.51,11.19,0.45,-5.99,4.33,11.68,2.01,-6.16,2.78,11.61,3.27,-6.42,0.92,10.97,4.2,-6.73,-1.2,9.81,4.8,-7.05,-3.48,8.2,5.1,-7.35,-5.81,6.23,5.14,-7.55,-8.07,4,4.96,-7.59,-10.15,1.64,4.65,-7.42,-11.93,-0.73,4.25,-6.99,-13.31,-2.99,3.83,-6.25,-14.21,-5.04,3.45,-5.2,-14.56,-6.81,3.12,-3.84,-14.35,-8.21,2.88,-2.22,-13.58,-9.24,2.71,-0.38,-12.29,-9.87,2.6,1.59,-10.56</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B260" t="str">
+        <v>[L_14_标记]</v>
+      </c>
+      <c r="C260" t="str">
+        <v>76.1uv</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B261" t="str">
+        <v>[R_15_名字]</v>
+      </c>
+      <c r="C261" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B262" t="str">
+        <v>[R_15_放大器]</v>
+      </c>
+      <c r="C262" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B263" t="str">
+        <v>[R_15_闪光]</v>
+      </c>
+      <c r="C263" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B264" t="str">
+        <v>[R_15_闪光背景]</v>
+      </c>
+      <c r="C264" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B265" t="str">
+        <v>[R_15_采样]</v>
+      </c>
+      <c r="C265" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B266" t="str">
+        <v>[R_15_分析时间]</v>
+      </c>
+      <c r="C266" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B267" t="str">
+        <v>[R_15_数据长度]</v>
+      </c>
+      <c r="C267" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B268" t="str">
+        <v>[R_15_详细数据(uv)]</v>
+      </c>
+      <c r="C268" t="str">
+        <v>-11.02,-21.42,-24.04,-16.69,-6.79,-4.21,-11.76,-22.49,-26.37,-19.97,-9.74,-5.83,-12.26,-23.1,-28.13,-22.73,-12.3,-7.08,-12.26,-23,-29.06,-24.71,-14.24,-7.79,-11.58,-22.06,-29.1,-25.86,-15.56,-7.93,-10.38,-20.45,-28.36,-26.28,-16.21,-7.74,-8.79,-18.38,-27.48,-27.01,-17.13,-8.36,-7.91,-17.04,-27.16,-28.48,-19.4,-9.9,-8.78,-18.61,-27.55,-30.65,-23.14,-16.91,-14.12,-22.16,-32.75,-35.12,-32.95,-23.03,-22.41,-26.42,-43.2,-44.79,-47.87,-37.57,-27.71,-36.94,-45.53,-55.48,-56.51,-39.42,-46.76,-56.36,-64.33,-73.82,-67.46,-67.82,-51.88,-61.05,-66.77,-86.34,-60.49,-65.04,-65.83,-59.93,-59.84,-68.07,-63.19,-42.5,-25.09,-45.99,-28.97,-49.28,-34.99,-11.73,-5.59,13.6,12.39,9.75,-9.19,41.82,36.75,56.04,55.64,37.56,68.16,76.84,109.94,136.16,103.63,99.72,120.78,144.1,181.09,193.23,178.01,208.79,202.85,177.27,203.13,275.07,255.25,253.33,286.02,289.97,272.44,276.36,316.83,302.28,320.58,342.85,378.9,369.68,406.59,319.46,317.95,329.39,348.14,385.4,357.49,439.27,413.02,370.82,421.51,388.62,426.54,394.77,397.74,383.17,399.57,405.44,398.29,396.33,442.03,442.72,362.66,459.02,404.34,412.87,362.43,335.44,405.71,414.89,379.28,366.58,320.82,386.44,325.14,336.5,379.4,301.82,286.66,285.47,284.77,285.96,328.57,314.98,255.57,231.89,275.06,267.63,277.36,245.56,236.67,222.51,224.87,199.92,227.03,208.49,224.7,177.37,196.45,195.65,176.72,168.03,158.46,152.61,153.12,122.37,146.27,152.51,137.28,125.11,129.28,124.33,132.96,112.41,102.2,94,98.94,102.36,106.3,96.8,87.82,103.67,64.53,70.23,102.38,103.28,87.41,67.56,54.58,60.66,79.49,79.74,57.24,52.04,40.24,48.62,57.03,74.88,55.03,42.27,35.31,39.25,31.11,58.44,37.49,36.04,20.19,14.51,23.85,35.34,37.66,25.24,4.14,10.84,19.08,17.86,20.72,18.57,-2.12,2.42,-1,15.68,11.05,5.84,-3.94,-7.87,-7.22,1.06,4.24,-3.09,-12.11,-20.66,-19.76,-9.88,-6.02,-6.83,-17.71,-28.41,-27.63,-13.38,-9.37,-14.48,-27.1,-36.82,-31.61,-20.75,-17.68,-20.13,-28.59,-40.15,-39.55,-29.66,-24.65,-24.98,-32.11,-40.49,-44.49,-31.24,-24.07,-23.32,-30.58,-46.78,-43.33,-41.26,-30.35,-27.41,-33.28,-45.6,-46.64,-44.71,-26.29,-27.86,-31.11,-40.72,-51.89,-41.54,-37.22,-31.33,-30.16,-43.67,-48.79,-48.63,-32.37,-23.46,-27.92,-39.28,-56.49,-41.57,-41.92,-30.85,-29.29,-49.45,-51.88,-43.49,-44.39,-38.09,-35.21,-40.85,-58.48,-55.13,-40.71,-36.38,-40.62,-41.23,-58.4,-48.67,-41.46,-45.3,-38.27,-50.51,-51.04,-58.74,-45.08,-39.08,-37.98,-44.58,-62.28,-62.05,-64.88,-38.97,-52.92,-48.89,-67.59,-78.04,-73.15,-56.89,-47.82,-63.43,-61.57,-73.1,-74.63,-59.01,-49.95,-51.25,-78.17,-70.28,-61.17,-66.65,-52.36,-54.03,-71.63,-67.39,-86.38,-57.26,-60.83,-67.9,-69.04,-71.97,-87.68,-66.77,-63.63,-65.79,-55.83,-88.09,-64.78,-61.52,-51.15,-47.97,-64.3,-68.62,-71.75,-64.37,-60.76,-48.33,-69.95,-64.64,-81.45,-62.15,-43.9,-51.86,-66.54,-78.44,-79.63,-54.66,-45.7,-49.89,-58.68,-55.22,-74.42,-71.2,-44.54,-50.4,-46.75,-67.21,-65.1,-65.48,-50.97,-46.23,-34.94,-49.96,-57.13,-58.61,-54.4,-32.17,-50.43,-61.76,-61.61,-63.59,-46.55,-47.76,-40.82,-49.58,-66.45,-58.53,-41.25,-37.82,-38.32,-41.5,-59.77,-55.95,-47.88,-37.29,-43.38,-52.45,-49.59,-50.46,-47.35,-37.99,-37.03,-36.71,-58.76,-54.89,-51.39,-34.59,-39.35,-44.18,-53.94,-55.14,-53.91,-44.74,-32.12,-36.67,-50.82,-52,-46.68,-33.97,-26.18,-31.6,-42.72,-53.59,-45.62,-35.16,-29.46,-24.69,-39.37,-49.98,-42.37,-31.56,-20.23,-22.57,-35.87,-44.16,-38.66,-28.03,-20.32,-19.66,-25.66,-38.94,-34.73,-29.67,-14.84,-17.44,-22.64,-34.26,-31.13,-24.32</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B269" t="str">
+        <v>[R_15_标记]</v>
+      </c>
+      <c r="C269" t="str">
+        <v>a: 40.8ms -109.5uv b: 84.3ms 581.5uv</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B270" t="str">
+        <v>[L_15_名字]</v>
+      </c>
+      <c r="C270" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B271" t="str">
+        <v>[L_15_放大器]</v>
+      </c>
+      <c r="C271" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B272" t="str">
+        <v>[L_15_闪光]</v>
+      </c>
+      <c r="C272" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B273" t="str">
+        <v>[L_15_闪光背景]</v>
+      </c>
+      <c r="C273" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B274" t="str">
+        <v>[L_15_采样]</v>
+      </c>
+      <c r="C274" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B275" t="str">
+        <v>[L_15_分析时间]</v>
+      </c>
+      <c r="C275" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B276" t="str">
+        <v>[L_15_数据长度]</v>
+      </c>
+      <c r="C276" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B277" t="str">
+        <v>[L_15_详细数据(uv)]</v>
+      </c>
+      <c r="C277" t="str">
+        <v>-17.2,-7.19,-6.52,-16.32,-25.18,-22.82,-12.43,-6.83,-13.1,-24.08,-26.94,-18.6,-9.42,-10.73,-21.31,-28.76,-24.45,-13.83,-9.92,-17.67,-28,-28.75,-19.23,-11.02,-14.17,-25.02,-30.7,-24.46,-13.95,-11.76,-20.66,-29.91,-28.51,-18.17,-11.43,-16.14,-27.12,-30.94,-22.98,-13.28,-13.02,-23.17,-31.15,-28.72,-17.42,-13.66,-20.23,-31.01,-33.52,-25.9,-15.86,-22,-32.64,-38.23,-36.59,-23.6,-22.99,-36.06,-47.59,-45.48,-41.52,-29.03,-43.94,-57.79,-61.19,-59.58,-42.23,-45.85,-65.49,-63.57,-74.41,-64.18,-49.78,-60.96,-85.09,-69.76,-72.09,-52.92,-70.72,-74.09,-83.63,-73.34,-57.12,-66.49,-58.21,-81.95,-58.32,-60.81,-42,-32.14,-46.64,-34.88,-41.8,-15.35,4.24,9.57,-0.19,-0.86,6.45,34.88,39.57,29.25,54.71,47.31,77.92,82.21,90.78,93.5,136.08,117.51,153.61,162.38,136.29,139.58,163.12,192.77,235.03,188.3,241.82,242.49,240.54,301.63,302.38,273.38,250.06,297.32,320.48,349.52,302.81,321.92,360.33,391.92,373.35,326.88,366.63,359.68,370.86,392.35,358.01,381.23,420.43,365.17,406.63,412.87,361.95,441.17,391.29,407.99,460.3,441.48,394.16,383.18,369.75,373.67,426.32,357.93,394.93,380.35,399.74,387.02,371.87,365.48,373.83,308.69,382.15,341.06,313.82,283.88,295.16,328.75,295.37,298.97,279.88,280.18,270.75,263.31,250.04,229.46,232.6,238.33,225.98,209.99,188.2,180.65,196.54,184.56,192.96,176.08,155.96,155.2,132.85,172.97,159.95,136.58,121.95,111.31,163.7,126.29,132.07,113.55,100.7,98.36,124.18,124.87,85.49,78.37,101.85,109.88,92.38,82.65,78.95,78.05,81.84,85.84,74.38,49.66,43.63,69.97,86.94,61.47,51.58,48.42,41.87,54.24,69.18,42.53,39.69,50.6,51.26,44.42,52.6,22.88,23.61,20.68,41.75,50.16,26.23,28.71,24.85,27,30.1,19.31,16.69,10.75,12.32,16.82,20.53,6.42,6.56,-0.36,13.83,21.23,7.16,-6.21,-2.92,5.22,13.22,2.13,-2.89,-16.73,-6.89,1.36,3.15,-7.74,-18.06,-15.7,-10.89,-3.03,-6.77,-18.3,-29.11,-19.48,-8.6,-8.86,-21.31,-30.74,-27.95,-15.62,-11.21,-21.35,-31.29,-36.61,-25.56,-20.18,-16.9,-30.82,-37.29,-31.81,-23.92,-24.79,-25.57,-36.7,-42.59,-29.9,-23.83,-26.65,-41.74,-47.75,-34.32,-31.8,-27.38,-39.4,-44.61,-46.04,-28.96,-27.11,-27.59,-38.47,-41.66,-35.34,-32.01,-29.8,-36.22,-46.23,-48.72,-33.56,-24.14,-34.37,-48.43,-48.96,-38.3,-35.77,-29.05,-50.15,-50.18,-40.83,-28.83,-30.9,-34.59,-42.03,-53.03,-38.57,-33.89,-39.28,-44.34,-57.01,-43.56,-29.03,-27.4,-53.04,-58.74,-43.96,-44.39,-42.47,-42.77,-57.85,-66.78,-39.86,-41.34,-39,-58.39,-67.47,-52.24,-42.46,-37.7,-60.71,-55.05,-58.25,-46.75,-55.63,-39.74,-62.78,-57.26,-63.76,-49.01,-44.81,-63.45,-61.36,-56.58,-64.6,-52.54,-59.42,-70.39,-65.91,-65.92,-52.12,-43.16,-66.19,-60.53,-78.44,-53.02,-46.03,-64.25,-74.31,-71.31,-66.25,-56.54,-66.73,-56.16,-83.16,-75.98,-50.5,-45.61,-60.31,-79.32,-68.33,-62.51,-44.78,-58.96,-65.52,-56.43,-54.09,-44.83,-47.25,-46.2,-62.34,-61.38,-40,-50.06,-52.44,-48.29,-63.21,-42.84,-43.6,-41.57,-59.5,-68.16,-63.11,-35.74,-47.63,-45.48,-47.71,-54.5,-45.47,-37.66,-31.94,-56.89,-50.16,-54.49,-31.11,-23.93,-45.71,-43.51,-42.39,-30.59,-26.74,-33.04,-37.83,-44.83,-49.84,-24.17,-34.36,-46.67,-40.98,-41.53,-31.4,-21.32,-30.21,-43.9,-40.5,-34.27,-25.86,-25.53,-39.91,-45.36,-45.77,-37.2,-24.81,-38.79,-48.93,-41.81,-29.29,-30.39,-24.82,-40.27,-49.36,-41.57,-31.2,-25.9,-31.67,-45.47,-37.93,-25.6,-21.24,-23.42,-34.22,-36.18,-30.25,-21.62,-21.04,-31.56,-35.3,-35.64,-22.55,-12.6,-18.62,-28.3,-33.82,-25.79,-12.78,-12.09,-24.04,-28.76,-27.04,-11.35,-9.71,-14.85,-26.61,-24.57,-16.2</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B278" t="str">
+        <v>[L_15_标记]</v>
+      </c>
+      <c r="C278" t="str">
+        <v>a: 40.8ms -113.8uv b: 84.4ms 556.1uv</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B279" t="str">
+        <v>[R_16_名字]</v>
+      </c>
+      <c r="C279" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B280" t="str">
+        <v>[R_16_放大器]</v>
+      </c>
+      <c r="C280" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B281" t="str">
+        <v>[R_16_闪光]</v>
+      </c>
+      <c r="C281" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B282" t="str">
+        <v>[R_16_闪光背景]</v>
+      </c>
+      <c r="C282" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B283" t="str">
+        <v>[R_16_采样]</v>
+      </c>
+      <c r="C283" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B284" t="str">
+        <v>[R_16_分析时间]</v>
+      </c>
+      <c r="C284" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B285" t="str">
+        <v>[R_16_数据长度]</v>
+      </c>
+      <c r="C285" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B286" t="str">
+        <v>[R_16_详细数据(uv)]</v>
+      </c>
+      <c r="C286" t="str">
+        <v>-3.2,0.97,1.54,-1.8,-7.74,-13.89,-17.76,-17.74,-13.9,-7.88,-2.18,0.81,-0.12,-4.58,-10.74,-15.92,-18.02,-16.08,-10.88,-4.51,0.44,1.98,-0.49,-5.87,-11.88,-15.95,-16.25,-12.74,-6.59,-0.45,3.27,3.28,-0.49,-6.19,-11.4,-13.75,-12.09,-6.93,-0.16,5.31,7.99,6,1.31,-4.68,-9.49,-10.57,-7.76,-2.36,3.53,7.25,7.2,2.91,-3.22,-9.98,-13.51,-13.21,-9.3,-2.62,2.76,5.62,4.79,0.66,-4.86,-8.92,-10.42,-7.53,-0.65,5.73,9.64,11.58,7.53,1.31,-6.41,-12.22,-14.21,-12.35,-8.71,-4.46,-4.46,-8.02,-11.35,-19.04,-25.92,-27.69,-24.36,-19.24,-10.89,-3.72,0.32,1.38,-1.69,-5.41,-5.06,-4.4,-1.65,6.54,7.74,13.04,6.93,0.64,-8.52,-18.72,-26.29,-28.67,-30.05,-29.06,-24.61,-22.94,-23.8,-26.7,-30.03,-36.87,-30.36,-21.75,-10.74,2.29,12.12,21.84,19.12,22.07,15.6,16.3,15.11,16.82,14.5,12.63,12.18,3.25,-8.08,-21.83,-35.73,-41.35,-38.52,-37.05,-27.67,-31.21,-27.72,-20.55,-22.48,-19.11,-15.55,-8,1.94,17.92,24.82,40.58,32.17,37.4,23.7,14.73,4.55,4.67,2.38,0.2,-2.56,-10.09,-15.48,-27.89,-42.81,-40.53,-48.53,-41.69,-32.13,-24.33,-14.79,-10.7,-7.96,-7.46,-8.88,-6.98,-4.2,6.52,13.39,18.24,19.49,14.16,7.05,-4.77,-13.93,-20.11,-22.47,-21.21,-19.28,-20.1,-20.11,-22.29,-32.2,-38.76,-39.6,-37.29,-27.37,-19.04,-10.12,-3.57,-1.66,-3.59,-8.38,-9.8,-12.22,-10.61,-6.56,-0.09,2.74,2.99,-0.35,-8.57,-16.19,-22.16,-23.69,-21.39,-14.9,-9.51,-6.88,-6.95,-9.97,-14.86,-19.52,-20.4,-17.54,-11.4,-3.91,2.27,4.79,3.45,-2.04,-7.83,-12.44,-13.29,-11.31,-5.78,-0.46,2.99,2.43,-1.84,-8.41,-14.41,-18.3,-17.56,-13.71,-7.59,-1.97,0.33,-1.3,-6.28,-12.55,-17.52,-19.25,-17,-11.7,-5.85,-1.71,-1.22,-4.83,-10.96,-17.39,-21.62,-21.95,-18.47,-12.81,-7.48,-4.84,-6.15,-11,-17.48,-23.06,-25.48,-23.88,-18.98,-12.9,-8.22,-6.92,-9.63,-15.23,-21.45,-25.71,-26.26,-22.89,-17.01,-11.02,-7.45,-7.71,-11.7,-17.71,-23.22,-25.88,-24.53,-19.67,-13.24,-7.83,-5.61,-7.4,-12.36,-18.33,-22.73,-23.62,-20.52,-14.6,-8.2,-3.87,-3.29,-6.59,-12.27,-17.88,-20.98,-20.17,-15.69,-9.31,-3.58,-0.8,-2.04,-6.72,-12.82,-17.76,-19.43,-17.09,-11.69,-5.43,-0.9,0.03,-3.02,-8.8,-14.92,-18.87,-19.05,-15.42,-9.54,-3.92,-0.96,-1.97,-6.61,-13.04,-18.71,-21.35,-19.99,-15.3,-9.36,-4.75,-3.53,-6.32,-12.12,-18.64,-23.32,-24.35,-21.46,-15.97,-10.3,-6.95,-7.44,-11.69,-18.07,-24.05,-27.27,-26.5,-22.16,-16.17,-11.09,-9.13,-11.18,-16.46,-22.83,-27.72,-29.12,-26.51,-20.99,-14.87,-10.7,-10.22,-13.62,-19.46,-25.31,-28.69,-28.16,-23.89,-17.6,-11.83,-8.9,-9.96,-14.48,-20.48,-25.39,-27.07,-24.71,-19.19,-12.69,-7.8,-6.43,-9.04,-14.43,-20.26,-23.97,-23.93,-20.04,-13.81,-7.73,-4.21,-4.64,-8.73,-14.72,-20.04,-22.4,-20.77,-15.77,-9.42,-4.33,-2.57,-4.86,-10.22,-16.43,-20.92,-21.83,-18.8,-13.14,-7.21,-3.55,-3.72,-7.72,-13.96,-19.93,-23.25,-22.62,-18.42,-12.49,-7.42,-5.42,-7.45,-12.8,-19.38,-24.58,-26.4,-24.2,-19.05,-13.21,-9.27,-8.98,-12.61,-18.78,-25.07,-28.99,-29.04,-25.31,-19.48,-14.07,-11.43,-12.76,-17.59,-24,-29.4,-31.63,-29.8,-24.74,-18.58,-13.91,-12.7,-15.46,-21.06,-27.15,-31.21,-31.53,-27.93,-21.89,-15.86,-12.28,-12.6,-16.6,-22.54,-27.89,-30.33,-28.75,-23.72,-17.21,-11.84,-9.71,-11.61,-16.62,-22.57,-26.85,-27.59,-24.35,-18.38,-12.04,-7.86,-7.46,-10.92,-16.7,-22.31,-25.33,-24.44,-19.92,-13.59,-8.02,-5.46,-6.95,-11.81,-18.02,-22.97,-24.59,-22.23,-16.85,-10.72,-6.41</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B287" t="str">
+        <v>[R_16_标记]</v>
+      </c>
+      <c r="C287" t="str">
+        <v>71.4uv</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B288" t="str">
+        <v>[L_16_名字]</v>
+      </c>
+      <c r="C288" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B289" t="str">
+        <v>[L_16_放大器]</v>
+      </c>
+      <c r="C289" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B290" t="str">
+        <v>[L_16_闪光]</v>
+      </c>
+      <c r="C290" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B291" t="str">
+        <v>[L_16_闪光背景]</v>
+      </c>
+      <c r="C291" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B292" t="str">
+        <v>[L_16_采样]</v>
+      </c>
+      <c r="C292" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B293" t="str">
+        <v>[L_16_分析时间]</v>
+      </c>
+      <c r="C293" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B294" t="str">
+        <v>[L_16_数据长度]</v>
+      </c>
+      <c r="C294" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B295" t="str">
+        <v>[L_16_详细数据(uv)]</v>
+      </c>
+      <c r="C295" t="str">
+        <v>-2.44,7.2,11.89,8.6,-0.87,-11.1,-16.26,-13.32,-4.3,5.45,10.04,6.59,-2.9,-12.93,-17.66,-14.28,-4.95,4.8,9.36,5.82,-3.52,-13.19,-17.17,-13.27,-3.23,6.87,11.52,8.21,-0.79,-10.01,-13.32,-8.84,1.32,11.63,15.72,11.87,2.59,-6.9,-10.52,-6.23,3.55,12.83,16.14,11.55,1.74,-7.64,-10.63,-5.6,4.96,14.41,18.71,14.8,6.02,-2.05,-3.84,2.43,13.06,22.64,27.45,22.65,12.86,3.37,-0.59,3.06,11.01,18.4,19.22,11.59,-1.37,-11.76,-15.17,-10.73,-1.15,7.01,9.14,3.94,-5.61,-12.3,-11.86,-2.99,9.38,19.98,25.23,23.5,13.94,1.61,2.89,7.29,14.1,18.26,17.26,6.72,-8.84,-22.54,-29.45,-28.53,-17.83,-10.05,-10.8,-22.25,-27.42,-38.04,-30.27,-19.77,-4.13,9.31,17.23,17.45,8.94,4.85,8.38,16.63,27.09,34.76,35.38,24.13,5.4,-8.16,-15.96,-17.68,-11.01,-8.13,-15.32,-19.37,-38.33,-47.72,-42.97,-33.49,-14.04,-0.71,10.05,9.76,9.02,5.6,13.3,23.39,40.22,53.84,50.34,37.36,28.84,13.42,7.24,10.25,13.01,13.52,4.46,-5.54,-27.15,-31.4,-34.61,-25.76,-17.03,-9.49,-1.58,-3.73,-9.4,-8.33,-0.68,13.45,28.44,38.05,39.27,34.34,22.45,10.82,9.18,14.05,18.68,19.58,13.84,-0.57,-16.03,-25.63,-29.39,-24.36,-15.72,-9.71,-5.15,-16.25,-23.75,-26.62,-20.95,-8.59,4.78,12.9,15.36,8.3,-1.38,-8.93,-3.87,3.27,10.57,14.78,11.16,0.66,-12.15,-19.34,-18.3,-11.56,-0.63,2.26,1.13,-7.99,-18.02,-21.49,-17.16,-6.86,5.14,11.46,9.82,1.85,-6.81,-9.81,-6.12,3.47,13.5,18.86,15.66,6.12,-4.01,-8.64,-5.55,3.71,13.34,17.4,13.78,4.31,-5.34,-9.09,-5.25,4.82,14.81,19.3,15.45,6.07,-3.24,-6.89,-2.63,7.11,16.56,20.24,15.81,5.67,-4.09,-7.97,-3.92,5.47,14.39,17.34,12.27,1.93,-7.89,-11.59,-7.25,2.32,11.14,13.79,8.48,-1.93,-11.5,-14.81,-10.15,-0.5,8.22,10.64,5.07,-5.37,-14.74,-17.66,-12.66,-2.8,5.86,8.1,2.42,-7.92,-16.92,-19.35,-13.83,-3.68,5.07,7.23,1.54,-8.61,-17.18,-19.03,-12.99,-2.53,6.27,8.35,2.62,-7.38,-15.56,-16.9,-10.42,0.27,9.05,10.95,5.09,-4.84,-12.72,-13.65,-6.83,3.96,12.58,14.19,8.08,-1.9,-9.61,-10.26,-3.24,7.5,15.83,17.01,10.52,0.37,-7.28,-7.77,-0.69,9.89,17.8,18.45,11.5,1.11,-6.56,-6.97,0.12,10.47,17.92,18,10.58,-0.06,-7.74,-8.06,-0.97,9.17,16.19,15.74,7.9,-2.92,-10.54,-10.68,-3.51,6.5,13.17,12.31,4.17,-6.7,-14.13,-13.98,-6.6,3.4,9.85,8.71,0.41,-10.37,-17.46,-16.88,-9.17,0.94,7.3,5.99,-2.34,-12.9,-19.54,-18.44,-10.31,-0.01,6.32,4.93,-3.36,-13.64,-19.78,-18.11,-9.55,0.94,7.26,5.78,-2.48,-12.49,-18.16,-15.97,-7.02,3.6,9.81,8.18,-0.12,-9.94,-15.23,-12.62,-3.41,7.21,13.2,11.28,2.82,-6.92,-11.96,-9.08,0.25,10.73,16.36,14.02,5.28,-4.52,-9.42,-6.38,2.93,13.14,18.3,15.44,6.33,-3.6,-8.45,-5.33,3.9,13.77,18.4,14.99,5.49,-4.58,-9.38,-6.19,2.96,12.5,16.63,12.71,2.87,-7.28,-11.95,-8.62,0.52,9.82,13.53,9.21,-0.85,-10.95,-15.39,-11.79,-2.54,6.63,10.06,5.47,-4.66,-14.57,-18.62,-14.63,-5.16,4.01,7.28,2.56,-7.52,-17.11,-20.66,-16.18,-6.38,2.86,6.05,1.27,-8.67,-17.87,-20.88,-15.86,-5.73,3.61,6.73,1.89,-7.91,-16.74,-19.22,-13.71,-3.29,6.08,9.06,4.11,-5.63,-14.16,-16.2,-10.31,0.28,9.55,12.28,7.09,-2.69,-11.04,-12.78,-6.64,3.97,13.01,15.34,9.79,-0.17,-8.46,-10.02,-3.77,6.73,15.41,17.23,11.22,1,-7.33</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B296" t="str">
+        <v>[L_16_标记]</v>
+      </c>
+      <c r="C296" t="str">
+        <v>73.4uv</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B297" t="str">
+        <v>[R_17_名字]</v>
+      </c>
+      <c r="C297" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B298" t="str">
+        <v>[R_17_放大器]</v>
+      </c>
+      <c r="C298" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B299" t="str">
+        <v>[R_17_闪光]</v>
+      </c>
+      <c r="C299" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B300" t="str">
+        <v>[R_17_闪光背景]</v>
+      </c>
+      <c r="C300" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B301" t="str">
+        <v>[R_17_采样]</v>
+      </c>
+      <c r="C301" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B302" t="str">
+        <v>[R_17_分析时间]</v>
+      </c>
+      <c r="C302" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B303" t="str">
+        <v>[R_17_数据长度]</v>
+      </c>
+      <c r="C303" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B304" t="str">
+        <v>[R_17_详细数据(uv)]</v>
+      </c>
+      <c r="C304" t="str">
+        <v>-6.66,-7.39,-7.42,-6.74,-5.4,-3.49,-1.17,1.41,4.03,6.51,8.66,10.31,11.36,11.73,11.42,10.46,8.96,7.06,4.93,2.76,0.76,-0.91,-2.09,-2.65,-2.54,-1.76,-0.33,1.6,3.94,6.53,9.04,11.44,13.44,14.96,15.69,15.76,15.21,13.85,11.99,9.55,7.13,4.64,1.98,-0.26,-2.2,-2.95,-3.49,-3.92,-2.62,-1.97,-1.42,1.68,3.62,2.89,4.76,5.7,3.63,5.21,-0.9,-0.03,-5.12,-8.95,-10.82,-15.31,-19.1,-25.69,-29.29,-27.97,-36.63,-34.41,-39.66,-30.9,-34.46,-31.46,-33.88,-32.58,-38.82,-30.94,-32.21,-31.6,-46,-32.6,-29.7,-44.02,-48.25,-40.14,-43.52,-44.95,-47.69,-33.59,-53.3,-48.12,-29.44,-38.96,-37.54,-12.87,-1.86,-11.58,10.41,3.51,18.66,22.69,38.04,37.68,50.08,49.26,41.19,42.28,58.83,64.48,90.73,102.57,93.19,111.38,127.89,123.2,155.53,177.17,187.21,169.6,197.51,224.97,195.11,217.71,220.8,249.74,257.98,277.81,300.97,288.66,259.63,257.24,290.21,307.97,348.32,301.61,341.63,338.93,331.44,330.3,393.47,345.76,409.38,376.55,388.05,421.35,432.51,379.41,385.53,356.89,361.12,399.46,424.4,430.85,373.98,371.32,384.35,356.26,432.35,403.74,441.48,410.81,417.38,370.76,392.84,391.46,423,355.32,399.42,409.63,329.1,373.3,339.86,324.43,350.11,338.56,310.94,282.95,309.63,271.5,304.23,299.33,297.58,282.22,302.51,306.36,274.87,260.8,269.53,253.32,279.73,231.29,245.44,242.53,251.21,201.31,220.78,219.71,198.38,177.51,166.65,201.19,194.37,175.61,161.61,193.45,155.73,139.6,158.09,151.17,168.55,145.05,144.66,155.09,122.81,111.57,110.71,130.85,109.83,106.58,94.47,99.3,105.09,91.16,82.34,76.88,92.84,75.35,77.93,105.74,90.89,80.84,93.19,79.29,87.17,67.89,61.8,76.31,69.24,64.23,37.73,46,38.34,37.98,31.54,38.68,32.78,29.54,41.06,32.41,27.5,34.03,31.7,31.68,33.07,31.93,30.01,27.43,21.84,20.39,14.72,11.59,7.79,5.02,0.49,2.51,-4.39,-0.56,-0.31,-3.52,-0.14,1.82,3.19,5.42,8.09,6.35,5.32,5.92,2.1,4.87,-0.63,-4.01,-8.36,-10.31,-8.44,-11.21,-11.03,-16.16,-14.34,-11.57,-12.45,-10.66,-6.6,-8.55,-8.27,-5.42,-0.01,1.22,0.01,-5.04,-3.96,-4.65,-10.84,-10.06,-9.23,-17.65,-20.98,-22.06,-17.99,-24.1,-22.27,-22.36,-21.19,-22.28,-20.74,-18.52,-9.37,-12.84,-7.78,-14.04,-11.85,-13.41,-20.58,-15.19,-24.32,-21.08,-25.21,-23.57,-36.64,-40.55,-33.22,-34.25,-39.09,-40.06,-32.85,-36.61,-31.59,-26.6,-26.34,-36.22,-20.05,-21.27,-23.29,-24.89,-28.45,-35.73,-27.52,-31.15,-43.91,-47.02,-51.34,-44.01,-52.96,-49.41,-44.51,-47.21,-51.24,-47.71,-44.86,-44.19,-30.64,-36.25,-25.27,-33.73,-35.08,-35.75,-36.4,-46.92,-48.75,-41.17,-53.49,-51.73,-42.08,-58.63,-43.54,-48,-59.3,-40.44,-44.01,-35.97,-38.55,-43.29,-41.9,-32.01,-25.33,-39.79,-29.71,-38.79,-36.87,-43.38,-47.05,-31.66,-44.79,-38.21,-50.27,-47.83,-60.71,-59.08,-40.89,-41.44,-43.6,-35.6,-39.53,-51.78,-38.08,-38.39,-41.52,-41.68,-30.73,-30.42,-32.96,-41.52,-33.26,-45.64,-49.8,-44.96,-54.14,-49.69,-61.47,-58.44,-50.13,-43.98,-56.5,-44.97,-35.43,-37.13,-29.6,-28.33,-29.76,-33.52,-24.79,-41.85,-28.04,-31.29,-39.46,-30.37,-35.36,-38,-43.78,-51.93,-50,-50.7,-44.27,-39.54,-37.28,-39.5,-37.98,-26.51,-33.73,-24.63,-20.36,-21.86,-27.5,-19.3,-20.72,-30.88,-27.68,-25.25,-27.55,-36.74,-27.71,-30.68,-34.23,-34.36,-37.48,-29.18,-27.81,-27.75,-22.89,-23.43,-20.16,-10.15,-12.21,-12.29,-11.72,-8.61,-12.88,-6.17,-9.81,-12.24,-18.14,-14.82,-21.96,-24.03,-18.62,-20.39,-23.54,-17.4,-14.72,-18.29,-10.37,-10.09,-9.86,-3.45,-3.97,-1.64,-2.42,-3.67,-2.95,-4.27</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B305" t="str">
+        <v>[R_17_标记]</v>
+      </c>
+      <c r="C305" t="str">
+        <v>a: 43.5ms -115.8uv b: 90.8ms 597.6uv</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B306" t="str">
+        <v>[L_17_名字]</v>
+      </c>
+      <c r="C306" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B307" t="str">
+        <v>[L_17_放大器]</v>
+      </c>
+      <c r="C307" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B308" t="str">
+        <v>[L_17_闪光]</v>
+      </c>
+      <c r="C308" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B309" t="str">
+        <v>[L_17_闪光背景]</v>
+      </c>
+      <c r="C309" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B310" t="str">
+        <v>[L_17_采样]</v>
+      </c>
+      <c r="C310" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B311" t="str">
+        <v>[L_17_分析时间]</v>
+      </c>
+      <c r="C311" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B312" t="str">
+        <v>[L_17_数据长度]</v>
+      </c>
+      <c r="C312" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B313" t="str">
+        <v>[L_17_详细数据(uv)]</v>
+      </c>
+      <c r="C313" t="str">
+        <v>-12.78,-15.33,-15.97,-14.6,-11.45,-7.06,-2.18,2.36,5.8,7.56,7.37,5.28,1.69,-2.73,-7.19,-10.86,-13.07,-13.39,-11.72,-8.29,-3.65,1.45,6.18,9.76,11.59,11.51,9.41,5.84,1.43,-3.01,-6.79,-9.18,-9.66,-8.04,-4.9,-0.52,3.76,8.31,10.78,12.75,11.92,8.45,3.41,-2.17,-7.9,-12.68,-14.54,-17.88,-16.19,-14.56,-11.91,-9.4,-7.74,-8.22,-11.03,-9.27,-18.8,-19.37,-26.23,-37.8,-46,-47.68,-60.97,-59.81,-58.07,-48.78,-55.33,-57.21,-58.64,-57.17,-52.2,-66.43,-55.99,-73.69,-82.06,-77.67,-82.53,-80.76,-93.43,-74.72,-75.94,-55.99,-61.94,-52.72,-35.62,-46.95,-30.02,-37.66,-24.82,-27.3,-23.21,-16.11,-8.23,-1.89,16.09,13.67,45.19,55.2,54.05,69.72,81.32,99.05,101.57,100.54,114.16,126.16,150.76,153.55,149.08,156.92,168.59,220.84,207.6,214.35,265.12,238.11,293.95,247.21,293.79,304.65,266.65,333.32,283.43,333.15,311.98,345.6,331.72,349.17,383.4,390.13,370.7,397.17,356.84,350.57,426.84,429.16,416.77,418.4,419.04,370.98,373.6,436.55,407.84,416.74,417.09,436.8,375.83,422.09,356.69,363.7,347.59,344.13,326.52,338.5,323.11,355.78,366.59,291.68,294.16,301.31,315.58,306.69,269.59,253.43,246.69,230.84,217.03,225.01,208.67,211.85,228.45,189.46,209.82,193.52,198.75,195.32,176.1,180.79,163.61,152.38,148.67,153.92,118.6,121.02,123.74,114.34,113.28,134.81,122.97,136.4,133.89,126.32,119.05,104.73,109.57,93.63,75.98,96.45,96.45,67.46,84.77,83.21,89.67,78.17,80.41,100.54,95.34,95.39,65.12,79.46,50.77,58.38,63.31,54.13,63.7,74.48,65.52,81.75,65.94,57.72,51.94,53.75,42.29,60.24,35.29,28.45,42.68,38.26,24.17,39.67,30.27,28.02,38.87,33.23,40.74,37.25,32.11,27.67,12.93,8.68,8.41,-0.23,-1.28,-3.22,0.33,2.66,3.3,8.06,6.7,8.95,5.77,3.3,-2.79,-9.33,-11.66,-19.84,-24.93,-26.64,-26.59,-20.71,-18.62,-14.19,-10.94,-10.61,-9.18,-7.05,-11.95,-17.25,-21.67,-29.02,-32.28,-31.62,-36.71,-35.91,-32.31,-23.67,-24.71,-16.92,-18.58,-13.89,-16.86,-21.09,-24.33,-26.21,-31.75,-35.71,-42.25,-39.86,-34.19,-32.79,-29.03,-26.43,-16.82,-18.03,-19.36,-17.11,-17.07,-25.48,-27.92,-39.18,-40.98,-44.44,-41.12,-36.7,-39.09,-30.44,-29.22,-30.05,-18.48,-18.63,-28,-26.75,-29.01,-36.87,-40.31,-39.01,-46.2,-51.35,-49.7,-39.67,-42.21,-33.25,-27.34,-28.47,-26.57,-26.21,-35.49,-42.68,-52.08,-58.38,-48.21,-55.61,-52.91,-61.57,-52.23,-59,-52.87,-36.91,-47.59,-40.45,-40.91,-49.82,-43.64,-54.74,-67.51,-63.75,-60.57,-62.53,-68.59,-63.34,-66.48,-52.55,-56.9,-54.56,-52.58,-41.55,-54.88,-58.19,-57.56,-72.81,-68.92,-85.18,-72.35,-75.44,-67.34,-71.68,-53.48,-62.17,-60.54,-56.55,-55.05,-46.85,-66.2,-64.93,-75.34,-69.43,-82.71,-80.06,-73.99,-60.43,-61.07,-58.67,-42.43,-43.09,-39.51,-41.03,-61.82,-53.85,-69.71,-57.74,-59.4,-60.21,-71.92,-60.32,-61.49,-67.05,-50.54,-53.72,-48.22,-37.56,-35.25,-55.95,-52.83,-52.39,-62.87,-61.35,-63.18,-71.25,-58.47,-53.38,-45.87,-53.51,-52.41,-39.59,-41.41,-50.91,-46.77,-46.08,-57.07,-68.27,-69.34,-70.3,-64.7,-71.94,-66.86,-51.5,-41.77,-44.2,-36.65,-37.68,-36.55,-46.48,-55.9,-50.97,-61.73,-69.8,-60.06,-65.85,-64.65,-50.49,-51.37,-47.23,-43.23,-43.57,-38.17,-34.15,-37.23,-51.8,-47.52,-57.93,-59.42,-58.06,-61.48,-51.53,-54.76,-46.58,-34.01,-35.94,-33.51,-33.94,-27.01,-33.5,-40.39,-42.4,-41.41,-45.98,-46.52,-46.8,-45.16,-37.36,-32.17,-25.15,-22.84,-21.21,-15.48,-16.4,-23.63,-26.97,-28.21,-31.13,-36.35,-36.94,-35.4,-32.47,-31.63,-24.45,-20.37,-18.21,-14.58,-10.81,-12.43,-19.15,-21.77,-26.25,-30.73,-35.02,-35.62,-37.45,-37.84,-30.51</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B314" t="str">
+        <v>[L_17_标记]</v>
+      </c>
+      <c r="C314" t="str">
+        <v>a: 43.4ms -116.8uv b: 90.8ms 582.9uv</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B315" t="str">
+        <v>[R_18_名字]</v>
+      </c>
+      <c r="C315" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B316" t="str">
+        <v>[R_18_放大器]</v>
+      </c>
+      <c r="C316" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B317" t="str">
+        <v>[R_18_闪光]</v>
+      </c>
+      <c r="C317" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B318" t="str">
+        <v>[R_18_闪光背景]</v>
+      </c>
+      <c r="C318" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B319" t="str">
+        <v>[R_18_采样]</v>
+      </c>
+      <c r="C319" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B320" t="str">
+        <v>[R_18_分析时间]</v>
+      </c>
+      <c r="C320" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B321" t="str">
+        <v>[R_18_数据长度]</v>
+      </c>
+      <c r="C321" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B322" t="str">
+        <v>[R_18_详细数据(uv)]</v>
+      </c>
+      <c r="C322" t="str">
+        <v>-1.54,-1.94,-2.32,-2.79,-3.12,-3.39,-3.77,-4.01,-4.25,-4.41,-4.53,-4.71,-4.83,-4.72,-4.41,-4.42,-4.13,-3.95,-3.7,-3.47,-3.47,-3.4,-3.55,-3.55,-3.68,-3.56,-3.63,-3.71,-3.07,-2.71,-2.79,-2.28,-1.18,-0.45,0.6,1.65,2.71,4.07,5.19,6.23,6.87,8,8.46,9.03,9.21,8.42,8.21,7.74,6.84,5.41,3.74,2.25,1.58,-1.23,-1.1,-1.54,-2.09,-4.12,-3.71,-3.64,-2.53,-1.01,0.66,2.46,3.35,4.91,6.85,5.77,8.07,6,6.22,6.38,1.92,0.32,-3.47,-7.22,-10.64,-15.01,-16.77,-23.16,-21.81,-24.88,-26.17,-24.48,-23.87,-24.27,-22.37,-16.77,-13.17,-8.81,-4.82,2.02,3.57,10.33,13.74,12.05,9.36,9.92,9.68,3.64,-0.07,-3.72,-8.46,-13.3,-19.36,-20.9,-29.35,-26.52,-23.86,-27.82,-21.07,-21.04,-14.83,-9.23,-1.7,5.57,11.74,23.09,22.82,29.78,37.08,31.63,40.24,37.97,30.93,28.3,17.44,10.15,3.01,-4.06,-15.53,-20.34,-24.45,-30.31,-31.68,-35.04,-34.51,-25.26,-22.44,-14.9,-9.89,-1.65,5.55,11.47,16.02,24.08,29.01,19.78,19.58,16.84,16.78,12.16,2.45,-6.11,-13.69,-23.39,-29.64,-34.48,-38.17,-49.45,-46.1,-44.84,-46.28,-44.63,-41.93,-31.38,-23.98,-17.61,-9.82,-2.96,0.54,6.54,12.33,15.09,13.06,14.41,12.54,6.1,1.52,-4.12,-8.21,-12.5,-17.18,-23.44,-26,-26.92,-28.51,-22.83,-26.87,-22.2,-19.24,-10.9,-5.68,-1.28,4.18,10.01,13.66,15.27,18.9,18.43,21.12,21.38,17.06,16.24,12.23,8.5,5.04,1.14,-2.45,-6.51,-9.64,-8.48,-13.22,-10.93,-13.26,-10.15,-10.87,-10.44,-8.69,-6.78,-5.3,-3.79,-3.69,-2.34,-2.22,-4.62,-2.83,-5.01,-7.26,-9,-11.84,-13.69,-15.41,-17.7,-19.68,-21.16,-23.22,-23.12,-23.98,-24.9,-24.9,-23.88,-24.03,-23.12,-22.16,-21.04,-19.93,-18.72,-17.64,-16.8,-16.01,-15.41,-14.69,-13.91,-14.22,-13.22,-13.39,-12.85,-12.73,-12.31,-11.95,-11.55,-10.87,-10.1,-9.66,-8.76,-8.07,-7.15,-6.36,-5.3,-4.32,-3.6,-2.81,-2.11,-1.48,-1.02,-0.47,-0.33,-0.12,-0.05,-0.01,-0.03,-0.3,-0.56,-0.88,-1.28,-1.74,-2.24,-2.76,-3.32,-3.93,-4.53,-5.18,-5.83,-6.53,-7.2,-7.96,-8.69,-9.44,-10.23,-11.02,-11.79,-12.61,-13.38,-14.16,-14.96,-15.7,-16.43,-17.13,-17.79,-18.39,-18.96,-19.48,-19.93,-20.34,-20.68,-20.97,-21.18,-21.34,-21.42,-21.46,-21.43,-21.33,-21.19,-20.98,-20.73,-20.42,-20.07,-19.67,-19.23,-18.75,-18.25,-17.71,-17.14,-16.55,-15.95,-15.33,-14.7,-14.07,-13.44,-12.81,-12.19,-11.59,-11.01,-10.44,-9.91,-9.4,-8.93,-8.5,-8.1,-7.75,-7.45,-7.19,-6.98,-6.82,-6.71,-6.65,-6.65,-6.7,-6.79,-6.94,-7.14,-7.38,-7.67,-8.01,-8.38,-8.79,-9.24,-9.72,-10.22,-10.75,-11.3,-11.87,-12.45,-13.04,-13.64,-14.23,-14.82,-15.41,-15.98,-16.54,-17.08,-17.6,-18.09,-18.55,-18.99,-19.38,-19.75,-20.07,-20.36,-20.6,-20.8,-20.96,-21.07,-21.14,-21.17,-21.15,-21.09,-20.99,-20.85,-20.68,-20.47,-20.22,-19.94,-19.64,-19.31,-18.96,-18.59,-18.2,-17.8,-17.4,-16.98,-16.57,-16.16,-15.75,-15.36,-14.97,-14.61,-14.26,-13.93,-13.63,-13.35,-13.11,-12.89,-12.71,-12.57,-12.46,-12.39,-12.35,-12.36,-12.4,-12.48,-12.6,-12.76,-12.95,-13.17,-13.43,-13.72,-14.04,-14.38,-14.75,-15.14,-15.55,-15.97,-16.4,-16.84,-17.29,-17.74,-18.19,-18.63,-19.07,-19.49,-19.9,-20.29,-20.66,-21,-21.32,-21.62,-21.88,-22.11,-22.3,-22.46,-22.59,-22.68,-22.72,-22.74,-22.71,-22.65,-22.54,-22.41,-22.24,-22.03,-21.8,-21.53,-21.24,-20.93,-20.59,-20.23,-19.86,-19.48,-19.09,-18.69,-18.29,-17.89,-17.5,-17.12,-16.74,-16.39,-16.05,-15.73,-15.44,-15.17,-14.94,-14.74,-14.57,-14.44,-14.35,-14.3,-14.29,-14.32</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B323" t="str">
+        <v>[R_18_标记]</v>
+      </c>
+      <c r="C323" t="str">
+        <v>72.4uv</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B324" t="str">
+        <v>[L_18_名字]</v>
+      </c>
+      <c r="C324" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B325" t="str">
+        <v>[L_18_放大器]</v>
+      </c>
+      <c r="C325" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B326" t="str">
+        <v>[L_18_闪光]</v>
+      </c>
+      <c r="C326" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B327" t="str">
+        <v>[L_18_闪光背景]</v>
+      </c>
+      <c r="C327" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B328" t="str">
+        <v>[L_18_采样]</v>
+      </c>
+      <c r="C328" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B329" t="str">
+        <v>[L_18_分析时间]</v>
+      </c>
+      <c r="C329" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B330" t="str">
+        <v>[L_18_数据长度]</v>
+      </c>
+      <c r="C330" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B331" t="str">
+        <v>[L_18_详细数据(uv)]</v>
+      </c>
+      <c r="C331" t="str">
+        <v>-11.65,-11.6,-11.53,-11.46,-11.39,-11.29,-11.2,-11.08,-10.94,-10.81,-10.66,-10.5,-10.34,-10.17,-9.98,-9.81,-9.62,-9.44,-9.27,-9.1,-8.94,-8.78,-8.6,-8.42,-8.27,-8.05,-7.87,-7.73,-7.52,-7.25,-7.03,-6.74,-6.46,-6.16,-5.83,-5.55,-5.33,-5.02,-4.62,-4.56,-4.41,-4.3,-4.16,-4.03,-4.08,-4.23,-4.42,-4.64,-4.81,-4.93,-5.01,-5.42,-5.47,-5.1,-5.44,-4.6,-4.65,-3.87,-3.32,-2.54,-1.96,-1.08,0.12,0.38,0.6,0.91,2.06,1.79,1.89,0.71,-0.49,-1.49,-2.7,-4.17,-5.52,-7.49,-8.77,-8.75,-8.88,-8.89,-8.78,-9.71,-8.32,-5.71,-3.4,-0.78,2.48,4.45,6.3,11.36,11.51,11.93,15.2,12.23,12.84,7.16,5.83,2.77,-1.87,-6.64,-9.76,-15.82,-15.41,-19.73,-22.18,-25.03,-21.43,-16.99,-18.21,-10.71,-7.16,-1.72,4.16,9.51,14.79,19.11,20.22,23.91,25.83,20.48,20.86,14.95,10.32,4.14,-2.48,-11.06,-18.78,-26.61,-27.35,-32.24,-33.05,-41.79,-39.15,-37.42,-27.25,-19.99,-16.15,-7.03,-0.01,10.16,15.51,20.78,31.09,24.18,25.22,24.03,24.85,16.59,15.3,3.62,-2.53,-10.19,-19.8,-27.61,-30.76,-28.52,-33.32,-34.55,-36.85,-33.52,-29.99,-23.17,-15.01,-7.02,-0.24,6.03,10.56,15.99,16.6,22.05,24.93,20.19,22.59,14.96,13.39,6.26,3.51,-1.33,-4.96,-10.79,-12.8,-15.52,-12.59,-11.84,-12.62,-12.79,-9.26,-5.16,-1.42,1.29,4.98,8.87,11.77,12.3,16.5,17.09,17.9,15.81,13.66,13.38,12.76,10.3,8.29,6.79,5.34,3.78,2.55,1.65,1.55,1.52,2.17,2.69,3.05,4.06,4.9,5.56,6.44,7.07,7.75,8.35,8.56,8.48,8.41,7.47,7,6.47,5.66,5,4.21,3.59,2.9,2.34,1.66,1.44,1.18,0.66,0.59,0.46,0.12,0.22,0.13,0.01,-0.05,-0.1,-0.19,-0.3,-0.5,-0.58,-0.71,-0.96,-1.11,-1.3,-1.42,-1.6,-1.71,-1.83,-1.91,-1.97,-2,-2,-1.99,-1.93,-1.86,-1.75,-1.61,-1.49,-1.33,-1.17,-0.98,-0.79,-0.59,-0.38,-0.17,0.06,0.29,0.53,0.77,1.03,1.29,1.56,1.82,2.1,2.37,2.66,2.94,3.22,3.51,3.79,4.08,4.36,4.64,4.91,5.18,5.44,5.7,5.95,6.2,6.43,6.66,6.88,7.08,7.28,7.47,7.65,7.82,7.98,8.13,8.27,8.4,8.52,8.63,8.73,8.82,8.9,8.97,9.03,9.08,9.13,9.16,9.19,9.21,9.22,9.23,9.23,9.22,9.21,9.19,9.17,9.15,9.12,9.08,9.05,9.01,8.97,8.93,8.88,8.84,8.79,8.75,8.7,8.66,8.61,8.57,8.52,8.48,8.44,8.4,8.36,8.32,8.28,8.24,8.21,8.17,8.14,8.11,8.08,8.05,8.02,7.99,7.96,7.93,7.9,7.87,7.84,7.81,7.78,7.75,7.72,7.69,7.65,7.62,7.58,7.54,7.5,7.46,7.42,7.37,7.33,7.28,7.23,7.18,7.12,7.07,7.01,6.96,6.9,6.84,6.79,6.73,6.67,6.62,6.56,6.51,6.46,6.41,6.36,6.32,6.28,6.24,6.21,6.18,6.16,6.15,6.14,6.14,6.14,6.15,6.18,6.21,6.24,6.29,6.35,6.42,6.49,6.58,6.68,6.79,6.91,7.04,7.18,7.33,7.49,7.66,7.85,8.04,8.24,8.46,8.68,8.91,9.15,9.4,9.66,9.92,10.19,10.46,10.74,11.03,11.32,11.61,11.9,12.19,12.49,12.78,13.07,13.36,13.65,13.93,14.21,14.48,14.75,15.01,15.25,15.49,15.72,15.94,16.15,16.34,16.52,16.69,16.84,16.98,17.1,17.21,17.3,17.37,17.43,17.47,17.49,17.49,17.48,17.45,17.4,17.33,17.25,17.15,17.03,16.9,16.75,16.59,16.42,16.23,16.02,15.81,15.58,15.35,15.1,14.84,14.58,14.31,14.04,13.76,13.48,13.19,12.91,12.62,12.33,12.05,11.77,11.5,11.23</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B332" t="str">
+        <v>[L_18_标记]</v>
+      </c>
+      <c r="C332" t="str">
+        <v>76.9uv</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B333" t="str">
+        <v>[R_19_名字]</v>
+      </c>
+      <c r="C333" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B334" t="str">
+        <v>[R_19_放大器]</v>
+      </c>
+      <c r="C334" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B335" t="str">
+        <v>[R_19_闪光]</v>
+      </c>
+      <c r="C335" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B336" t="str">
+        <v>[R_19_闪光背景]</v>
+      </c>
+      <c r="C336" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B337" t="str">
+        <v>[R_19_采样]</v>
+      </c>
+      <c r="C337" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B338" t="str">
+        <v>[R_19_分析时间]</v>
+      </c>
+      <c r="C338" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B339" t="str">
+        <v>[R_19_数据长度]</v>
+      </c>
+      <c r="C339" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B340" t="str">
+        <v>[R_19_详细数据(uv)]</v>
+      </c>
+      <c r="C340" t="str">
+        <v>12.83,8.53,2.93,-2.79,-7.39,-9.91,-9.79,-7,-2.09,3.98,10,14.77,17.34,17.18,14.33,9.36,3.25,-2.77,-7.51,-10.04,-9.89,-7.13,-2.36,3.4,8.92,13.03,14.83,13.89,10.33,4.8,-1.66,-7.81,-12.5,-14.84,-14.44,-11.47,-6.61,-0.91,4.38,8.13,9.49,8.12,4.23,-1.47,-7.87,-13.74,-17.96,-19.7,-18.68,-15.12,-9.81,-3.83,1.58,5.29,6.56,5.09,1.21,-4.33,-10.35,-15.68,-19.16,-20.07,-18.27,-14.04,-8.14,-1.91,3.76,7.45,8.57,6.98,2.82,-2.45,-8.43,-13.76,-16.25,-17,-14.36,-10.67,-4.95,1.32,6.86,10.39,10.69,7.97,3.4,-3.55,-10.35,-14.51,-18.85,-20.79,-19.04,-13.58,-5.56,-2.2,0.69,4.2,5.17,-2.15,-4.97,-10.09,-21.28,-23.54,-27.89,-28.12,-28.09,-25.93,-13.62,-14.84,-3.6,-7.69,-5.09,-6.87,-13.53,-19.86,-22.03,-31.99,-29.13,-27.82,-19.97,-16.06,-5.2,-0.79,-0.86,4.81,10.73,3.89,4.89,-2.56,-3.89,-6.36,-8.74,1.31,5.76,13.74,26.03,32.01,34.92,38.41,40.56,42.13,32.09,40.28,32.37,30.76,31.33,32,47.9,57.22,74.47,82.59,76.53,77.23,78.6,80.43,72.76,71.43,86.09,89.46,86.5,93.8,93.3,96.18,117.17,129.17,110.9,116.76,140.15,113.27,119.85,106.25,114.46,103.63,116.01,138.55,118.74,152.71,153.39,166.94,165.39,165.69,152.78,153.01,157.79,148.2,144.52,122.8,119.89,116.59,142.2,136.32,144.33,130.53,153.77,138.09,141.1,134.61,116.66,106.41,100.92,112.66,101.27,110.53,114.52,119.11,110.52,100.9,119.28,98.32,102.42,100.15,81.93,66.95,58.32,64.11,70.62,71.41,55.92,75.67,63.55,75.95,68.54,65.24,56.12,53.15,38.53,35.15,30.48,24.1,19.39,23.59,29.33,32.92,35.86,36.21,39.43,33.7,27.45,24.32,14.19,7.34,3.39,0.2,4.21,6.14,10.86,17.34,21.77,24.25,22.83,21.2,17.09,11.01,4.74,-0.67,-3.24,-5.67,-2.02,2.53,7.73,14.13,19.31,21.61,21.62,19.15,14.93,9.57,2.91,-1.43,-4.21,-4.77,-2.12,3,8.7,14.22,19.65,22.02,22.09,18.72,13.87,7.32,0.26,-3.48,-7,-6.99,-3.13,1.25,7.57,11.75,17.25,18.19,16.77,13.8,7.74,-0.63,-4.56,-10.21,-11.87,-12.81,-9.08,-4.66,-0.04,5.83,7.33,8.43,9.47,4.33,-1.5,-9.58,-15.25,-21.08,-22.47,-21.93,-15.7,-10.81,-6.9,0.86,0.1,0.22,-1.44,-0.07,-7.82,-14.75,-18.49,-21.68,-28.73,-23.14,-18.82,-16.85,-6.83,-4.53,1.58,1.05,2.61,-3.68,-7.56,-15.86,-19.4,-21.79,-21.43,-24.57,-14.69,-10.08,-6.3,2.69,0.11,-0.77,0,0.79,-4.6,-15.32,-16.41,-17.11,-20.07,-19.1,-17.62,-2.98,-6.03,4.57,5.52,4.87,3.6,0.28,-6.01,-16.09,-19.37,-22.36,-16.1,-16.52,-12.35,-9.67,2.37,5.11,5.42,5.72,-5.15,-1.63,-8.22,-16.16,-20.95,-29.05,-18.96,-27.89,-17.3,-12.06,-0.6,-2.05,-3.52,-3.74,-2.88,-10.75,-23,-28.73,-25.75,-28.46,-24.12,-28.82,-18.64,-15.41,-9.58,-4.14,-9.52,-8.9,-7.94,-13.77,-17.63,-32.46,-35.18,-30.38,-29.25,-29.28,-22.46,-15.3,-5.59,-4,-3.51,-10.3,-3.72,-12.44,-18.85,-21.19,-25.19,-28.94,-29.57,-20.34,-10.55,-5.8,0.43,6.29,0.67,2.23,0.98,-5.92,-8.26,-15.6,-15.81,-19.54,-12.45,-5.96,-7.61,5.4,7.87,14.3,13.98,10.38,4.45,-0.84,-4.99,-7.17,-13.68,-6.82,-5.88,1.54,4.83,10.8,15.23,20.55,18.06,16.35,9.92,5.28,-1.48,-7.27,-5.35,-6.04,-4.55,3.41,7.21,11.59,17.83,17.36,17.5,15.68,10.1,4.04,-3.09,-6.37,-9.59,-9.09,-6.98,0.14,6.41,9.83,15.7,16.94,14.06,10.64,4.22,-1.73,-6.26,-10.38,-12.94,-11.05,-6.42,-0.59,4.71,9.98,13.39,14.99,13.58,10.81</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B341" t="str">
+        <v>[R_19_标记]</v>
+      </c>
+      <c r="C341" t="str">
+        <v>a: 48.0ms -13.9uv b: 97.9ms 62.0uv</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B342" t="str">
+        <v>[L_19_名字]</v>
+      </c>
+      <c r="C342" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B343" t="str">
+        <v>[L_19_放大器]</v>
+      </c>
+      <c r="C343" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B344" t="str">
+        <v>[L_19_闪光]</v>
+      </c>
+      <c r="C344" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B345" t="str">
+        <v>[L_19_闪光背景]</v>
+      </c>
+      <c r="C345" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B346" t="str">
+        <v>[L_19_采样]</v>
+      </c>
+      <c r="C346" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B347" t="str">
+        <v>[L_19_分析时间]</v>
+      </c>
+      <c r="C347" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B348" t="str">
+        <v>[L_19_数据长度]</v>
+      </c>
+      <c r="C348" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B349" t="str">
+        <v>[L_19_详细数据(uv)]</v>
+      </c>
+      <c r="C349" t="str">
+        <v>9.88,14.73,19.65,24.17,27.87,30.41,31.57,31.25,29.51,26.56,22.73,18.41,14.08,10.19,7.14,5.26,4.75,5.65,7.87,11.19,15.27,19.66,23.92,27.59,30.28,31.69,31.66,30.15,27.31,23.38,18.72,13.79,9.03,4.92,1.81,-0.03,-0.42,0.58,2.89,6.18,10.06,14.12,17.88,20.88,22.88,23.49,22.65,20.56,16.97,12.57,7.89,2.96,-1.64,-5.56,-8.35,-9.33,-9.43,-7.63,-5.02,-1.29,2.84,7.71,10.49,12.98,15.38,15.65,13.88,10.98,5.94,0.57,-4.62,-8.16,-11.62,-16.44,-19.05,-17.31,-16.83,-12.88,-13.54,-6.36,-3.29,-2.25,4.04,3.02,3.62,6.03,7.95,0.7,0.4,-5.78,-5.48,-18.26,-12.4,-15.55,-18.01,-21.13,-12.83,-12.14,-2.97,2.42,0.47,12.09,18.36,20.21,22.54,24.69,21.95,20.79,22.2,16.87,21.42,18.52,12.65,20.06,14.46,29.06,29.25,32.13,47.41,41.15,51.92,62.33,67.72,67.32,71.56,73.79,73.03,70.83,66.51,70.59,66.62,71.78,75.12,70.96,79.2,87.82,79.52,92.01,94.34,113.47,115.99,122.59,116.55,127.37,119.62,116.97,136.25,109.5,120.32,114.37,124.67,115.25,117.18,104.56,123.24,143.24,124.21,140.65,135.67,156.13,145.35,152.48,171.48,146,144.85,177.24,163.73,155.78,161.8,152.25,124.99,151.4,136.47,138.7,130.32,135.13,142.22,153.37,136.75,144.66,149.34,141.67,162.06,150.6,144.48,138.06,146.23,121.09,113.2,126.5,102.6,95.47,92.5,96.32,94.78,83.54,89.81,103.91,104.39,91.69,94.21,103.28,103.31,89.56,93.05,78.43,74.83,71.08,61.99,56.83,53.2,46.31,40.02,44.36,43.54,35.34,46.14,43,48.92,47.42,51.93,46.72,46.36,43.85,37.46,33.73,25,20.59,17.26,12.94,6.21,3.71,3.37,2.7,7.14,8.69,11.34,16.17,20.3,22.75,25.1,24.67,24.12,21.36,18.2,13.46,9.54,4.3,0.69,-3.31,-4.63,-6.25,-4.11,-1.54,0.8,5.49,9.81,14.67,18.39,22.57,22.99,23.72,23.44,20.93,18.71,14.69,10.61,5.06,2.87,-1.67,-1.39,-2.41,-0.94,1.11,5,10.75,14.92,17.73,24.31,27.03,27.7,25.43,22.36,20.65,16.38,10.89,9.39,4.73,-1.33,-5.43,-2.88,-6.6,-2.32,-0.31,4,6.09,11.67,11.31,13.9,17.46,16.91,13.12,15.83,7.43,6.8,-2.2,-6.02,-12.6,-14.48,-17.56,-21.11,-17.73,-17.09,-12.81,-7.26,-4.29,-1.07,1.94,6.68,3.28,8.43,7.11,2.67,-5.81,-7.96,-13.51,-16.05,-19.2,-20.76,-29.15,-25.08,-23.48,-19.76,-15.9,-9.54,-9.37,-6.43,2.15,-3.91,1.45,-1.14,1.36,-3.09,-4.97,-12.27,-18.56,-14.74,-25.66,-27.28,-27.14,-25.79,-22.24,-12.77,-16.92,-8.96,-0.8,5.69,11.28,7.97,2.19,5.95,7.57,-4.83,-8.55,-2.72,-14.78,-8.72,-12.03,-14.27,-22.73,-16.1,-17.55,-13.34,-0.58,3.13,-4.25,10.4,11.05,8.37,4.87,6.29,6.43,1.54,-9.73,-13.79,-14.32,-14.69,-17.08,-27.09,-25.61,-21.64,-13.23,-12.03,-7.19,-1.93,-4.09,4.77,1.7,-0.16,7.24,-2.75,-1.85,-6.17,-13.97,-21.36,-16.45,-22.82,-23.23,-26.86,-20.27,-22.1,-21.91,-17.85,-12.45,-6.76,1.03,-1.8,6.97,1.68,1.38,3.5,-0.73,-3.67,-14.61,-18.38,-20.91,-20.56,-17.23,-18.05,-19.35,-15.07,-10.53,-5.33,4.61,4.81,11.78,13.7,16.15,17.68,16.22,12.15,6.81,4.47,-2.04,-1.16,-5.88,-9.2,-6.26,-3.14,-1.42,0.32,6.43,12.51,14.54,21.65,24.79,26,25.34,26.55,21.47,19.03,13.73,11.66,5.53,3.61,0.79,-2.15,-1.87,-1.41,2.65,5.58,9.88,15.51,18.92,21.16,23.28,23.92,23.75,22.04,18.57,14.49,9.14,4.95,-0.05,-3.41,-6.51,-6.9,-6.6,-4.4,-2.08,1.75,6.78,9.83,14.47,17.46,18.86,19.31,17.71,15.77,11.91</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B350" t="str">
+        <v>[L_19_标记]</v>
+      </c>
+      <c r="C350" t="str">
+        <v>a: 47.9ms -12.9uv b: 97.9ms 94.8uv</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B351" t="str">
+        <v>[R_20_名字]</v>
+      </c>
+      <c r="C351" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B352" t="str">
+        <v>[R_20_放大器]</v>
+      </c>
+      <c r="C352" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B353" t="str">
+        <v>[R_20_闪光]</v>
+      </c>
+      <c r="C353" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B354" t="str">
+        <v>[R_20_闪光背景]</v>
+      </c>
+      <c r="C354" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B355" t="str">
+        <v>[R_20_采样]</v>
+      </c>
+      <c r="C355" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B356" t="str">
+        <v>[R_20_分析时间]</v>
+      </c>
+      <c r="C356" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B357" t="str">
+        <v>[R_20_数据长度]</v>
+      </c>
+      <c r="C357" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B358" t="str">
+        <v>[R_20_详细数据(uv)]</v>
+      </c>
+      <c r="C358" t="str">
+        <v>26.75,24.92,27.1,33.22,41.53,38.77,29.59,27.59,25.7,21.88,34.92,37.94,39.16,31.26,31.17,19.57,21.2,30.3,37.59,40.66,40.59,35.36,25.64,25.52,22,33.43,36.53,38.12,37.94,29.39,23.4,22.46,27.38,29.97,37.77,34.02,31.73,23.94,16.99,16.5,19.07,23.6,27.16,25.11,15.62,8.05,6.42,4.85,8.72,13.44,13.81,8.2,-1.64,-6.5,-8.28,-6.16,-4.59,1.25,-1.29,-9.05,-15.99,-22.84,-24.42,-18.58,-17.9,-14.43,-14.76,-20.86,-27.88,-34.52,-32.69,-27.24,-16.56,-19.76,-16.27,-32.21,-35.76,-29.23,-29.52,-15.13,-15.45,-17.62,-16.24,-22.47,-27.11,-19.46,-17.41,-6.22,-2.81,-4.24,-6.08,-10.64,-9.49,-4.14,-0.23,9.99,9.46,11.11,6.76,3.79,3.99,11.28,17.82,24.94,22.14,17.81,13.31,10.15,16.9,20.9,27.95,31.83,28,22.4,17.88,15.76,21.8,28.59,33.87,31.81,29.63,22.38,17.83,19.45,23.53,29.07,34.11,32.66,24.45,22.38,18.01,22.71,27.45,36.22,35.13,28.97,24.29,18.05,22.64,27.29,35.86,39.38,40.74,31.01,30.08,23.9,24.23,28.71,40.11,43.34,36.58,32.87,27.01,29.79,30.54,35.93,42.04,41.19,37.76,31.63,28.09,25.63,32.64,35.88,37.06,36.24,30.88,22.14,16.99,19.24,20.65,27.19,26.9,21.46,12.61,8.42,3.87,4.26,10.86,12.38,9.13,2.48,-8.52,-13.26,-15.81,-10.2,-4.36,-3.96,-8.98,-12.33,-21.97,-28.89,-28.07,-20.31,-21.67,-14.19,-20.34,-30.35,-29.84,-31.52,-29.49,-26.02,-22.28,-21.27,-25.82,-33.53,-30.52,-32.83,-24.79,-17.78,-10.22,-14.23,-20.3,-20.48,-22.34,-18.57,-7.39,-3.85,2.51,-1.47,-7.26,-7.88,-6.12,1.75,10.4,14.09,17.28,12.77,7.84,7.07,9.36,16.6,24.5,27.99,25.33,20.6,18.76,16.95,22.15,28.63,35.28,34.77,33.23,26.12,23.15,24.18,29.21,38.95,38.64,36.57,35.16,30.63,21.89,28.36,34.4,45.82,44.56,37.13,35.26,31.83,27.61,34.01,40.5,42.22,44.26,39.45,33.03,27.15,31.12,34.64,46.54,46.35,43.36,35.48,33.83,32.16,35.12,38.34,41.42,45.63,41.41,33.41,30.36,26.94,31.47,37.13,39.26,38,30.34,23.79,19.28,20.21,22.08,25,28.04,21.35,12.83,8.8,4.49,3.84,9.52,11.14,11.51,3.7,-3.59,-9.89,-11.97,-9.53,-4.12,-4.67,-10.54,-15.81,-25.51,-25.7,-27.31,-23.4,-18.95,-14.79,-18.74,-27.1,-31.87,-33.36,-26.38,-25.57,-19.5,-22.65,-22.6,-30.82,-32.29,-30.48,-26.27,-16.98,-10.36,-8.31,-16.87,-22.05,-18.2,-11.97,-4.13,0.03,2.24,0.85,-3.07,-4.66,-4.7,0.96,13.6,19.78,20.18,15.49,11.16,8.59,11.24,19.38,30.02,31.73,30.29,22.9,19.75,19.72,26.37,31.85,35.96,39.51,33.46,29.73,23.74,23.19,31.57,37.77,40.64,37.74,32.09,23.36,22.69,26.46,34.12,33.76,42.92,35.01,29.35,23.41,22.24,27.9,32.85,34.48,32.65,33.16,29.59,21.56,26.2,29.04,33.15,39.13,34.08,28.17,27.69,25.52,25.7,31.32,41.38,41.72,40.33,29.03,24.04,26.46,32.32,35.86,38.73,38.34,34.24,26.25,23.03,21.77,29.56,31.53,33.86,31.15,22.27,15.91,13.08,15.69,20.09,24.71,21.14,14.21,5.98,2.25,0.47,3.16,8.33,6.91,7.17,-3.39,-11.79,-14.63,-16.06,-10.69,-8.12,-8.11,-10.31,-14.7,-21.78,-26.54,-19.34,-13.3,-17.68,-18.71,-17.63,-27.06,-31.14,-32.5,-18.67,-19.66,-16.47,-9.87,-22.2,-19.53,-25.31,-19.93,-9.62,-8.9,-6.5,-4.89,-12.24,-10.93,-13.66,-4.53,4.52,8.23,7.7,8.12,-0.94,2.53,3.02,12.04,17.41,22.77,22.8,14.24,13.2,10.49,16.22,23.59,31.61,31.06,26.76,23.06,16.74,18.91,27.45,30.77,37.58,34.42,31.07,24.24,20.57,25.28,32.12,40.22</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B359" t="str">
+        <v>[R_20_标记]</v>
+      </c>
+      <c r="C359" t="str">
+        <v>幅值: 30.7uv 相位: 51.3°</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B360" t="str">
+        <v>[L_20_名字]</v>
+      </c>
+      <c r="C360" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B361" t="str">
+        <v>[L_20_放大器]</v>
+      </c>
+      <c r="C361" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B362" t="str">
+        <v>[L_20_闪光]</v>
+      </c>
+      <c r="C362" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B363" t="str">
+        <v>[L_20_闪光背景]</v>
+      </c>
+      <c r="C363" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B364" t="str">
+        <v>[L_20_采样]</v>
+      </c>
+      <c r="C364" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B365" t="str">
+        <v>[L_20_分析时间]</v>
+      </c>
+      <c r="C365" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B366" t="str">
+        <v>[L_20_数据长度]</v>
+      </c>
+      <c r="C366" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B367" t="str">
+        <v>[L_20_详细数据(uv)]</v>
+      </c>
+      <c r="C367" t="str">
+        <v>11.37,13.52,26.31,25.62,22.47,19.38,13.15,13.44,17.29,21.85,23.5,27.37,30.61,29.25,25.17,19.33,19.61,20.64,24.86,30.87,34.45,30.44,34.16,28.19,17.96,14.89,15.73,16.9,22.22,22.62,21.23,21.1,13.26,7.05,0.96,-3.37,-2.51,1.92,4.06,4.93,1.27,-5.22,-13.23,-19.89,-23.32,-24.01,-22.27,-17.77,-16.33,-19.24,-25.81,-30.76,-40.64,-42.8,-38.12,-40.48,-36.58,-34.11,-34.4,-36.56,-40.28,-47.12,-52.66,-50.63,-41.91,-40.02,-32.63,-33.48,-36.28,-43.05,-47.07,-48.12,-42.97,-38.14,-31.91,-22.44,-26.6,-25.99,-30.24,-32.4,-36.36,-33.51,-27.15,-20.5,-16.09,-10.93,-15.47,-14.62,-18.9,-21.24,-18.69,-12.1,-6.93,-0.53,2.67,0.16,-7.3,-10,-13.69,-12.11,-7.35,-1.65,2.81,5.32,3.45,-0.97,-6.14,-10.04,-9.17,-4.88,0.66,3.97,10.45,8.34,5.77,-0.14,-5.41,-1.68,0.96,3.4,7.73,10.92,14.51,7.42,7.12,2.54,1.42,10.14,9.22,18.19,21.31,24.17,20.05,15.52,9.32,11.69,12.44,22.72,23.17,32.6,32.23,28.24,22.84,19.96,15.25,22.87,22.24,26.17,33.51,28.97,29.79,21.74,16.18,13.28,13.35,17.2,21.03,24.15,20.81,17.77,9.63,3.11,-0.39,-1.26,0.81,4.02,5.76,4.09,-1.13,-7.91,-15.63,-19.92,-20.73,-18.76,-15.92,-14.57,-14.81,-18.26,-26.39,-34.16,-39.65,-37.89,-35.28,-31.32,-27.72,-28.17,-28.34,-32.64,-38.7,-40.59,-39.9,-35.02,-29.9,-28.91,-25.27,-32.68,-30.21,-34.35,-41.02,-38.69,-34.7,-30.56,-26.26,-19.24,-18.24,-25.56,-26.53,-34.34,-30.3,-26.46,-20.46,-11.58,-14.87,-14.23,-11.8,-16.18,-23.55,-21.41,-19.59,-11.62,-6.07,-4.09,-3.64,-7.47,-12.64,-16.24,-16.85,-13.39,-7.45,-1.33,2.16,2.56,-0.7,-5.16,-9.79,-10.18,-7.13,-2.51,6.98,11.42,8.21,4.93,5.34,3.63,0.18,1,11.07,13.06,19.05,21.06,20.29,17.2,11.72,13.02,17.44,25.29,31.57,36.49,35.26,29.32,24.8,26.15,22,22.15,32.57,35.71,40.58,41.35,36.2,33.9,24.25,24.24,26.91,24.06,32.79,37.31,34.78,32.77,24.68,16.98,14.7,15.8,14.3,19.46,20.22,20.58,16.39,7.76,0.11,-4.55,-7.66,-6.75,-3.72,-1.66,-3.12,-6.6,-13.76,-21.37,-26.77,-31.53,-30.39,-26.58,-20.71,-22.52,-29,-35.44,-38.59,-41.52,-44.84,-46.15,-34.36,-36.05,-37.3,-34.82,-39.7,-44.89,-46.31,-51.27,-41.36,-37.01,-34.34,-30.21,-30.37,-31.18,-36.2,-38.86,-42.48,-38.51,-32.21,-19.98,-16.98,-14.37,-18.01,-24.6,-24.91,-25.03,-22.27,-13.99,-6.83,-6.29,-1.79,-6.81,-9.78,-10.62,-14.92,-11.14,-5.43,0.7,4.94,8.71,4.19,-0.06,-4.34,-5.91,-3.94,1.01,6.71,11.5,14.41,11.81,4.8,1.71,-1.95,2.58,7.17,13.03,19.5,20.41,18.69,11.21,9.99,4.37,3.35,12.21,21.93,28.03,28.87,24.75,16.81,12.51,11.07,16.07,20.89,23.39,31.02,32.06,33.66,25.8,27.11,17.63,17.92,25.2,28.18,35.87,37.72,36.92,27.83,23.92,15.68,18.63,18.68,22.95,24.12,28.79,26.83,22.05,14.93,7.9,3.77,7.01,9.39,13.48,14.14,10.74,3.7,-2.75,-9.79,-12.73,-12.74,-9.76,-6.74,-5.96,-7.39,-13.61,-20.67,-27.62,-30.47,-27.97,-28.89,-22.4,-22.48,-20.73,-25.55,-32.67,-35.83,-40.23,-35.94,-31.1,-29.24,-27.7,-20.05,-28.89,-32.64,-37.27,-37.38,-33.23,-33.97,-28.02,-21.5,-14.03,-18.57,-26.3,-30.48,-30.7,-23.53,-17.2,-18.39,-10.83,-4.2,-4.85,-15.02,-17.63,-15.93,-17.43,-12.08,-7.41,-1.74,-0.47,-2.45,-6.23,-10.93,-12.3,-11.99,-6.11,-2.41,2.56,5.59,3.6,-0.88,-5.69,-9.08,-7.67,-4.26,0.89,8.42,9.51,9.8,4.71,0.8,-2.04,-3.66,1.92,7.2,12.44,18.58,17.65,12.19,10,2.9,9.03</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B368" t="str">
+        <v>[L_20_标记]</v>
+      </c>
+      <c r="C368" t="str">
+        <v>幅值: 30.2uv 相位: 50.5°</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B369" t="str">
+        <v>[R_21_名字]</v>
+      </c>
+      <c r="C369" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B370" t="str">
+        <v>[R_21_放大器]</v>
+      </c>
+      <c r="C370" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B371" t="str">
+        <v>[R_21_闪光]</v>
+      </c>
+      <c r="C371" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B372" t="str">
+        <v>[R_21_闪光背景]</v>
+      </c>
+      <c r="C372" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B373" t="str">
+        <v>[R_21_采样]</v>
+      </c>
+      <c r="C373" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B374" t="str">
+        <v>[R_21_分析时间]</v>
+      </c>
+      <c r="C374" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B375" t="str">
+        <v>[R_21_数据长度]</v>
+      </c>
+      <c r="C375" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B376" t="str">
+        <v>[R_21_详细数据(uv)]</v>
+      </c>
+      <c r="C376" t="str">
+        <v>25.41,12.34,-1.52,0.76,15.71,23.83,14.25,-1.52,-4.16,9.08,20.87,15.72,-0.41,-7.69,2.55,16.86,16.67,1.75,-9.47,-3.21,12.24,17.02,4.78,-9.27,-7.61,7.48,16.76,8.39,-7.12,-10.21,3.04,15.93,12.24,-3.23,-10.77,-0.66,14.57,15.92,1.99,-9.28,-3.3,12.77,19.02,7.98,-5.95,-4.7,10.63,21.14,14.04,-1.19,-4.8,8.24,22,19.51,4.43,-3.77,5.77,21.19,23.5,10.08,-1.95,2.93,18.84,25.63,15.05,0.3,0.22,14.59,25.36,17.88,2.15,-3.21,7.81,20.53,18.61,1.61,-6.25,-1.13,14.49,16.92,1.89,-11.11,-8.09,6.41,11.76,-2.76,-18.2,-17.43,-4.02,4.07,-2.62,-24.06,-29.87,-15.15,-3.96,-3.33,-26.14,-36.51,-23.19,-12.06,-8.14,-26.54,-30.31,-31.36,-19.22,-10.03,-11.45,-28.73,-32.4,-19.17,-3.58,-4.65,-19.92,-26.99,-12.65,9.66,4.45,-4.48,-15.2,-8.13,15.61,26.02,15.73,1.76,10.48,23.28,37.12,29.17,28.06,22.48,33.13,54.52,53.64,38.86,31.03,49.09,63.55,82.6,72.75,53.16,57.69,78,98.17,88.96,81.17,84.74,109.93,106.34,117.33,108.85,107.61,124.4,139.38,111.92,107.88,112.2,111.99,125.55,145.19,147.37,110.35,117.19,132.01,147.22,127.31,141.93,146.95,161.98,139.92,154.6,146,117.77,123.1,156.45,153.96,150.66,110.61,134.98,144.25,164.91,146.04,105.02,116.88,144.08,146.38,115.19,106.36,105.52,133.21,128.19,123,111.9,81.39,92.34,106.05,99.89,78.22,82.62,77.29,104.8,105.51,72,57.01,58.16,75.02,83.47,60,53.91,39.77,63.57,65.57,63.44,45.86,33.65,43.57,47.49,52.58,35.49,25.55,29.99,38.49,39.19,29.49,17.19,14.06,26.76,39.9,29.36,10.22,6.4,19.8,33.76,27.72,11.74,4.46,12.4,27.37,26.29,13.23,1.05,5.24,21.39,26.63,14.39,-0.38,0.11,14.87,24.42,16.51,-0.18,-4.24,8.79,21.06,17.48,0.64,-8.09,1.28,16.11,16.74,2.69,-9.61,-5.26,10.23,16.46,4.07,-11.31,-11.86,2.29,12.3,5.24,-11.35,-15.86,-5.34,9.13,4.31,-11.61,-21.04,-13.12,2.06,4.31,-8,-21.09,-17.67,-3.18,2.21,-7.5,-23.15,-22.67,-9.34,1.88,-4.25,-22.93,-28.87,-15.75,-1.56,-3.46,-19.53,-28.89,-19.39,-5.25,0.33,-16.42,-28.07,-26.71,-8.22,0.13,-12.42,-26.73,-28.01,-13.05,-2.43,-2.9,-23.94,-29.27,-18.68,-2.3,-4.46,-16.39,-28.56,-22.98,-5.91,-1.74,-8.17,-28.62,-21.24,-5.39,-2.19,-7.99,-20.15,-28.26,-8.92,-0.05,-0.45,-17.86,-22.82,-13.3,-3.93,0.8,-15.53,-23.87,-22.4,-1.63,-5.31,-12.2,-32.77,-23.32,-16.07,-6.49,-6.41,-30.97,-28.14,-18.23,-7.19,-16.17,-28.49,-33.45,-26.54,-7.66,-12.79,-22.72,-40.3,-33.66,-22.04,-7.83,-23.16,-44.09,-41.59,-23.37,-10.71,-28.31,-44.91,-44.27,-33.27,-23.64,-23.96,-34.77,-47.66,-34.21,-20.73,-19.02,-33.82,-43.13,-35.86,-23.41,-21.16,-27.34,-45.6,-46.72,-33.28,-17.51,-20.49,-36.72,-49.64,-30.09,-15.36,-15.92,-34.06,-46.26,-32.55,-18.83,-14.17,-31,-43.54,-34.63,-22.91,-7.26,-18.49,-36.61,-35.72,-21.85,-7.74,-15.16,-25.17,-32.01,-18.9,-10.31,-4.11,-21.81,-29.57,-21.16,-4.07,-0.49,-17.46,-25.7,-27.46,-5.51,3.04,-12.62,-20.47,-22.27,-11.06,-1.98,-4.18,-19.18,-24.04,-18.94,0.96,-5.44,-13.97,-25.63,-19.61,-7.51,-0.18,-10.7,-26.5,-27.19,-10.83,-2.92,-10.17,-26,-29.6,-18.59,-1.92,-7.73,-25.34,-33.52,-23.74,-4.97,-7.56,-21.93,-33.4,-24.73,-9.91,-6.35,-15.86,-31.53,-29.52,-13.26,-5.07,-13.25,-28.26,-29.86,-19.68,-4.33,-8.41,-21.25,-30.44,-20.68,-4.92,-2.68,-15.55,-27.66,-24.13,-6.85,0.46,-9.15,-23.46,-24.16,-9.38,3.46,-2.54,-18.83,-23.52,-10.57,3.6,3.2,-11.66,-20.88,-11.58,4.3</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B377" t="str">
+        <v>[R_21_标记]</v>
+      </c>
+      <c r="C377" t="str">
+        <v>a: 51.8ms -28.3uv b: 106.3ms 69.9uv</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B378" t="str">
+        <v>[L_21_名字]</v>
+      </c>
+      <c r="C378" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B379" t="str">
+        <v>[L_21_放大器]</v>
+      </c>
+      <c r="C379" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B380" t="str">
+        <v>[L_21_闪光]</v>
+      </c>
+      <c r="C380" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B381" t="str">
+        <v>[L_21_闪光背景]</v>
+      </c>
+      <c r="C381" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B382" t="str">
+        <v>[L_21_采样]</v>
+      </c>
+      <c r="C382" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B383" t="str">
+        <v>[L_21_分析时间]</v>
+      </c>
+      <c r="C383" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B384" t="str">
+        <v>[L_21_数据长度]</v>
+      </c>
+      <c r="C384" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B385" t="str">
+        <v>[L_21_详细数据(uv)]</v>
+      </c>
+      <c r="C385" t="str">
+        <v>11.22,18.33,19.4,13.13,5.74,4.57,10.61,17.44,17.84,11.16,4,3.45,9.82,16.36,16.13,9.14,2.3,2.4,9.11,15.36,14.55,7.31,0.89,1.68,8.72,14.67,13.31,5.93,-0.02,1.48,8.83,14.47,12.59,5.12,-0.3,1.92,9.54,14.83,12.45,4.94,0.09,3,10.83,15.71,12.83,5.31,1.02,4.58,12.54,16.97,13.55,6,2.29,6.42,14.43,18.27,14.3,6.78,3.46,8.18,15.93,19.2,14.74,6.82,4.19,9.13,16.76,18.87,13.71,6.44,3.54,8.5,16.5,17.6,11.85,3.54,1.65,6.2,14.08,14.49,7.55,-2.03,-3.44,4.28,7.57,8.25,-0.91,-5.29,-11.16,-2.54,4.6,-1.88,-2.95,-13.42,-14.99,-7.73,1.15,-5.58,-9.04,-22.62,-24.06,-10.56,-8.56,-6.27,-17.85,-24.7,-14.71,-7.73,-6.35,-3.18,-15.08,-17.78,-5.26,-1.02,-0.05,1.09,3.05,-3.02,-3.16,9.96,17.12,18.83,11.95,12.68,16.37,27.14,32.9,30.93,31.4,29.35,39.26,50.65,53.2,49.93,44.83,50.11,62.17,68.02,68.25,72.28,67.3,58.61,70.75,86.26,103.58,88.05,85.13,96.94,99.08,119.02,124.97,111.53,110.32,95.04,106.87,131.07,135.08,116.75,112.34,110.36,117.79,154.29,145.78,151.23,126.17,141.5,155.55,141.7,167.65,131.51,143.84,152.5,156.79,147.48,159.44,135.94,145.16,141.59,152.7,144.86,143.74,158.68,130.36,153.41,142.66,138.31,140.25,149.33,125.1,115.78,139.16,134.75,141.07,126.5,121.52,111.53,115.76,111.64,106.16,102.05,84.61,92.56,100.85,98.57,99.26,88.3,83.62,85.3,79.52,94.63,83.1,62.22,55.52,58.67,68.78,69.89,62.04,53.56,44.55,47.22,58.25,62.18,48.91,45.14,35.58,38.4,44.92,45.13,37.17,33.91,30,33.74,38.7,38.97,29.35,23.97,20.8,24.72,30.8,32.66,26.25,16.06,15.24,21.61,29.5,29.78,21.47,14.54,14.54,19.57,26.46,24.6,17.19,11.18,11.43,17.63,23.92,21.98,14.91,8.24,8.91,15.58,21.55,18.89,12.13,5.78,6.86,14,19.49,15.9,8.64,2.51,5.76,12.63,15.9,13.96,5.37,1.47,4.22,10.29,14.12,10.1,2.3,-1.38,0.73,8.34,12.92,6.59,-0.98,-4.32,-0.02,5.52,11.4,5.42,-3.4,-5.92,-1.54,8.17,8.83,1.48,-3.95,-9.17,-3.68,4.02,7.14,0.79,-5.58,-6.9,0.41,7.52,4.11,-1.82,-7.86,-8.25,-3,7.52,4.13,-2.48,-6.76,-5.64,-2.42,6.9,6.69,1.97,-8.56,-7.23,-2,2.9,3.93,0.65,-9.04,-6.01,-2.47,5.39,3.31,-5.37,-10.69,-7.45,-1.86,2.97,7.67,-8.32,-6.81,-10.61,-2.22,-0.57,4.79,-5.79,-16.44,-11.47,-5.45,2.82,-5.08,-13.04,-9.21,-8.07,-4.4,-4.12,2.74,-9.23,-12.26,-13.97,-5.69,0.72,-10,-15.67,-22.71,-14.39,-2.52,0.11,-4.47,-13.07,-18.15,-15.63,-2.85,-2.19,-10.83,-14.35,-26.26,-20.34,-10.04,-0.4,-13.09,-20.14,-20.09,-19.88,-3.09,-4.25,-6.82,-16.67,-25.99,-12.94,-6.33,0.09,-15.5,-17.8,-21.5,-16.71,-10.02,-7.7,-7.03,-11.03,-11.9,-11.53,1.95,-1.01,-7.88,-19.18,-18.96,-7.13,4.59,3.92,-4.87,-10.85,-6.72,-5.67,-1.07,0.92,-4.53,-8.51,-11.56,0.13,2.92,5.96,-2.25,-9.3,-2.51,3.61,5.08,9.86,-2.42,-6.65,-2.83,4.26,8.61,7.4,-3.56,-4.46,-2.15,10.02,10,3.73,-3.88,-1.97,0.83,10.06,9.46,6.16,1.92,-4.77,0.13,6.64,13.03,7.04,0.19,-6.34,1.65,8.32,12.7,7.75,-1.05,-5.22,3.42,9.9,9.29,5.12,-3.17,-1.67,3.74,9.41,12.19,3.88,-1.58,-1.16,3.9,11.81,12.2,4.94,-0.45,-2.23,6.8,11.82,13.88,5.16,0.81,0.11,9.05,14.38,14.16,7.21,0.77,3.24,10.65,16.63,16.43,8.95,2.91,6.18,13.17,20.01</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B386" t="str">
+        <v>[L_21_标记]</v>
+      </c>
+      <c r="C386" t="str">
+        <v>a: 51.8ms -26.5uv b: 106.2ms 105.1uv</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B387" t="str">
+        <v>[R_22_名字]</v>
+      </c>
+      <c r="C387" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B388" t="str">
+        <v>[R_22_放大器]</v>
+      </c>
+      <c r="C388" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B389" t="str">
+        <v>[R_22_闪光]</v>
+      </c>
+      <c r="C389" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B390" t="str">
+        <v>[R_22_闪光背景]</v>
+      </c>
+      <c r="C390" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B391" t="str">
+        <v>[R_22_采样]</v>
+      </c>
+      <c r="C391" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B392" t="str">
+        <v>[R_22_分析时间]</v>
+      </c>
+      <c r="C392" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B393" t="str">
+        <v>[R_22_数据长度]</v>
+      </c>
+      <c r="C393" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B394" t="str">
+        <v>[R_22_详细数据(uv)]</v>
+      </c>
+      <c r="C394" t="str">
+        <v>15.7,40.64,34.71,14.26,11.47,35.16,34.61,14.82,13.07,29.48,34.44,14.18,5.47,26.17,31.4,15.15,6.53,29.61,35.19,15.19,8.38,26.22,35.09,13.98,5.54,28.96,31.56,11.36,6.53,25.95,31.47,11.8,4.54,27.25,29.6,9.25,4.78,22,28.85,8.64,-0.48,19.93,24.35,2.42,-3.87,11.95,18.42,-0.29,-10.03,6.01,11.92,-8.01,-21.33,-2.54,8.72,-15.37,-24.11,-11.34,2.1,-19.09,-33.22,-11.67,-2.11,-24.46,-33.85,-22,-10.79,-29.16,-41.22,-24.03,-15.77,-27.24,-43.92,-23.02,-8.86,-31.67,-36.3,-19.3,-11.77,-26.48,-33.52,-18.63,-2.54,-21.3,-32.67,-12.33,0.45,-14.95,-25.83,-5.71,9.77,-7.09,-16.55,0.08,15.22,3.16,-8.85,6.39,23.17,8.72,-1.55,13.66,27.39,14.79,2.21,18.44,34.94,18.93,7.84,20.41,37.84,24.55,11.49,26.33,39.07,25.93,10.84,28.27,42.51,29.54,14.3,29.1,41.61,28.24,13.43,29.05,46.6,31.37,16.13,29.41,39.86,28.9,11.43,22.3,44.12,34.09,11.42,25.3,45.5,37.1,14.8,22.35,45.37,33.7,15.15,24.05,41.57,31.64,14.44,21.58,40.5,30.53,13.04,22.41,38.3,30.31,8.18,18,33.4,25.55,3.98,9.44,29.61,20.29,-4.39,5.07,20.78,10.54,-8.25,-3.18,11.78,1.35,-18.9,-16.17,3.72,-3.5,-31.32,-24.51,-7.44,-13.17,-34.56,-36.76,-15.82,-22.66,-44.31,-43.91,-22.7,-27.5,-51.08,-47.43,-28.65,-32.39,-47.74,-51.2,-31.8,-27.82,-48.64,-44.84,-23.61,-27.94,-49.79,-44.12,-24.81,-21.27,-40.06,-37.94,-13.07,-16.74,-32.73,-29.35,-3.64,-3.3,-20.44,-16.73,6.52,8.98,-11.62,-7.34,15.68,18.21,1.03,0.19,25,27.87,7.9,9.86,31.16,36.67,17.05,14.56,38.17,39.19,21.44,19.94,40.26,45.21,22.75,20.91,41.35,42.36,23.73,20.53,41.28,47.31,21.54,17.85,37.85,44.04,23.19,14.79,37.96,42,19.25,13.17,32.06,37.85,18.11,5.06,31.68,35.08,10.46,4.84,23.53,27.35,12.97,4.7,20.89,28.51,11.34,0.03,20.8,27.98,7.87,-1.33,16.18,23.8,7.25,-2.39,15.52,22.5,4.88,-5.53,13.3,20.31,0.15,-7.85,10.42,17.39,-4.29,-11.56,3.42,11.67,-9.24,-17.91,0.28,7.1,-10.08,-22.12,-5.41,1.94,-14.69,-29.11,-15.29,-5.07,-20.07,-36.1,-21.92,-7.14,-26.89,-41.71,-25.19,-12.62,-26.59,-39.39,-27.21,-12.66,-36.26,-47.61,-31.21,-10.15,-31.89,-46.84,-27.73,-12.01,-25.59,-41.3,-20.78,-8.39,-21.82,-35.9,-24.08,-5.95,-16.33,-31.07,-13.95,2.05,-11.05,-23,-9.13,9.82,-2.51,-17.6,-2.53,16.77,4.58,-8.93,3.15,20.32,10,-5.23,10.62,27.87,15,-1.12,11.41,31.74,16.64,0.95,14.25,34.52,18.26,3.83,14.14,34.29,23.91,3.72,16.35,35.42,19.57,0.21,12.58,34.63,24.55,3.64,16.33,30.12,24.52,2.05,13.66,27.76,21.76,2.04,9.07,28.73,20.06,3.34,11.71,36.1,22.4,7.84,13.35,29.21,24.61,7.25,12.41,31.97,28.42,4.28,11.34,32.81,26,7.39,12.18,32.26,25.66,4.24,9.58,30.45,24.28,1.93,5.73,25.95,21.1,-3.98,2.94,19.75,11.76,-7.01,-7.8,11.57,9.35,-13.89,-12.88,4.72,-1.39,-27.39,-22.9,-6.27,-13.89,-31.52,-34.95,-17.77,-22.05,-40.11,-39.78,-22.07,-26.28,-47.7,-49.88,-29.42,-30.06,-51.77,-51.8,-28.61,-35.8,-51.38,-53.99,-34.03,-35.33,-57.36,-53.61,-29.2,-26.66,-46.86,-47.29,-24.03,-20.7,-40.21,-43.59,-17.66,-13.97,-34.3,-33.99,-9.11,-3.29,-21.8,-23.36,-1.09,5.46,-14.32,-13.63,9.71,14.05,-4.1,-3.66,18.38,21.72,3.58,-0.49,23.09,31.1,10.27,9.84,26.65,34.17,18.4,9.64,33.19,36.61,19.56,16.74,31.49,42.69,20.98,15.07,34.32,37.54,24.11,13.46,28.2</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B395" t="str">
+        <v>[R_22_标记]</v>
+      </c>
+      <c r="C395" t="str">
+        <v>幅值: 29.8uv 相位: 50.9°</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B396" t="str">
+        <v>[L_22_名字]</v>
+      </c>
+      <c r="C396" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B397" t="str">
+        <v>[L_22_放大器]</v>
+      </c>
+      <c r="C397" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B398" t="str">
+        <v>[L_22_闪光]</v>
+      </c>
+      <c r="C398" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B399" t="str">
+        <v>[L_22_闪光背景]</v>
+      </c>
+      <c r="C399" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B400" t="str">
+        <v>[L_22_采样]</v>
+      </c>
+      <c r="C400" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B401" t="str">
+        <v>[L_22_分析时间]</v>
+      </c>
+      <c r="C401" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B402" t="str">
+        <v>[L_22_数据长度]</v>
+      </c>
+      <c r="C402" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B403" t="str">
+        <v>[L_22_详细数据(uv)]</v>
+      </c>
+      <c r="C403" t="str">
+        <v>23.37,15.66,2.83,3.02,20.49,22.08,14.33,0.81,10.75,21.56,18.36,-0.21,8.01,22.01,25.87,5.16,0.09,11.21,17.45,6.29,-3.49,1.89,13.21,9.96,-5.27,-7.05,4.71,6.75,-6.68,-17.58,-9.88,-1.19,-10.15,-25.89,-25.06,-12.43,-13.21,-30.46,-37.17,-24.91,-18.88,-31.21,-46.43,-36.38,-24.69,-34.21,-49.4,-48.44,-39.29,-29.93,-45.42,-52.2,-46.16,-36.34,-42.91,-60.69,-50,-33.6,-37.07,-51.2,-54.76,-39.28,-32.12,-43.77,-52.14,-40.13,-32.04,-32.78,-43.57,-40.93,-26.85,-19.49,-32.94,-42.38,-25.74,-19.49,-26.67,-35.83,-29.98,-16.22,-14.24,-29.13,-31.14,-15.99,-9.2,-20.47,-28.85,-17.2,-4.35,-8.49,-24.5,-21.64,-6.52,-3.06,-16.97,-23.84,-11.16,-1.38,-8.89,-22.63,-14.57,-0.07,-2.14,-14.61,-20.42,-2.97,3.04,-8.07,-16.23,-7.42,5.75,-0.39,-16.63,-8.24,4.69,7.85,-0.15,-6.7,2.3,19.29,7.9,-3.06,0.76,18.81,18.15,0.25,5.85,20.62,26.43,10.32,4.97,18.75,25.82,25.08,9.82,13.73,24.47,28.25,11.71,11.22,21.65,30.37,18.8,7.6,10.99,22.49,22.15,5.37,4.19,13.91,17.54,1.45,-5.61,2.29,10.94,0.89,-14.26,-12.88,-1.71,-4.48,-20.63,-28.51,-16.71,-11.42,-25.01,-38.65,-32.99,-22.78,-30.2,-46.62,-49.81,-35.23,-37.61,-50.1,-57.87,-47.66,-35.66,-46.86,-63.02,-58.94,-41.83,-45.71,-57.53,-65.96,-45.52,-41.72,-54.88,-59.18,-55.57,-42.5,-45.5,-59.5,-54.34,-36.18,-37.43,-50.09,-54.58,-41.73,-24.26,-36.09,-44.54,-37.32,-22.59,-22.4,-35.98,-37.45,-22.26,-12.53,-24.42,-36.04,-22.64,-8.07,-12.71,-26.34,-22.43,-5.3,-3.23,-15.41,-21.6,-8.31,3.36,-5.94,-17.16,-10.51,5.18,3.19,-9.27,-10.69,3.79,10.01,-3.08,-11.34,-1.01,15.84,11.02,-7.48,-1.38,15.16,13.18,0.67,-5.27,14.87,23.45,13.97,1.5,7.54,21.41,24.65,8.86,7.18,20,27.67,12.39,4.56,15.53,28.69,18.86,6.73,8.21,24.69,30.11,12.65,7.58,18.64,23.36,11.98,6.35,10.3,20.27,15.67,-2.92,-0.74,8.34,12.16,-4.88,-12.36,-2.08,4.64,-5.39,-20.71,-17.45,-6.05,-9.41,-27.24,-32.6,-21.33,-17.11,-31.49,-42.89,-38.6,-26.67,-33.82,-50.5,-50.44,-38.27,-35.72,-50.52,-60.75,-49.48,-37.71,-47.38,-58.28,-57.33,-41.5,-43.98,-54.97,-62.05,-43.67,-37.63,-50.63,-56.63,-47.76,-33.41,-41.6,-56.38,-50.46,-34.68,-25.85,-46.24,-43.27,-34.51,-20.89,-27.75,-43.6,-33.24,-19.14,-20.24,-28.42,-32.18,-15.66,-11.18,-19.13,-29.61,-14.95,-5.05,-7.56,-21.73,-18.91,-3.47,-1.09,-13.51,-20.75,-6.73,3.47,-7.51,-18.15,-11.66,2.89,-0.7,-14.6,-16.79,-2.41,3.25,-7.77,-19.06,-5.76,5.19,-4.43,-14.94,-13.87,6.85,3.82,-7.39,-13.67,0.16,9.77,0.88,-10.88,-0.79,13.41,10.85,-9.41,-4.06,8.91,15.41,4.14,-6.22,11.56,22.32,15.45,2.27,9.52,18.08,23.58,7.16,2.54,20.12,27.23,10.42,4.39,12.29,20.1,18.15,1.96,-0.01,16.24,16.2,4.55,-3.47,3.7,14.61,6.31,-10.02,-7.64,5.71,1.67,-14.62,-19.58,-7.51,-3.82,-16.88,-30.51,-23,-12.4,-21.34,-38.47,-37.24,-22.57,-22.27,-37.32,-47.56,-36.1,-28.23,-41.64,-51,-49.52,-34.39,-41.37,-53.11,-56.73,-43.71,-33.23,-53.86,-58.19,-47.86,-41.59,-40.19,-53.95,-51.03,-37.78,-32.89,-47.08,-51.79,-42.43,-29.11,-40.43,-48.57,-37.9,-26.16,-26.62,-42.83,-43.44,-26.88,-20.94,-32.04,-40.63,-28.39,-17.18,-19.37,-33.49,-27.28,-12.39,-13.44,-24.6,-27.27,-15.34,-4.89,-16.36,-26.26,-18.08,-2.99,-6.82,-19.58,-19.52,-3.01,0.84,-13.28,-18.34,-6.73,2.96,-2.57,-15.98,-8.59,3.22,7.05,-3.81,-10.26,8.62,18.72,-0.13,-6.44,5.44,22.39,15.57,4.42,7.13,22.81,27.63,7.38,5.94</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B404" t="str">
+        <v>[L_22_标记]</v>
+      </c>
+      <c r="C404" t="str">
+        <v>幅值: 29uv 相位: 50.4°</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B405" t="str">
+        <v>[R_23_名字]</v>
+      </c>
+      <c r="C405" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B406" t="str">
+        <v>[R_23_放大器]</v>
+      </c>
+      <c r="C406" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B407" t="str">
+        <v>[R_23_闪光]</v>
+      </c>
+      <c r="C407" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B408" t="str">
+        <v>[R_23_闪光背景]</v>
+      </c>
+      <c r="C408" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B409" t="str">
+        <v>[R_23_采样]</v>
+      </c>
+      <c r="C409" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B410" t="str">
+        <v>[R_23_分析时间]</v>
+      </c>
+      <c r="C410" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B411" t="str">
+        <v>[R_23_数据长度]</v>
+      </c>
+      <c r="C411" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B412" t="str">
+        <v>[R_23_详细数据(uv)]</v>
+      </c>
+      <c r="C412" t="str">
+        <v>-14.58,0.33,-7.54,-16.64,-2.03,-2.98,-16.53,-5.52,0.69,-14.2,-9.26,2.75,-10.06,-12.26,2.84,-4.92,-13.72,1.11,0.21,-13.12,-1.89,4.34,-10.44,-5.29,6.71,-6.09,-8.13,6.97,-0.89,-9.61,5.22,4.15,-9.21,2.03,8.04,-6.87,-1.73,10.03,-3.01,-5.11,9.76,1.57,-7.26,7.36,5.92,-7.63,3.42,9,-6.18,-1.24,10.15,-3.32,-5.51,8.92,0.26,-8.9,5.52,3.62,-10.45,0.55,5.4,-9.86,-5.55,5.57,-8.55,-11.16,2.82,-6.33,-15.89,-1.84,-3.15,-19.26,-7.05,-3.59,-19.36,-13.9,-6.71,-20.49,-23.54,-10.27,-18.01,-27.33,-14.03,-19.92,-28.31,-24.12,-13.6,-30.73,-24.82,-15.1,-35.54,-35.53,-18.09,-27.78,-36.91,-23.84,-25.51,-35.8,-26.02,-16.98,-30.03,-25.81,-16.7,-29.34,-21.58,-13.93,-17.2,-22.31,-0.61,-10.77,-21.53,-0.23,5.33,-10.89,-0.28,15.25,7.71,11.04,21.31,22.09,10.46,25.74,27.4,15.96,39.6,50.61,30.85,36.94,53.88,40.12,46.55,57.82,63.88,53.34,66.72,65.76,53.49,86.14,79.63,72.22,75.06,99.44,76.15,93.03,106.94,87.93,89.58,109.99,109.92,110.58,99.97,130.06,111.89,110.13,116.47,131.87,109.11,117.95,129.29,134.39,137.73,118.21,114.43,151.31,136.19,126.88,131.54,127.58,144.88,113.52,160.4,139.94,121.32,139.95,116.32,108.71,145.42,127.59,130.96,110.02,137.49,106.47,121.09,142.08,108.81,114.48,122.97,108.15,92.18,112.33,108.35,100.06,103.85,95.07,91.99,98.09,112.98,94.72,76.17,94.49,94.18,69.42,75.9,75.41,71.1,66.06,87.28,68.85,51.21,66.04,61.69,53.32,69.05,54.16,48.25,56.41,49.27,33.57,44.63,54.31,33.86,33.53,41.53,30.96,24.21,34.52,30.46,20.89,26.6,29.03,16.32,19.9,30.21,15.34,13.32,24.58,16.18,6.03,20.65,16.34,2.42,13.35,16.36,0.43,6.26,15.87,0.95,0.14,12.99,2.16,-4.51,10.49,6.03,-7.73,4.18,7.92,-7.69,-1.44,7.71,-6.41,-5.81,7.06,-3.3,-10.59,4.09,0.35,-12.42,0.54,4.41,-11.32,-2.87,6.02,-9.21,-7.92,5.02,-3.37,-10.4,2.99,-0.31,-11.73,0.73,4.41,-8.8,-4.67,6.25,-8.44,-7.81,8.97,-2.5,-9.9,3.8,0.33,-11.75,2.31,4.85,-8.66,-1.64,10.54,-8.42,-6.9,8.19,-1.48,-10.31,7.68,1.39,-8.96,0.83,7.78,-8.97,0.12,10.09,-7.55,-10.24,6,-3.8,-12.06,3.41,1.2,-15.52,-4.14,0.22,-11.03,-3.18,3.86,-12.27,-11.33,0.71,-9.53,-17.89,1.35,-3.43,-22.65,-8.84,-6.69,-22.67,-18.09,-6.57,-21.62,-19.99,-7.93,-14.62,-24.69,-10.01,-16.24,-22.89,-15.24,-6.6,-28.09,-13.86,-4.12,-22.26,-20.02,-7.5,-18.01,-27.71,-10.31,-10.18,-32.97,-12.5,-18.01,-29.89,-15.55,-8.14,-28.43,-20.51,-14.21,-22.4,-19.67,-4.77,-18.4,-27.29,-7.94,-13.47,-21.69,-16.98,-4,-22.2,-17.28,-5.91,-17.97,-21.26,-0.91,-6.11,-27.32,-9.76,-9.35,-17.29,-12.45,0,-10.42,-13.45,-2.85,-7.06,-22.67,3.34,-2.98,-20.64,-2.76,1.31,-15.53,-6.84,1.63,-11.02,-14.12,-1.15,-9.27,-19.24,2.88,-2,-15.03,-0.34,0.36,-18.4,-11.01,4.89,-16.31,-7.37,-2.85,-9.33,-19.37,0.2,-0.87,-16.78,-2.79,2.98,-20.03,-8.8,1.1,-17.28,-12.25,3.73,-8.2,-15.52,3.82,-3.17,-13.69,0.74,-2.05,-13.24,-7.08,3.78,-14.57,-7.16,1.84,-3.87,-13.51,1.34,-3.26,-10.82,-0.25,2.2,-12.51,0.85,9.91,-7.21,-6.09,10.15,0.57,-4.71,10.09,5.27,-7.95,5.97,10.94,-5.78,4.49,12.85,0.75,1.98,16.64,6.68,1.15,14.66,10.42,0.04,13.59,15.59,1.17,11.23,20.34,4.11,7.94,21.4,9.04,5.01,20.94,15.1,3.66,17.21,18.18,5.01,13.45,21.55,6.25,9.23,21.57,10.9,5.83,20.25,14.75</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B413" t="str">
+        <v>[R_23_标记]</v>
+      </c>
+      <c r="C413" t="str">
+        <v>a: 55.4ms -33.4uv b: 113.7ms 72.2uv</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B414" t="str">
+        <v>[L_23_名字]</v>
+      </c>
+      <c r="C414" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B415" t="str">
+        <v>[L_23_放大器]</v>
+      </c>
+      <c r="C415" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B416" t="str">
+        <v>[L_23_闪光]</v>
+      </c>
+      <c r="C416" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B417" t="str">
+        <v>[L_23_闪光背景]</v>
+      </c>
+      <c r="C417" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B418" t="str">
+        <v>[L_23_采样]</v>
+      </c>
+      <c r="C418" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B419" t="str">
+        <v>[L_23_分析时间]</v>
+      </c>
+      <c r="C419" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B420" t="str">
+        <v>[L_23_数据长度]</v>
+      </c>
+      <c r="C420" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B421" t="str">
+        <v>[L_23_详细数据(uv)]</v>
+      </c>
+      <c r="C421" t="str">
+        <v>20.16,11.82,12.99,20.66,15.88,10.31,17.57,19.8,11.52,13.09,20.71,15.75,10.5,17.99,19.99,11.78,13.73,21.28,16.14,11.2,18.88,20.62,12.46,14.77,22.21,16.85,12.19,20.02,21.45,13.31,15.93,23.2,17.59,13.19,21.11,22.18,14.04,16.93,23.98,18.08,13.87,21.84,22.51,14.31,17.4,24.17,17.96,13.98,21.81,22.13,13.92,16.99,23.55,16.95,13.17,20.94,20.39,12.25,15.4,21.73,14.31,10.57,18.82,17.18,9.28,12.78,17.67,10.35,7.14,13.36,13.62,5.29,7.02,14.26,6.66,2.49,8.7,5.43,-2.17,1.51,6.9,-3.71,-7.46,5.1,-0.23,-6.09,-7.44,4,-4.84,-14.05,-2.4,-2.29,-11.27,-5.19,-0.15,-10.75,-12.98,-0.57,-1.23,-5.72,-1.66,2.96,0.34,-1.62,3.16,-1.41,-2.6,5.62,14.21,10.01,7.01,15.45,18.68,9.97,17.93,32.54,24.74,20.02,34.05,35.05,26.07,46.3,53.83,48.65,46.7,59.33,50.24,63.06,65.71,77.06,71.96,68.87,75.98,75.67,75.29,88.46,94.71,96.03,91.73,112.1,92.36,88.06,93.32,99.06,113.82,122.32,127.39,114.55,112.46,130.62,132.4,117.39,136.67,139.95,129.6,134.52,142.49,136.02,129.78,151.26,128.36,155.85,154.51,146.86,151.34,155.85,136.69,137.3,157.49,141.6,132.92,167.22,145.47,161.27,152.08,154.15,129.09,140.77,151.8,130.51,134.74,124.51,125.31,139.55,140.48,136.99,122.66,132.82,147.11,135.98,123.05,134.41,134.47,122.73,113.62,111.1,112.14,98.54,119.78,108.07,102.77,91.35,100.6,99.2,82.78,84.76,82,78.34,73.49,89.31,71.95,70.5,76.06,73.64,61.37,65.71,66.71,58.01,51.01,59.26,63.18,48.48,53.99,53.45,48.16,38.45,45.08,46.41,34.64,40.3,41.94,31.51,31.75,37.21,33.68,23.72,30.61,33.41,26.07,21.61,29.81,25.46,17.93,19.72,24.31,17.82,14.55,22.54,19.97,10.27,15.17,20.31,12.62,8.44,16.22,14.09,6.4,11.08,14.18,7.75,5.29,13.15,10.42,2.5,7.94,12.16,4.51,2.28,9.99,6.91,0.64,5.81,10.49,2.79,1.67,7.8,4.96,-0.16,4.31,7.46,0.59,-1.04,7.84,5.9,-0.93,5.13,8.89,0.75,-1.33,6.8,4.13,-1.35,3.97,6.54,-0.61,-0.99,7.24,1.83,-3.37,5.37,6.62,0.27,-3.17,7,2.25,-4.07,4.71,7.02,-4.75,0.1,3.42,3.61,-5.74,0.12,2.96,-4.85,-3.48,6.31,-0.52,-7.89,-2.59,4.86,-5.26,-9.16,0.12,-5.25,-11.33,-3.47,-4.3,-7.05,-7.39,0.48,-10.18,-9.37,-2.9,-9.01,-10.08,-11.75,-8.59,-8.5,-15,-11.58,-5.57,-15.02,-18.88,-11.7,-14.36,-15.92,-13.94,-15.53,-23.5,-17.55,-14.58,-19.86,-22.54,-12.31,-9.72,-15.69,-16.98,-14.32,-12.73,-25.04,-18.77,-8.09,-18.38,-16.65,-12.25,-16.94,-24.55,-7.86,-9.52,-27.38,-22.01,-17.2,-16.15,-24.33,-11.5,-17.86,-22.01,-12.45,-12.7,-11.97,-19.79,-5.56,-15.84,-17.9,-9.75,-13.34,-15.82,-20.89,-11.82,-7.36,-13.22,-16.18,-1.62,-10.39,-19.48,-2.82,-8.73,-14.94,-14.19,-8.1,-7.61,-13.32,-12.11,-10.44,-16.69,-12.22,-6.39,-17.16,-18.82,-2.62,-5.04,-16.69,-9.16,-1.48,-14.29,-18.13,-7.9,-7.6,-10.27,-11.83,-8.25,-12.92,-12.04,-9.09,-6.15,-18.24,-9.96,-4.88,-7.91,-13.59,-3.45,-6.23,-15.13,-7.57,-5.16,-10.66,-11.39,-1.89,-7.08,-12.99,-5.56,-4.31,-11.76,-13.07,-1.73,-6.61,-12.5,-4.28,0.75,-6.78,-7.37,-0.72,-3.91,-10.23,-4.18,2.19,-6.59,-6.55,2.46,-2.62,-6.82,-3.04,1.7,-6.08,-4.16,5.25,0.5,-7.12,1.39,3.28,-3,-2.13,5.65,1.8,-3.44,2.37,5.45,-1.37,-1.27,7.84,2.97,-3.06,5.03,7.14,-0.46,0.87,8.38,3.86,-1.1,6.41,7.85,0.58,2.35,9.98,3.97,-0.31,5.99,8.59</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B422" t="str">
+        <v>[L_23_标记]</v>
+      </c>
+      <c r="C422" t="str">
+        <v>a: 55.4ms -34.7uv b: 113.6ms 89.9uv</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B423" t="str">
+        <v>[R_24_名字]</v>
+      </c>
+      <c r="C423" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B424" t="str">
+        <v>[R_24_放大器]</v>
+      </c>
+      <c r="C424" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B425" t="str">
+        <v>[R_24_闪光]</v>
+      </c>
+      <c r="C425" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B426" t="str">
+        <v>[R_24_闪光背景]</v>
+      </c>
+      <c r="C426" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B427" t="str">
+        <v>[R_24_采样]</v>
+      </c>
+      <c r="C427" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B428" t="str">
+        <v>[R_24_分析时间]</v>
+      </c>
+      <c r="C428" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B429" t="str">
+        <v>[R_24_数据长度]</v>
+      </c>
+      <c r="C429" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B430" t="str">
+        <v>[R_24_详细数据(uv)]</v>
+      </c>
+      <c r="C430" t="str">
+        <v>11.4,-4.28,-13.06,12.13,-12.51,-2.76,12.05,-10.11,4.6,4.12,-13.38,8.82,-3.37,-8.84,12.48,-8.76,0.8,8.49,-11.41,6.75,2.8,-11.61,9.07,-8.3,-8.45,6.5,-13.47,-3.21,0.89,-19.19,-0.54,-12.33,-21.21,-3.25,-21.14,-20.86,-9.77,-30.72,-18.39,-22.12,-36.71,-20.67,-32.77,-40.33,-26.29,-44.59,-38.98,-31.69,-54.98,-41.41,-44.62,-56.82,-40.88,-54.87,-58.03,-39.83,-62.36,-54.18,-48.84,-67.27,-45.86,-60.09,-68.08,-41.59,-58.67,-57.27,-46.96,-65.15,-46.77,-43.89,-59.23,-36.63,-48.85,-48.04,-29.95,-48.89,-38.21,-27.74,-44.74,-24.62,-26.54,-34.07,-11.73,-23.23,-20.47,-4.37,-22.47,-9.45,-1.03,-16.89,5.51,-2.4,-6.08,12.3,-2.53,3.19,13.78,-1.67,16.19,15.69,0.63,20.83,12.36,7.18,24.95,7.53,12.5,25.4,3.57,19.57,17.82,5.93,28.03,11.32,12.57,22.86,7.33,14.54,22.7,5.91,18.86,13.33,3.31,17.47,2.39,7.82,16.91,-4.81,14.91,16.68,-6.41,16.26,4.7,0.05,19.63,-3.51,4.14,12.01,-7.86,11.17,6.4,-7.72,11.45,-6.61,-5.51,7.84,-13.51,-1,2.29,-15.85,-0.04,-9.25,-20.15,1.52,-20.24,-14.42,-6.71,-28.52,-14.97,-15.25,-31.13,-15.19,-27.64,-37.57,-20.49,-38.83,-32.05,-26.43,-47.11,-31.68,-36.92,-49.48,-32.06,-52.28,-53.63,-34.76,-60.46,-43.19,-44.82,-62.84,-38.85,-49.2,-57.99,-35.55,-54.88,-55.16,-39.44,-52.97,-44.85,-41.4,-50.45,-29.58,-43.61,-42.37,-23,-41.16,-33.88,-23.94,-39.26,-20.12,-22.45,-32.06,-7.77,-21.28,-17.95,-1.44,-18.36,-4.27,-0.9,-14.56,6.24,1.77,-5.03,14.92,0.94,6.89,19.67,-1.15,18.38,19.89,3.87,21.98,12.26,9.78,29.91,4.89,18.24,26.19,3.8,22.94,19.19,6.36,23.78,9.63,11.07,21.24,4.49,17.25,18.64,-1.77,21.2,12.78,4.93,23.72,3.09,8.3,13.06,-6.88,8.6,8.63,-4.12,13.8,2.95,0.34,17.18,-3.05,3.17,11.67,-9,10.77,9.1,-5,14.33,2.29,1.52,15.67,-4.85,8.28,11.42,-8.41,12.12,4.02,-4.47,13.53,-4.78,-1.82,10.64,-8.82,1.75,4.69,-15.34,4.23,-9.56,-13.06,3.92,-17.05,-7.17,-5.88,-25.38,-9.5,-14.6,-30.87,-8.51,-30.68,-25.91,-15.67,-36.96,-28.25,-23.99,-44.85,-29.42,-38.11,-45.25,-24.58,-45.57,-39.41,-33.58,-50.41,-37.92,-35.53,-48.4,-27.73,-44.65,-49.09,-30.45,-50.57,-38.25,-32.55,-49.28,-31.86,-32.85,-43.76,-17.12,-35.71,-33.04,-16.06,-35.55,-19.01,-13.32,-29.61,-7.75,-14.51,-18.92,2.37,-13.99,-6.78,7.07,-12.12,4.15,5.94,-5.3,16.29,5.03,1.46,18.67,2.18,11.78,23.87,3.93,24.84,22.1,6.33,30.01,13.86,15.64,29.36,13,26.22,26.81,9.69,30.11,20.39,10.54,28.42,13.16,22.96,26.44,12.09,25.8,19.72,8.82,34.63,18.36,8.31,30.06,10.37,15.58,30,5.85,28.26,22.57,9.18,31.49,13.08,13.24,27.43,6.91,20.95,24.67,7.39,24.77,15.6,7.34,25.67,7.76,12.59,22.54,1.29,15.21,12.98,-4.64,14.45,0.03,-5.44,10.05,-11.63,-3.99,3.58,-16.52,-1.35,-8.99,-23.99,-4.41,-24.67,-24.34,-9.91,-33.33,-23.39,-22.36,-37.58,-25.22,-33.89,-40.6,-23.76,-41.38,-40.65,-31.28,-49.76,-36.15,-34.38,-49.44,-35.97,-44.96,-48.18,-31.71,-53.32,-38.94,-31.44,-49.52,-31.21,-34.16,-48.5,-27.15,-36.53,-34.14,-18.62,-36.65,-20.51,-16.54,-32.62,-6.41,-13.57,-18.48,2.94,-14.25,-6.43,6.98,-10.36,8.27,10.77,-2.82,20.12,8.96,7.42,28.85,9.96,21.96,31.9,11.36,32.79,29.31,18.03,37.99,23.99,27.02,40.95,19.09,36.49,37.65,22.75,38.73,30.69,19.8,44.09,22.48,26.76,35.67,14.52,34.35,27.86,17.39,33.53,17.49,21.88,32.35,17.33,24.69,26.8,12.78,29.26</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B431" t="str">
+        <v>[R_24_标记]</v>
+      </c>
+      <c r="C431" t="str">
+        <v>幅值: 30.2uv 相位: 51.1°</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B432" t="str">
+        <v>[L_24_名字]</v>
+      </c>
+      <c r="C432" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B433" t="str">
+        <v>[L_24_放大器]</v>
+      </c>
+      <c r="C433" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B434" t="str">
+        <v>[L_24_闪光]</v>
+      </c>
+      <c r="C434" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B435" t="str">
+        <v>[L_24_闪光背景]</v>
+      </c>
+      <c r="C435" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B436" t="str">
+        <v>[L_24_采样]</v>
+      </c>
+      <c r="C436" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B437" t="str">
+        <v>[L_24_分析时间]</v>
+      </c>
+      <c r="C437" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B438" t="str">
+        <v>[L_24_数据长度]</v>
+      </c>
+      <c r="C438" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B439" t="str">
+        <v>[L_24_详细数据(uv)]</v>
+      </c>
+      <c r="C439" t="str">
+        <v>-2.46,0.03,-9.02,2.59,0.54,-6.24,4.28,-3.91,-3.91,4.68,-2.98,-6.48,4.43,-4.54,-3.29,5.8,-4.15,-1.38,4.04,-7.06,-1.12,2.09,-8.92,-0.49,1.21,-12.21,-1.92,-2.18,-14.07,-4.48,-7.04,-18.67,-6.71,-12.01,-22.56,-12.08,-23.79,-26.8,-20.34,-28.44,-32.47,-24.23,-33.19,-34.5,-28.8,-40.43,-38.72,-34.65,-52.02,-43.14,-45.18,-51.13,-43.34,-49.91,-60.1,-47.61,-54.7,-65.79,-53.63,-52.43,-57.06,-50.75,-57.43,-63.06,-49.22,-59.7,-53.29,-43.76,-57.27,-55.19,-41.5,-54.3,-48.03,-40.49,-49.66,-41.42,-33.17,-42.22,-32.29,-28.12,-35.4,-23.75,-22.17,-29.24,-14.26,-17.64,-20.54,-9.13,-10.67,-16.47,0,-9.04,-8.43,4.32,-2.54,-1.77,9.6,0.85,5.94,12.74,4.19,5.56,14.98,3.22,11.85,13.86,2.36,12.75,17.28,2.37,17.53,17.37,5.33,18.73,13.97,4.08,12.06,6,8.06,17.87,9.75,8.65,16.18,6.41,4.05,18.69,2.25,10.41,13.19,0.58,4.31,9.44,0.72,8.74,10.31,-0.04,7.18,9.06,-1.99,10.85,6.23,-3.5,7.97,1,-4.16,5.18,-2.57,-5.63,3.97,-6.86,-6.62,0.27,-10.38,-8.91,-2.81,-15.89,-10.16,-6.04,-21.02,-19.15,-17.66,-27.27,-20.49,-19.35,-34.44,-25.71,-27.71,-40.84,-29.04,-37.68,-46.64,-33.32,-39.6,-46.36,-38.87,-44.95,-48.41,-41.87,-54.51,-50.59,-49.14,-56.07,-48.79,-42.75,-57.04,-46.5,-44.44,-58.96,-48.61,-44.94,-58.17,-43.32,-40.61,-48.76,-38.61,-39.06,-48.37,-30.39,-35.05,-38.6,-23.45,-32.43,-28.86,-18.96,-24.13,-23.17,-10.51,-18.94,-11.73,-3.81,-12.24,-5.15,1.61,-7.44,1.89,8.47,-1.8,7.58,8.9,3.43,13.53,14.41,3.67,18.09,12.01,8.96,23.27,12.11,10.03,20.26,9.94,11.96,23.62,9.12,12.69,19.57,5.43,10.05,16.69,7.84,15.84,13.03,5.75,13.63,15.96,-0.08,14.68,8.13,-3.71,9.25,8.76,0.03,11.81,4.27,-1.04,11.09,3.41,1.51,12.08,2.12,5.05,13.96,-1.05,1.3,11.14,-2.27,3.7,11.27,-1.81,6.57,7.42,-4.61,3.84,5.68,-6.48,3.03,1.15,-9.73,2.68,-3.24,-8.83,1.9,-8.56,-14.61,-2.6,-14.36,-19.49,-9.54,-17.5,-20.3,-14.01,-27.98,-26.34,-18.88,-32.16,-26.58,-27.45,-37.49,-33.7,-27.91,-43.93,-35.22,-37.35,-50.57,-37.68,-40.9,-47.47,-34.95,-41.39,-44.12,-37.74,-46.32,-45.1,-42.3,-49.32,-43.44,-36.78,-42.18,-43.24,-31.27,-39.25,-35.88,-25.33,-37.34,-30.25,-27.03,-33.08,-21.52,-20.84,-27.99,-14.74,-15.44,-20.54,-7.79,-8.94,-13.29,-0.26,-6.61,-6.01,5.86,-1.35,0.55,12.73,1.65,4.79,14.49,4.51,10.35,17.92,7.31,15.21,21.38,7.58,20.8,22.41,11.35,22.17,21.52,12.05,24.56,14.94,10.54,23.39,17.98,13.01,22.63,16.36,14.69,20.26,9.25,12.75,21.84,10.5,12.12,22,9.03,9.88,20.55,11.97,19.25,24.13,7.12,15.76,20.7,9.43,22.18,14.54,7.78,17.56,12.86,7.6,17.99,9.92,7.41,18.55,8.38,8.57,16.82,2.85,6.25,14.3,-0.8,3.32,7.81,-5.99,3.04,1.47,-11.83,-4.05,-5.48,-15.17,-7.29,-12.49,-25.07,-12.44,-21.64,-26.82,-18.57,-26.9,-33.15,-21.38,-36.18,-34.14,-24.96,-42.17,-38.41,-30.93,-49.83,-43.26,-36.86,-47.6,-41.28,-34.26,-47.65,-48.78,-40.49,-53.38,-41.03,-40.17,-46.59,-38.16,-35.26,-48.69,-32.91,-36.6,-41.1,-28.62,-34.91,-32.72,-18.2,-29.19,-25.03,-13.27,-21.89,-17.33,-6.42,-16.1,-7.45,-1.04,-8.13,0.68,7.68,-2.98,9.93,13.92,4.93,16.85,15.73,8.63,23.92,18.94,12.13,24.29,20.69,17.98,32.51,23.79,21.13,32.95,24.31,25.67,30.81,22.14,25.16,30.66,16.79,25.12,30.88,14.41,25.09,25.24,14.91,25.38,23.54,15.11,20.95,19.91,15.85,19.94,19.42</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B440" t="str">
+        <v>[L_24_标记]</v>
+      </c>
+      <c r="C440" t="str">
+        <v>幅值: 30.2uv 相位: 50.8°</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C440"/>
   </ignoredErrors>
 </worksheet>
 </file>